--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>23251</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>25.3500003814697</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>24.9500007629395</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>25.2000007629395</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>25.1499996185303</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>12922</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>25.2999992370605</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>24.7999992370605</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>25.2000007629395</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>25.3500003814697</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -62917,7 +62917,7 @@
         <v>12922</v>
       </c>
       <c r="C2720" t="n">
-        <v>25.2999992370605</v>
+        <v>25.3500003814697</v>
       </c>
       <c r="D2720" t="n">
         <v>24.7999992370605</v>
@@ -62929,6 +62929,29 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>15885</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="G2721" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>17400</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>25.9500007629395</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>25.3999996185303</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>25.3999996185303</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>25.8999996185303</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>12315</v>
+        <v>4772</v>
       </c>
       <c r="C2715" t="n">
-        <v>25.9500007629395</v>
+        <v>25.8999996185303</v>
       </c>
       <c r="D2715" t="n">
-        <v>25.5</v>
+        <v>25.5499992370605</v>
       </c>
       <c r="E2715" t="n">
         <v>25.7000007629395</v>
       </c>
       <c r="F2715" t="n">
-        <v>25.5</v>
+        <v>25.7000007629395</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>25736</v>
+        <v>12315</v>
       </c>
       <c r="C2716" t="n">
+        <v>25.9500007629395</v>
+      </c>
+      <c r="D2716" t="n">
         <v>25.5</v>
       </c>
-      <c r="D2716" t="n">
-        <v>24.7999992370605</v>
-      </c>
       <c r="E2716" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="F2716" t="n">
         <v>25.5</v>
-      </c>
-      <c r="F2716" t="n">
-        <v>25</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>13287</v>
+        <v>25736</v>
       </c>
       <c r="C2717" t="n">
-        <v>25.3500003814697</v>
+        <v>25.5</v>
       </c>
       <c r="D2717" t="n">
-        <v>24.8500003814697</v>
+        <v>24.7999992370605</v>
       </c>
       <c r="E2717" t="n">
-        <v>25.1000003814697</v>
+        <v>25.5</v>
       </c>
       <c r="F2717" t="n">
-        <v>25.1000003814697</v>
+        <v>25</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>14311</v>
+        <v>13287</v>
       </c>
       <c r="C2718" t="n">
-        <v>25.4500007629395</v>
+        <v>25.3500003814697</v>
       </c>
       <c r="D2718" t="n">
-        <v>24.9500007629395</v>
+        <v>24.8500003814697</v>
       </c>
       <c r="E2718" t="n">
         <v>25.1000003814697</v>
       </c>
       <c r="F2718" t="n">
-        <v>25.3500003814697</v>
+        <v>25.1000003814697</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>23251</v>
+        <v>14311</v>
       </c>
       <c r="C2719" t="n">
-        <v>25.3500003814697</v>
+        <v>25.4500007629395</v>
       </c>
       <c r="D2719" t="n">
         <v>24.9500007629395</v>
       </c>
       <c r="E2719" t="n">
-        <v>25.2000007629395</v>
+        <v>25.1000003814697</v>
       </c>
       <c r="F2719" t="n">
-        <v>25.1499996185303</v>
+        <v>25.3500003814697</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>12922</v>
+        <v>23251</v>
       </c>
       <c r="C2720" t="n">
         <v>25.3500003814697</v>
       </c>
       <c r="D2720" t="n">
-        <v>24.7999992370605</v>
+        <v>24.9500007629395</v>
       </c>
       <c r="E2720" t="n">
         <v>25.2000007629395</v>
       </c>
       <c r="F2720" t="n">
-        <v>25.3500003814697</v>
+        <v>25.1499996185303</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>15885</v>
+        <v>12922</v>
       </c>
       <c r="C2721" t="n">
-        <v>25.7000007629395</v>
+        <v>25.3500003814697</v>
       </c>
       <c r="D2721" t="n">
-        <v>25.25</v>
+        <v>24.7999992370605</v>
       </c>
       <c r="E2721" t="n">
-        <v>25.25</v>
+        <v>25.2000007629395</v>
       </c>
       <c r="F2721" t="n">
-        <v>25.7000007629395</v>
+        <v>25.3500003814697</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>17400</v>
+        <v>15885</v>
       </c>
       <c r="C2722" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>47218</v>
+      </c>
+      <c r="C2723" t="n">
         <v>25.9500007629395</v>
       </c>
-      <c r="D2722" t="n">
-        <v>25.3999996185303</v>
-      </c>
-      <c r="E2722" t="n">
-        <v>25.3999996185303</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>25.8999996185303</v>
-      </c>
-      <c r="G2722" t="s">
+      <c r="D2723" t="n">
+        <v>25.4500007629395</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>25.7999992370605</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>25.5499992370605</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>24.9500007629395</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>8877</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>25.3500003814697</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>24.8999996185303</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>24.8999996185303</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>24.8999996185303</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>25.2000007629395</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>17711</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>25.6000003814697</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>24.9500007629395</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>25.0499992370605</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>25.0499992370605</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>25.0499992370605</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>14715</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>25.3500003814697</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>24.8500003814697</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>25.3500003814697</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>25.3500003814697</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>24.9500007629395</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>16994</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>25.2000007629395</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>24.9500007629395</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>15309</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>24.7999992370605</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>24.5499992370605</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>20.625</v>
       </c>
       <c r="G2" t="n">
-        <v>13.2848091125488</v>
+        <v>13.2848119735718</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>13.4297351837158</v>
+        <v>13.4297370910645</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>12.8822402954102</v>
+        <v>12.8822412490845</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>12.1415138244629</v>
+        <v>12.1415128707886</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>12.0126924514771</v>
+        <v>12.0126876831055</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>17.75</v>
       </c>
       <c r="G12" t="n">
-        <v>11.4329891204834</v>
+        <v>11.4329872131348</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>16.75</v>
       </c>
       <c r="G14" t="n">
-        <v>10.7888784408569</v>
+        <v>10.788875579834</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>16.7749996185303</v>
       </c>
       <c r="G16" t="n">
-        <v>10.8049802780151</v>
+        <v>10.8049793243408</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G17" t="n">
-        <v>10.7953176498413</v>
+        <v>10.7953186035156</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G20" t="n">
-        <v>10.7115831375122</v>
+        <v>10.7115840911865</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G22" t="n">
-        <v>11.2397556304932</v>
+        <v>11.2397565841675</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>17.25</v>
       </c>
       <c r="G23" t="n">
-        <v>11.110933303833</v>
+        <v>11.1109323501587</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G24" t="n">
-        <v>10.9176998138428</v>
+        <v>10.9176988601685</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G25" t="n">
-        <v>10.8854932785034</v>
+        <v>10.8854942321777</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>16.2749996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>10.4829235076904</v>
+        <v>10.4829244613647</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>16.5</v>
       </c>
       <c r="G29" t="n">
-        <v>10.6278467178345</v>
+        <v>10.6278476715088</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>15.5749998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>10.0320453643799</v>
+        <v>10.0320463180542</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>16.5</v>
       </c>
       <c r="G32" t="n">
-        <v>10.6278467178345</v>
+        <v>10.6278476715088</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>16.75</v>
       </c>
       <c r="G33" t="n">
-        <v>10.7888784408569</v>
+        <v>10.788875579834</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>17.5</v>
       </c>
       <c r="G35" t="n">
-        <v>11.2719621658325</v>
+        <v>11.2719602584839</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>17.5</v>
       </c>
       <c r="G36" t="n">
-        <v>11.2719621658325</v>
+        <v>11.2719602584839</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>18</v>
       </c>
       <c r="G37" t="n">
-        <v>11.5940179824829</v>
+        <v>11.5940160751343</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G38" t="n">
-        <v>11.3041658401489</v>
+        <v>11.3041667938232</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>17.5450000762939</v>
       </c>
       <c r="G39" t="n">
-        <v>11.3009471893311</v>
+        <v>11.3009462356567</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>18.2450008392334</v>
       </c>
       <c r="G40" t="n">
-        <v>11.7518262863159</v>
+        <v>11.751823425293</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>18.25</v>
       </c>
       <c r="G41" t="n">
-        <v>11.7550449371338</v>
+        <v>11.7550430297852</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>18.4750003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>11.8999710083008</v>
+        <v>11.8999700546265</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>19.9950008392334</v>
       </c>
       <c r="G47" t="n">
-        <v>12.879020690918</v>
+        <v>12.8790225982666</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>19.5</v>
       </c>
       <c r="G49" t="n">
-        <v>12.5601854324341</v>
+        <v>12.5601835250854</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>19.5049991607666</v>
       </c>
       <c r="G53" t="n">
-        <v>12.5634069442749</v>
+        <v>12.5634050369263</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G55" t="n">
-        <v>12.3798313140869</v>
+        <v>12.3798341751099</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>20</v>
       </c>
       <c r="G56" t="n">
-        <v>12.8822402954102</v>
+        <v>12.8822412490845</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>12.785623550415</v>
+        <v>12.7856245040894</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G59" t="n">
-        <v>12.3411865234375</v>
+        <v>12.3411874771118</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>19.3950004577637</v>
       </c>
       <c r="G60" t="n">
-        <v>12.4925527572632</v>
+        <v>12.4925518035889</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>19.7749996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>12.7373161315918</v>
+        <v>12.7373151779175</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G63" t="n">
-        <v>12.6696844100952</v>
+        <v>12.6696853637695</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G64" t="n">
-        <v>12.6181554794312</v>
+        <v>12.6181545257568</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>19.5650005340576</v>
       </c>
       <c r="G65" t="n">
-        <v>12.6020545959473</v>
+        <v>12.6020526885986</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>19.1350002288818</v>
       </c>
       <c r="G67" t="n">
-        <v>12.325083732605</v>
+        <v>12.3250856399536</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>19.25</v>
       </c>
       <c r="G68" t="n">
-        <v>12.3991556167603</v>
+        <v>12.3991565704346</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G70" t="n">
-        <v>12.2413473129272</v>
+        <v>12.2413501739502</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>12.1415138244629</v>
+        <v>12.1415128707886</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>19.2950000762939</v>
       </c>
       <c r="G72" t="n">
-        <v>12.4281415939331</v>
+        <v>12.4281425476074</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G74" t="n">
-        <v>12.3476266860962</v>
+        <v>12.3476285934448</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G75" t="n">
-        <v>12.154393196106</v>
+        <v>12.1543941497803</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>18.9750003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>12.2220258712769</v>
+        <v>12.2220249176025</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>12.0126924514771</v>
+        <v>12.0126876831055</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>19.2250003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>12.3830547332764</v>
+        <v>12.3830537796021</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>12.0835418701172</v>
+        <v>12.0835447311401</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>19.1749992370605</v>
       </c>
       <c r="G81" t="n">
-        <v>12.350848197937</v>
+        <v>12.3508491516113</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>19.1949996948242</v>
       </c>
       <c r="G82" t="n">
-        <v>12.363730430603</v>
+        <v>12.3637313842773</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>19.0750007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>12.2864370346069</v>
+        <v>12.2864379882812</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>12.3032245635986</v>
+        <v>12.3032236099243</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>12.0298204421997</v>
+        <v>12.0298185348511</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>12.1730327606201</v>
+        <v>12.1730337142944</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>12.2706785202026</v>
+        <v>12.2706775665283</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G94" t="n">
-        <v>12.1079368591309</v>
+        <v>12.1079359054565</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>18.4750003814697</v>
       </c>
       <c r="G95" t="n">
-        <v>12.0265665054321</v>
+        <v>12.0265645980835</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G96" t="n">
-        <v>12.0949153900146</v>
+        <v>12.0949182510376</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>18.5</v>
       </c>
       <c r="G97" t="n">
-        <v>12.042839050293</v>
+        <v>12.0428400039673</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>17.8349990844727</v>
       </c>
       <c r="G99" t="n">
-        <v>11.6099481582642</v>
+        <v>11.6099472045898</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>18</v>
       </c>
       <c r="G100" t="n">
-        <v>11.7173585891724</v>
+        <v>11.7173566818237</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>18</v>
       </c>
       <c r="G101" t="n">
-        <v>11.7173585891724</v>
+        <v>11.7173566818237</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>18</v>
       </c>
       <c r="G103" t="n">
-        <v>11.7173585891724</v>
+        <v>11.7173566818237</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G104" t="n">
-        <v>11.7108459472656</v>
+        <v>11.7108469009399</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>17.8349990844727</v>
       </c>
       <c r="G105" t="n">
-        <v>11.6099481582642</v>
+        <v>11.6099472045898</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>11.6522607803345</v>
+        <v>11.6522598266602</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>18</v>
       </c>
       <c r="G107" t="n">
-        <v>11.7173585891724</v>
+        <v>11.7173566818237</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>11.6685342788696</v>
+        <v>11.6685352325439</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>11.6685342788696</v>
+        <v>11.6685352325439</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G110" t="n">
-        <v>11.5285778045654</v>
+        <v>11.5285758972168</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>18.5</v>
       </c>
       <c r="G111" t="n">
-        <v>12.042839050293</v>
+        <v>12.0428400039673</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G112" t="n">
-        <v>12.2641668319702</v>
+        <v>12.2641696929932</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>18.2150001525879</v>
       </c>
       <c r="G114" t="n">
-        <v>11.8573141098022</v>
+        <v>11.8573150634766</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G115" t="n">
-        <v>11.2551736831665</v>
+        <v>11.2551746368408</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G116" t="n">
-        <v>11.3332872390747</v>
+        <v>11.3332891464233</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>15.75</v>
       </c>
       <c r="G119" t="n">
-        <v>10.2526874542236</v>
+        <v>10.2526865005493</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G120" t="n">
-        <v>10.6432666778564</v>
+        <v>10.6432676315308</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G121" t="n">
-        <v>10.7734594345093</v>
+        <v>10.773458480835</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G122" t="n">
-        <v>10.9752578735352</v>
+        <v>10.9752569198608</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>15.7650003433228</v>
       </c>
       <c r="G124" t="n">
-        <v>10.2624521255493</v>
+        <v>10.262451171875</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>10.1875915527344</v>
+        <v>10.1875905990601</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>10.1875915527344</v>
+        <v>10.1875905990601</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>17.5</v>
       </c>
       <c r="G129" t="n">
-        <v>11.3918771743774</v>
+        <v>11.3918752670288</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>19.25</v>
       </c>
       <c r="G132" t="n">
-        <v>12.5310611724854</v>
+        <v>12.5310621261597</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>19.5</v>
       </c>
       <c r="G133" t="n">
-        <v>12.6938047409058</v>
+        <v>12.6938037872314</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G134" t="n">
-        <v>12.9867401123047</v>
+        <v>12.9867382049561</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G135" t="n">
-        <v>12.9606981277466</v>
+        <v>12.9607000350952</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>20</v>
       </c>
       <c r="G136" t="n">
-        <v>13.0192852020264</v>
+        <v>13.019287109375</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G137" t="n">
-        <v>12.9704627990723</v>
+        <v>12.9704637527466</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>20</v>
       </c>
       <c r="G138" t="n">
-        <v>13.0192852020264</v>
+        <v>13.019287109375</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>12.7914485931396</v>
+        <v>12.791449546814</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>19.6749992370605</v>
       </c>
       <c r="G140" t="n">
-        <v>12.8077220916748</v>
+        <v>12.8077230453491</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G141" t="n">
-        <v>12.8500347137451</v>
+        <v>12.8500356674194</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>19.3250007629395</v>
       </c>
       <c r="G142" t="n">
-        <v>12.5798854827881</v>
+        <v>12.5798873901367</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G143" t="n">
-        <v>12.5440816879272</v>
+        <v>12.5440826416016</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>19.25</v>
       </c>
       <c r="G144" t="n">
-        <v>12.5310611724854</v>
+        <v>12.5310621261597</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G145" t="n">
-        <v>12.4594583511353</v>
+        <v>12.4594573974609</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G146" t="n">
-        <v>12.4920053482056</v>
+        <v>12.4920043945312</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G147" t="n">
-        <v>12.5961589813232</v>
+        <v>12.5961599349976</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G148" t="n">
-        <v>12.5961589813232</v>
+        <v>12.5961599349976</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G151" t="n">
-        <v>12.3715734481812</v>
+        <v>12.3715772628784</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G152" t="n">
-        <v>12.6156883239746</v>
+        <v>12.6156854629517</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>12.6287088394165</v>
+        <v>12.6287069320679</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>19.3050003051758</v>
       </c>
       <c r="G155" t="n">
-        <v>12.5668659210205</v>
+        <v>12.5668668746948</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G156" t="n">
-        <v>12.687294960022</v>
+        <v>12.6872959136963</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G158" t="n">
-        <v>12.9867401123047</v>
+        <v>12.9867382049561</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>20.0550003051758</v>
       </c>
       <c r="G159" t="n">
-        <v>13.0550889968872</v>
+        <v>13.0550899505615</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>20</v>
       </c>
       <c r="G160" t="n">
-        <v>13.0192852020264</v>
+        <v>13.019287109375</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G161" t="n">
-        <v>12.9704627990723</v>
+        <v>12.9704637527466</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>19.8299999237061</v>
       </c>
       <c r="G164" t="n">
-        <v>12.9086227416992</v>
+        <v>12.9086236953735</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>19.9750003814697</v>
       </c>
       <c r="G165" t="n">
-        <v>13.0030126571655</v>
+        <v>13.0030107498169</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>13.3122224807739</v>
+        <v>13.3122205734253</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>21.0049991607666</v>
       </c>
       <c r="G168" t="n">
-        <v>13.6735038757324</v>
+        <v>13.6735029220581</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>21.3700008392334</v>
       </c>
       <c r="G169" t="n">
-        <v>13.9111099243164</v>
+        <v>13.9111070632935</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G170" t="n">
-        <v>14.1975297927856</v>
+        <v>14.19753074646</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>22</v>
       </c>
       <c r="G171" t="n">
-        <v>14.3212156295776</v>
+        <v>14.3212146759033</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>22.1949996948242</v>
       </c>
       <c r="G172" t="n">
-        <v>14.4481515884399</v>
+        <v>14.4481534957886</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>22.1949996948242</v>
       </c>
       <c r="G173" t="n">
-        <v>14.4481515884399</v>
+        <v>14.4481534957886</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>14.4188613891602</v>
+        <v>14.4188604354858</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G175" t="n">
-        <v>14.7508525848389</v>
+        <v>14.7508506774902</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>14.7117948532104</v>
+        <v>14.7117958068848</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>22</v>
       </c>
       <c r="G178" t="n">
-        <v>14.3212156295776</v>
+        <v>14.3212146759033</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G179" t="n">
-        <v>14.2691354751587</v>
+        <v>14.2691373825073</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G180" t="n">
-        <v>14.2691354751587</v>
+        <v>14.2691373825073</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>21.7049999237061</v>
       </c>
       <c r="G181" t="n">
-        <v>14.1291780471802</v>
+        <v>14.1291809082031</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>22</v>
       </c>
       <c r="G182" t="n">
-        <v>14.3212156295776</v>
+        <v>14.3212146759033</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>14.3863134384155</v>
+        <v>14.3863115310669</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G185" t="n">
-        <v>14.1910228729248</v>
+        <v>14.1910200119019</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>21.7549991607666</v>
       </c>
       <c r="G186" t="n">
-        <v>14.1617269515991</v>
+        <v>14.1617279052734</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>21.875</v>
       </c>
       <c r="G188" t="n">
-        <v>14.2398443222046</v>
+        <v>14.2398433685303</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G189" t="n">
-        <v>14.2691354751587</v>
+        <v>14.2691373825073</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>22</v>
       </c>
       <c r="G191" t="n">
-        <v>14.3212156295776</v>
+        <v>14.3212146759033</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G193" t="n">
-        <v>14.6271686553955</v>
+        <v>14.6271667480469</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>22.0149993896484</v>
       </c>
       <c r="G194" t="n">
-        <v>14.3309783935547</v>
+        <v>14.3309774398804</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>21.9249992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>14.2723903656006</v>
+        <v>14.2723913192749</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>22.1700000762939</v>
       </c>
       <c r="G196" t="n">
-        <v>14.4318742752075</v>
+        <v>14.4318799972534</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>21.7649993896484</v>
       </c>
       <c r="G201" t="n">
-        <v>14.1682367324829</v>
+        <v>14.1682386398315</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>21.4950008392334</v>
       </c>
       <c r="G202" t="n">
-        <v>13.9924793243408</v>
+        <v>13.9924764633179</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>13.8980855941772</v>
+        <v>13.8980894088745</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>22.3850002288818</v>
       </c>
       <c r="G205" t="n">
-        <v>14.571834564209</v>
+        <v>14.5718336105347</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>22.3050003051758</v>
       </c>
       <c r="G208" t="n">
-        <v>14.5197582244873</v>
+        <v>14.5197591781616</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>22.4950008392334</v>
       </c>
       <c r="G209" t="n">
-        <v>14.6434421539307</v>
+        <v>14.6434440612793</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G212" t="n">
-        <v>14.1910228729248</v>
+        <v>14.1910200119019</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>21.6849994659424</v>
       </c>
       <c r="G213" t="n">
-        <v>14.1161603927612</v>
+        <v>14.1161613464355</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>21.6049995422363</v>
       </c>
       <c r="G214" t="n">
-        <v>14.0640850067139</v>
+        <v>14.0640859603882</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G216" t="n">
-        <v>13.624683380127</v>
+        <v>13.6246814727783</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>21.0699996948242</v>
       </c>
       <c r="G217" t="n">
-        <v>13.7158184051514</v>
+        <v>13.7158174514771</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>20.7549991607666</v>
       </c>
       <c r="G218" t="n">
-        <v>13.510763168335</v>
+        <v>13.5107622146606</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>20.75</v>
       </c>
       <c r="G220" t="n">
-        <v>13.5075073242188</v>
+        <v>13.5075101852417</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>20.9750003814697</v>
       </c>
       <c r="G223" t="n">
-        <v>13.6539783477783</v>
+        <v>13.653977394104</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>21.2150001525879</v>
       </c>
       <c r="G224" t="n">
-        <v>13.8102083206177</v>
+        <v>13.810206413269</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G226" t="n">
-        <v>13.8134632110596</v>
+        <v>13.8134622573853</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G227" t="n">
-        <v>13.8915777206421</v>
+        <v>13.8915767669678</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>13.7678928375244</v>
+        <v>13.7678937911987</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G231" t="n">
-        <v>13.8915777206421</v>
+        <v>13.8915767669678</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>21.1949996948242</v>
       </c>
       <c r="G232" t="n">
-        <v>13.7971878051758</v>
+        <v>13.7971887588501</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>21.0650005340576</v>
       </c>
       <c r="G233" t="n">
-        <v>13.7125644683838</v>
+        <v>13.7125625610352</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>20.9099998474121</v>
       </c>
       <c r="G234" t="n">
-        <v>13.6116647720337</v>
+        <v>13.611665725708</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>20.7549991607666</v>
       </c>
       <c r="G235" t="n">
-        <v>13.510763168335</v>
+        <v>13.5107622146606</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G238" t="n">
-        <v>13.5726051330566</v>
+        <v>13.572606086731</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G239" t="n">
-        <v>13.5856227874756</v>
+        <v>13.5856256484985</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>20.9099998474121</v>
       </c>
       <c r="G240" t="n">
-        <v>13.6116647720337</v>
+        <v>13.611665725708</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G241" t="n">
-        <v>13.6897802352905</v>
+        <v>13.6897783279419</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>21.0699996948242</v>
       </c>
       <c r="G242" t="n">
-        <v>13.7158184051514</v>
+        <v>13.7158174514771</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>21.0949993133545</v>
       </c>
       <c r="G243" t="n">
-        <v>13.7320919036865</v>
+        <v>13.7320909500122</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>20.7549991607666</v>
       </c>
       <c r="G244" t="n">
-        <v>13.510763168335</v>
+        <v>13.5107622146606</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>20.9150009155273</v>
       </c>
       <c r="G245" t="n">
-        <v>13.6149206161499</v>
+        <v>13.6149196624756</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G247" t="n">
-        <v>13.5400552749634</v>
+        <v>13.5400562286377</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>13.7353458404541</v>
+        <v>13.7353477478027</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G250" t="n">
-        <v>13.6311922073364</v>
+        <v>13.6311950683594</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>13.7353458404541</v>
+        <v>13.7353477478027</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>13.9306344985962</v>
+        <v>13.9306354522705</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G254" t="n">
-        <v>14.1975297927856</v>
+        <v>14.19753074646</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>21.8050003051758</v>
       </c>
       <c r="G255" t="n">
-        <v>14.1942768096924</v>
+        <v>14.1942758560181</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>22.3250007629395</v>
       </c>
       <c r="G257" t="n">
-        <v>14.5327796936035</v>
+        <v>14.5327758789062</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>14.6141510009766</v>
+        <v>14.6141471862793</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>22.3449993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>14.5457963943481</v>
+        <v>14.5457983016968</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>14.5816011428833</v>
+        <v>14.5816020965576</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>14.5816011428833</v>
+        <v>14.5816020965576</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>22.6149997711182</v>
       </c>
       <c r="G263" t="n">
-        <v>14.7215576171875</v>
+        <v>14.7215557098389</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>22.875</v>
       </c>
       <c r="G264" t="n">
-        <v>14.8908071517944</v>
+        <v>14.8908081054688</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>14.776891708374</v>
+        <v>14.7768898010254</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>22.75</v>
       </c>
       <c r="G266" t="n">
-        <v>14.8094396591187</v>
+        <v>14.80943775177</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>22.8950004577637</v>
       </c>
       <c r="G267" t="n">
-        <v>14.903826713562</v>
+        <v>14.903829574585</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>22.1700000762939</v>
       </c>
       <c r="G268" t="n">
-        <v>14.4318742752075</v>
+        <v>14.4318799972534</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>22.3850002288818</v>
       </c>
       <c r="G269" t="n">
-        <v>14.571834564209</v>
+        <v>14.5718336105347</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>22.3449993133545</v>
       </c>
       <c r="G271" t="n">
-        <v>14.5457963943481</v>
+        <v>14.5457983016968</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>22.4950008392334</v>
       </c>
       <c r="G272" t="n">
-        <v>14.6434421539307</v>
+        <v>14.6434440612793</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G273" t="n">
-        <v>14.529522895813</v>
+        <v>14.5295238494873</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>22.7549991607666</v>
       </c>
       <c r="G274" t="n">
-        <v>14.812689781189</v>
+        <v>14.8126926422119</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>22.6350002288818</v>
       </c>
       <c r="G276" t="n">
-        <v>14.7345781326294</v>
+        <v>14.7345771789551</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G277" t="n">
-        <v>14.8354778289795</v>
+        <v>14.8354768753052</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>14.8419876098633</v>
+        <v>14.8419847488403</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>22.9650001525879</v>
       </c>
       <c r="G279" t="n">
-        <v>14.9493970870972</v>
+        <v>14.9493951797485</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G280" t="n">
-        <v>15.0828418731689</v>
+        <v>15.0828447341919</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>23.125</v>
       </c>
       <c r="G281" t="n">
-        <v>15.0535497665405</v>
+        <v>15.0535488128662</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>23.25</v>
       </c>
       <c r="G282" t="n">
-        <v>15.1349191665649</v>
+        <v>15.1349201202393</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>23.1350002288818</v>
       </c>
       <c r="G284" t="n">
-        <v>15.06005859375</v>
+        <v>15.0600595474243</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>23.25</v>
       </c>
       <c r="G285" t="n">
-        <v>15.1349191665649</v>
+        <v>15.1349201202393</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G286" t="n">
-        <v>15.0893535614014</v>
+        <v>15.0893516540527</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>23.0049991607666</v>
       </c>
       <c r="G287" t="n">
-        <v>14.9754323959351</v>
+        <v>14.9754343032837</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>22.9650001525879</v>
       </c>
       <c r="G288" t="n">
-        <v>14.9493970870972</v>
+        <v>14.9493951797485</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>22.7749996185303</v>
       </c>
       <c r="G289" t="n">
-        <v>14.8257141113281</v>
+        <v>14.8257093429565</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G292" t="n">
-        <v>14.9461421966553</v>
+        <v>14.946138381958</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>22.7749996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>14.8257141113281</v>
+        <v>14.8257093429565</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>14.8745336532593</v>
+        <v>14.8745365142822</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G297" t="n">
-        <v>14.9982204437256</v>
+        <v>14.9982175827026</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G298" t="n">
-        <v>15.0633125305176</v>
+        <v>15.0633144378662</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G301" t="n">
-        <v>15.4278526306152</v>
+        <v>15.4278545379639</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>24.25</v>
       </c>
       <c r="G302" t="n">
-        <v>15.7858829498291</v>
+        <v>15.7858848571777</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>24.25</v>
       </c>
       <c r="G303" t="n">
-        <v>15.7858829498291</v>
+        <v>15.7858848571777</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>24.25</v>
       </c>
       <c r="G304" t="n">
-        <v>15.7858829498291</v>
+        <v>15.7858848571777</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>24.2450008392334</v>
       </c>
       <c r="G305" t="n">
-        <v>15.7826328277588</v>
+        <v>15.7826309204102</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>24.2700004577637</v>
       </c>
       <c r="G306" t="n">
-        <v>15.798903465271</v>
+        <v>15.7989015579224</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>24.6749992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>16.0625419616699</v>
+        <v>16.0625438690186</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>25.125</v>
       </c>
       <c r="G309" t="n">
-        <v>16.3554763793945</v>
+        <v>16.3554782867432</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>25.375</v>
       </c>
       <c r="G310" t="n">
-        <v>16.518217086792</v>
+        <v>16.5182189941406</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>25.75</v>
       </c>
       <c r="G311" t="n">
-        <v>16.7623329162598</v>
+        <v>16.7623310089111</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>25.9249992370605</v>
       </c>
       <c r="G312" t="n">
-        <v>16.8762512207031</v>
+        <v>16.8762493133545</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>25.7250003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>16.746057510376</v>
+        <v>16.7460556030273</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>25.125</v>
       </c>
       <c r="G315" t="n">
-        <v>16.3554763793945</v>
+        <v>16.3554782867432</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>16.8599758148193</v>
+        <v>16.859977722168</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>26.3250007629395</v>
       </c>
       <c r="G324" t="n">
-        <v>17.1366367340088</v>
+        <v>17.1366348266602</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>26.25</v>
       </c>
       <c r="G326" t="n">
-        <v>17.0878143310547</v>
+        <v>17.0878124237061</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>26.125</v>
       </c>
       <c r="G327" t="n">
-        <v>17.006441116333</v>
+        <v>17.0064430236816</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>25.9750003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>16.9087982177734</v>
+        <v>16.9088001251221</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>25.7250003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>16.746057510376</v>
+        <v>16.7460556030273</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>25.9750003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>16.9087982177734</v>
+        <v>16.9088001251221</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>25.4249992370605</v>
       </c>
       <c r="G334" t="n">
-        <v>16.5507698059082</v>
+        <v>16.5507678985596</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>25.4750003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>16.5833129882812</v>
+        <v>16.5833148956299</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>25.5</v>
       </c>
       <c r="G336" t="n">
-        <v>16.599588394165</v>
+        <v>16.5995903015137</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G337" t="n">
-        <v>16.5670413970947</v>
+        <v>16.5670433044434</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G339" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G342" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>25.6749992370605</v>
       </c>
       <c r="G346" t="n">
-        <v>17.0451259613037</v>
+        <v>17.0451240539551</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>25.4750003814697</v>
       </c>
       <c r="G347" t="n">
-        <v>16.9123477935791</v>
+        <v>16.9123497009277</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>16.8957557678223</v>
+        <v>16.895751953125</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>17.028528213501</v>
+        <v>17.0285301208496</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>16.3646488189697</v>
+        <v>16.3646469116211</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>24.8799991607666</v>
       </c>
       <c r="G354" t="n">
-        <v>16.5173397064209</v>
+        <v>16.5173416137695</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>24.8299999237061</v>
       </c>
       <c r="G355" t="n">
-        <v>16.4841499328613</v>
+        <v>16.4841480255127</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G358" t="n">
-        <v>16.3248157501221</v>
+        <v>16.3248176574707</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G359" t="n">
-        <v>16.1986789703369</v>
+        <v>16.1986770629883</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G360" t="n">
-        <v>16.2119541168213</v>
+        <v>16.2119560241699</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G362" t="n">
-        <v>16.1256561279297</v>
+        <v>16.1256542205811</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>16.2318744659424</v>
+        <v>16.2318725585938</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G364" t="n">
-        <v>16.2783432006836</v>
+        <v>16.2783451080322</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G367" t="n">
-        <v>16.2982578277588</v>
+        <v>16.2982616424561</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>24.8299999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>16.4841499328613</v>
+        <v>16.4841480255127</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>16.0327110290527</v>
+        <v>16.0327072143555</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G371" t="n">
-        <v>15.9663209915161</v>
+        <v>15.9663190841675</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G373" t="n">
-        <v>15.880012512207</v>
+        <v>15.8800163269043</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>24.5</v>
       </c>
       <c r="G375" t="n">
-        <v>16.265064239502</v>
+        <v>16.2650661468506</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>24.5</v>
       </c>
       <c r="G376" t="n">
-        <v>16.265064239502</v>
+        <v>16.2650661468506</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>24.5</v>
       </c>
       <c r="G377" t="n">
-        <v>16.265064239502</v>
+        <v>16.2650661468506</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>16.1654834747314</v>
+        <v>16.1654853820801</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G379" t="n">
-        <v>16.2584285736084</v>
+        <v>16.2584266662598</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G380" t="n">
-        <v>16.2318744659424</v>
+        <v>16.2318725585938</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>24</v>
       </c>
       <c r="G383" t="n">
-        <v>15.933126449585</v>
+        <v>15.9331283569336</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>15.8667364120483</v>
+        <v>15.866738319397</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>23.5400009155273</v>
       </c>
       <c r="G385" t="n">
-        <v>15.6277408599854</v>
+        <v>15.6277446746826</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>15.6343774795532</v>
+        <v>15.6343812942505</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G388" t="n">
-        <v>15.5148839950562</v>
+        <v>15.5148801803589</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G389" t="n">
-        <v>15.5746288299561</v>
+        <v>15.5746307373047</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G392" t="n">
-        <v>15.9065685272217</v>
+        <v>15.9065704345703</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G393" t="n">
-        <v>15.8667364120483</v>
+        <v>15.866738319397</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>23.6100006103516</v>
       </c>
       <c r="G394" t="n">
-        <v>15.6742134094238</v>
+        <v>15.6742153167725</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G396" t="n">
-        <v>15.9198484420776</v>
+        <v>15.919846534729</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G400" t="n">
-        <v>15.733962059021</v>
+        <v>15.7339639663696</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G401" t="n">
-        <v>15.8667364120483</v>
+        <v>15.866738319397</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G402" t="n">
-        <v>15.9198484420776</v>
+        <v>15.919846534729</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>23.5400009155273</v>
       </c>
       <c r="G403" t="n">
-        <v>15.6277408599854</v>
+        <v>15.6277446746826</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G404" t="n">
-        <v>15.733962059021</v>
+        <v>15.7339639663696</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>24</v>
       </c>
       <c r="G405" t="n">
-        <v>15.933126449585</v>
+        <v>15.9331283569336</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G406" t="n">
-        <v>16.0659008026123</v>
+        <v>16.0659027099609</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G408" t="n">
-        <v>15.826904296875</v>
+        <v>15.8269062042236</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>24</v>
       </c>
       <c r="G409" t="n">
-        <v>15.933126449585</v>
+        <v>15.9331283569336</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>15.880012512207</v>
+        <v>15.8800163269043</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>24</v>
       </c>
       <c r="G411" t="n">
-        <v>15.933126449585</v>
+        <v>15.9331283569336</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G412" t="n">
-        <v>15.8667364120483</v>
+        <v>15.866738319397</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>23.9300003051758</v>
       </c>
       <c r="G413" t="n">
-        <v>15.8866558074951</v>
+        <v>15.8866548538208</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>23.7600002288818</v>
       </c>
       <c r="G416" t="n">
-        <v>15.773796081543</v>
+        <v>15.7737941741943</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>15.8999328613281</v>
+        <v>15.8999309539795</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G420" t="n">
-        <v>15.9198484420776</v>
+        <v>15.919846534729</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>15.8335437774658</v>
+        <v>15.8335418701172</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G423" t="n">
-        <v>15.9198484420776</v>
+        <v>15.919846534729</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>23.7099990844727</v>
       </c>
       <c r="G425" t="n">
-        <v>15.7405996322632</v>
+        <v>15.7406015396118</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>23.6100006103516</v>
       </c>
       <c r="G426" t="n">
-        <v>15.6742134094238</v>
+        <v>15.6742153167725</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>23.9899997711182</v>
       </c>
       <c r="G428" t="n">
-        <v>15.9264888763428</v>
+        <v>15.9264869689941</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>15.5679941177368</v>
+        <v>15.5679931640625</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G432" t="n">
-        <v>15.5945491790771</v>
+        <v>15.5945453643799</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G435" t="n">
-        <v>15.3024415969849</v>
+        <v>15.3024406433105</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>14.9705009460449</v>
+        <v>14.970498085022</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G437" t="n">
-        <v>14.9107522964478</v>
+        <v>14.9107503890991</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G438" t="n">
-        <v>15.3356351852417</v>
+        <v>15.3356332778931</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G439" t="n">
-        <v>15.1829404830933</v>
+        <v>15.1829423904419</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>15.1696643829346</v>
+        <v>15.1696653366089</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G442" t="n">
-        <v>14.9705009460449</v>
+        <v>14.970498085022</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G443" t="n">
-        <v>15.3754682540894</v>
+        <v>15.3754692077637</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>23.0900001525879</v>
       </c>
       <c r="G444" t="n">
-        <v>15.3289957046509</v>
+        <v>15.3289947509766</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>22.6800003051758</v>
       </c>
       <c r="G446" t="n">
-        <v>15.0568027496338</v>
+        <v>15.0568056106567</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G447" t="n">
-        <v>15.2426919937134</v>
+        <v>15.2426900863647</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>22.8299999237061</v>
       </c>
       <c r="G448" t="n">
-        <v>15.1563863754272</v>
+        <v>15.1563854217529</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>23</v>
       </c>
       <c r="G449" t="n">
-        <v>15.2692441940308</v>
+        <v>15.2692470550537</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G450" t="n">
-        <v>15.2626094818115</v>
+        <v>15.2626047134399</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>23.2299995422363</v>
       </c>
       <c r="G451" t="n">
-        <v>15.4219398498535</v>
+        <v>15.4219379425049</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G452" t="n">
-        <v>15.2958030700684</v>
+        <v>15.2958011627197</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>15.0368881225586</v>
+        <v>15.03688621521</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>22.7800006866455</v>
       </c>
       <c r="G454" t="n">
-        <v>15.1231937408447</v>
+        <v>15.1231927871704</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G456" t="n">
-        <v>14.9173908233643</v>
+        <v>14.9173879623413</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G457" t="n">
-        <v>14.8576393127441</v>
+        <v>14.8576402664185</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G458" t="n">
-        <v>14.6717557907104</v>
+        <v>14.6717538833618</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G459" t="n">
-        <v>14.7381439208984</v>
+        <v>14.7381420135498</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G460" t="n">
-        <v>14.7514181137085</v>
+        <v>14.7514190673828</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>14.7049503326416</v>
+        <v>14.7049465179443</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G462" t="n">
-        <v>14.7978925704956</v>
+        <v>14.7978916168213</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G463" t="n">
-        <v>14.6850328445435</v>
+        <v>14.6850337982178</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>22.6100006103516</v>
       </c>
       <c r="G464" t="n">
-        <v>15.0103340148926</v>
+        <v>15.0103321075439</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G466" t="n">
-        <v>14.8576393127441</v>
+        <v>14.8576402664185</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>14.9041137695312</v>
+        <v>14.9041109085083</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G468" t="n">
-        <v>15.348913192749</v>
+        <v>15.3489103317261</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G469" t="n">
-        <v>15.2626094818115</v>
+        <v>15.2626047134399</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G470" t="n">
-        <v>15.3356351852417</v>
+        <v>15.3356332778931</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G471" t="n">
-        <v>15.3688278198242</v>
+        <v>15.3688268661499</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G472" t="n">
-        <v>15.3821039199829</v>
+        <v>15.3821058273315</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>23.25</v>
       </c>
       <c r="G473" t="n">
-        <v>15.4352140426636</v>
+        <v>15.4352178573608</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G474" t="n">
-        <v>15.3688278198242</v>
+        <v>15.3688268661499</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G475" t="n">
-        <v>15.2559680938721</v>
+        <v>15.2559719085693</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G476" t="n">
-        <v>15.2626094818115</v>
+        <v>15.2626047134399</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G477" t="n">
-        <v>15.196216583252</v>
+        <v>15.1962213516235</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G478" t="n">
-        <v>14.890832901001</v>
+        <v>14.8908357620239</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G479" t="n">
-        <v>14.7381439208984</v>
+        <v>14.7381420135498</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G480" t="n">
-        <v>14.7115879058838</v>
+        <v>14.7115869522095</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>22</v>
       </c>
       <c r="G481" t="n">
-        <v>14.6053676605225</v>
+        <v>14.6053667068481</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G482" t="n">
-        <v>14.6319227218628</v>
+        <v>14.6319217681885</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G483" t="n">
-        <v>14.8178081512451</v>
+        <v>14.8178071975708</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G484" t="n">
-        <v>14.6584749221802</v>
+        <v>14.6584768295288</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G485" t="n">
-        <v>14.7381439208984</v>
+        <v>14.7381420135498</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>14.7381439208984</v>
+        <v>14.7381420135498</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G487" t="n">
-        <v>14.7248630523682</v>
+        <v>14.7248659133911</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>14.8045310974121</v>
+        <v>14.8045301437378</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G490" t="n">
-        <v>15.0435276031494</v>
+        <v>15.0435266494751</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G491" t="n">
-        <v>15.348913192749</v>
+        <v>15.3489103317261</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>15.733962059021</v>
+        <v>15.7339639663696</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>15.5347986221313</v>
+        <v>15.5347967147827</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>24.0699996948242</v>
       </c>
       <c r="G495" t="n">
-        <v>15.9795989990234</v>
+        <v>15.9795970916748</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G496" t="n">
-        <v>15.733962059021</v>
+        <v>15.7339639663696</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>23.7299995422363</v>
       </c>
       <c r="G498" t="n">
-        <v>15.7538795471191</v>
+        <v>15.7538776397705</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>24.1100006103516</v>
       </c>
       <c r="G499" t="n">
-        <v>16.0061550140381</v>
+        <v>16.0061531066895</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G500" t="n">
-        <v>15.880012512207</v>
+        <v>15.8800163269043</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>23.7900009155273</v>
       </c>
       <c r="G501" t="n">
-        <v>15.7937135696411</v>
+        <v>15.7937116622925</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>23.7600002288818</v>
       </c>
       <c r="G502" t="n">
-        <v>15.773796081543</v>
+        <v>15.7737941741943</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>15.3688278198242</v>
+        <v>15.3688268661499</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G504" t="n">
-        <v>15.4816865921021</v>
+        <v>15.4816884994507</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>23.4799995422363</v>
       </c>
       <c r="G505" t="n">
-        <v>15.5879106521606</v>
+        <v>15.5879068374634</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>24.1900005340576</v>
       </c>
       <c r="G507" t="n">
-        <v>16.0592632293701</v>
+        <v>16.0592651367188</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G508" t="n">
-        <v>15.9065685272217</v>
+        <v>15.9065704345703</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>24.2800006866455</v>
       </c>
       <c r="G510" t="n">
-        <v>16.119010925293</v>
+        <v>16.1190128326416</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G511" t="n">
-        <v>15.8335437774658</v>
+        <v>15.8335418701172</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G512" t="n">
-        <v>16.0194301605225</v>
+        <v>16.0194320678711</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>24.5</v>
       </c>
       <c r="G515" t="n">
-        <v>16.265064239502</v>
+        <v>16.2650661468506</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>24.5</v>
       </c>
       <c r="G519" t="n">
-        <v>16.265064239502</v>
+        <v>16.2650661468506</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>16.4642314910889</v>
+        <v>16.4642295837402</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>16.4642314910889</v>
+        <v>16.4642295837402</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G524" t="n">
-        <v>16.5638122558594</v>
+        <v>16.563814163208</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>16.5638122558594</v>
+        <v>16.563814163208</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G528" t="n">
-        <v>16.4642314910889</v>
+        <v>16.4642295837402</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>16.4642314910889</v>
+        <v>16.4642295837402</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G532" t="n">
-        <v>16.3646488189697</v>
+        <v>16.3646469116211</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G534" t="n">
-        <v>16.2318744659424</v>
+        <v>16.2318725585938</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>15.6343774795532</v>
+        <v>15.6343812942505</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>15.5347986221313</v>
+        <v>15.5347967147827</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>15.3024415969849</v>
+        <v>15.3024406433105</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G541" t="n">
-        <v>15.5347986221313</v>
+        <v>15.5347967147827</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G542" t="n">
-        <v>15.5679941177368</v>
+        <v>15.5679931640625</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>15.8335437774658</v>
+        <v>15.8335418701172</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>23.5</v>
       </c>
       <c r="G544" t="n">
-        <v>15.6011867523193</v>
+        <v>15.6011848449707</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>15.733962059021</v>
+        <v>15.7339639663696</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>23.5</v>
       </c>
       <c r="G546" t="n">
-        <v>15.6011867523193</v>
+        <v>15.6011848449707</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>23.5</v>
       </c>
       <c r="G548" t="n">
-        <v>15.6011867523193</v>
+        <v>15.6011848449707</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G549" t="n">
-        <v>15.5347986221313</v>
+        <v>15.5347967147827</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G550" t="n">
-        <v>15.3024415969849</v>
+        <v>15.3024406433105</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>15.5347986221313</v>
+        <v>15.5347967147827</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>15.3688278198242</v>
+        <v>15.3688268661499</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G553" t="n">
-        <v>15.5016040802002</v>
+        <v>15.5016059875488</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>15.733962059021</v>
+        <v>15.7339639663696</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>23</v>
       </c>
       <c r="G555" t="n">
-        <v>15.2692441940308</v>
+        <v>15.2692470550537</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>15.0036945343018</v>
+        <v>15.0036964416504</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>15.0368881225586</v>
+        <v>15.03688621521</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>15.3356351852417</v>
+        <v>15.3356332778931</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>15.5016040802002</v>
+        <v>15.5016059875488</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G561" t="n">
-        <v>15.5347986221313</v>
+        <v>15.5347967147827</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>23.5</v>
       </c>
       <c r="G562" t="n">
-        <v>15.6011867523193</v>
+        <v>15.6011848449707</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>15.6343774795532</v>
+        <v>15.6343812942505</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G565" t="n">
-        <v>15.0036945343018</v>
+        <v>15.0036964416504</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>15.1696643829346</v>
+        <v>15.1696653366089</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G567" t="n">
-        <v>15.0700845718384</v>
+        <v>15.0700817108154</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G568" t="n">
-        <v>14.9705009460449</v>
+        <v>14.970498085022</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G569" t="n">
-        <v>14.7049503326416</v>
+        <v>14.7049465179443</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>21.75</v>
       </c>
       <c r="G570" t="n">
-        <v>14.4393978118896</v>
+        <v>14.4393949508667</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>14.1738424301147</v>
+        <v>14.173846244812</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G572" t="n">
-        <v>14.3398122787476</v>
+        <v>14.3398141860962</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G573" t="n">
-        <v>14.4062004089355</v>
+        <v>14.4062032699585</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G574" t="n">
-        <v>15.1696643829346</v>
+        <v>15.1696653366089</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G575" t="n">
-        <v>14.8709182739258</v>
+        <v>14.8709192276001</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>14.5389766693115</v>
+        <v>14.5389776229858</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G577" t="n">
-        <v>14.6717557907104</v>
+        <v>14.6717538833618</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>22</v>
       </c>
       <c r="G578" t="n">
-        <v>14.6053676605225</v>
+        <v>14.6053667068481</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>14.4725923538208</v>
+        <v>14.4725885391235</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>14.5389766693115</v>
+        <v>14.5389776229858</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>14.5389766693115</v>
+        <v>14.5389776229858</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>14.4725923538208</v>
+        <v>14.4725885391235</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>22</v>
       </c>
       <c r="G586" t="n">
-        <v>14.6053676605225</v>
+        <v>14.6053667068481</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>15.0368881225586</v>
+        <v>15.03688621521</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>15.0368881225586</v>
+        <v>15.03688621521</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>14.6717557907104</v>
+        <v>14.6717538833618</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G594" t="n">
-        <v>14.9041137695312</v>
+        <v>14.9041109085083</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>22.75</v>
       </c>
       <c r="G595" t="n">
-        <v>15.1032781600952</v>
+        <v>15.1032743453979</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>15.0700845718384</v>
+        <v>15.0700817108154</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>15.0700845718384</v>
+        <v>15.0700817108154</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G598" t="n">
-        <v>15.4102640151978</v>
+        <v>15.4102621078491</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>15.2741918563843</v>
+        <v>15.2741899490356</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>15.4102640151978</v>
+        <v>15.4102621078491</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>22.25</v>
       </c>
       <c r="G602" t="n">
-        <v>15.1381187438965</v>
+        <v>15.1381206512451</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G603" t="n">
-        <v>15.2741918563843</v>
+        <v>15.2741899490356</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>15.0020446777344</v>
+        <v>15.0020427703857</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>14.7639169692993</v>
+        <v>14.7639188766479</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>21.75</v>
       </c>
       <c r="G606" t="n">
-        <v>14.7979364395142</v>
+        <v>14.7979354858398</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>14.2196254730225</v>
+        <v>14.2196264266968</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>13.8794431686401</v>
+        <v>13.8794422149658</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G610" t="n">
-        <v>13.9134607315063</v>
+        <v>13.9134616851807</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>20.5</v>
       </c>
       <c r="G612" t="n">
-        <v>13.9474782943726</v>
+        <v>13.9474773406982</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G613" t="n">
-        <v>13.3623638153076</v>
+        <v>13.3623628616333</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G614" t="n">
-        <v>13.5800809860229</v>
+        <v>13.5800819396973</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>14.0495347976685</v>
+        <v>14.0495338439941</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>21.25</v>
       </c>
       <c r="G617" t="n">
-        <v>14.4577541351318</v>
+        <v>14.4577522277832</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>14.4917707443237</v>
+        <v>14.4917697906494</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>21</v>
       </c>
       <c r="G620" t="n">
-        <v>14.2876605987549</v>
+        <v>14.2876625061035</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G621" t="n">
-        <v>14.3216800689697</v>
+        <v>14.3216781616211</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>14.1515865325928</v>
+        <v>14.1515874862671</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G625" t="n">
-        <v>14.7639169692993</v>
+        <v>14.7639188766479</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>21.5</v>
       </c>
       <c r="G626" t="n">
-        <v>14.6278429031372</v>
+        <v>14.6278438568115</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>21.5</v>
       </c>
       <c r="G627" t="n">
-        <v>14.6278429031372</v>
+        <v>14.6278438568115</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G628" t="n">
-        <v>14.3216800689697</v>
+        <v>14.3216781616211</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G629" t="n">
-        <v>14.0155143737793</v>
+        <v>14.0155181884766</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>14.0835523605347</v>
+        <v>14.0835542678833</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>13.743371963501</v>
+        <v>13.743369102478</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G632" t="n">
-        <v>13.5528688430786</v>
+        <v>13.55286693573</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G633" t="n">
-        <v>14.0155143737793</v>
+        <v>14.0155181884766</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>14.1515865325928</v>
+        <v>14.1515874862671</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>14.0155143737793</v>
+        <v>14.0155181884766</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G636" t="n">
-        <v>14.0155143737793</v>
+        <v>14.0155181884766</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>21</v>
       </c>
       <c r="G637" t="n">
-        <v>14.2876605987549</v>
+        <v>14.2876625061035</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G638" t="n">
-        <v>14.2536430358887</v>
+        <v>14.2536449432373</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>14.1515865325928</v>
+        <v>14.1515874862671</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>20.5</v>
       </c>
       <c r="G640" t="n">
-        <v>13.9474782943726</v>
+        <v>13.9474773406982</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G642" t="n">
-        <v>13.8114061355591</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>14.2196254730225</v>
+        <v>14.2196264266968</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G644" t="n">
-        <v>14.2196254730225</v>
+        <v>14.2196264266968</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>20.5</v>
       </c>
       <c r="G645" t="n">
-        <v>13.9474782943726</v>
+        <v>13.9474773406982</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>14.0495347976685</v>
+        <v>14.0495338439941</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>14.0495347976685</v>
+        <v>14.0495338439941</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>13.8454236984253</v>
+        <v>13.8454256057739</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>13.8454236984253</v>
+        <v>13.8454256057739</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G651" t="n">
-        <v>14.2536430358887</v>
+        <v>14.2536449432373</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G652" t="n">
-        <v>14.1515865325928</v>
+        <v>14.1515874862671</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>13.9134607315063</v>
+        <v>13.9134616851807</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>13.8114061355591</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>20</v>
       </c>
       <c r="G655" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072969436646</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>13.6413145065308</v>
+        <v>13.6413154602051</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>13.743371963501</v>
+        <v>13.743369102478</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>20.5</v>
       </c>
       <c r="G659" t="n">
-        <v>13.9474782943726</v>
+        <v>13.9474773406982</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>20.5</v>
       </c>
       <c r="G660" t="n">
-        <v>13.9474782943726</v>
+        <v>13.9474773406982</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>13.8454236984253</v>
+        <v>13.8454256057739</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>13.743371963501</v>
+        <v>13.743369102478</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G663" t="n">
-        <v>13.743371963501</v>
+        <v>13.743369102478</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>13.6753339767456</v>
+        <v>13.6753349304199</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G666" t="n">
-        <v>13.5800809860229</v>
+        <v>13.5800819396973</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>13.6413145065308</v>
+        <v>13.6413154602051</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G670" t="n">
-        <v>13.4167947769165</v>
+        <v>13.4167957305908</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G672" t="n">
-        <v>13.2943286895752</v>
+        <v>13.2943305969238</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G674" t="n">
-        <v>13.335150718689</v>
+        <v>13.3351516723633</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G675" t="n">
-        <v>13.4848318099976</v>
+        <v>13.4848327636719</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>13.4712228775024</v>
+        <v>13.4712247848511</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G678" t="n">
-        <v>13.5664749145508</v>
+        <v>13.5664758682251</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G679" t="n">
-        <v>13.4712228775024</v>
+        <v>13.4712247848511</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G680" t="n">
-        <v>13.4440088272095</v>
+        <v>13.4440097808838</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G682" t="n">
-        <v>13.4440088272095</v>
+        <v>13.4440097808838</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G683" t="n">
-        <v>13.4440088272095</v>
+        <v>13.4440097808838</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>13.4712228775024</v>
+        <v>13.4712247848511</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G685" t="n">
-        <v>13.5256538391113</v>
+        <v>13.5256519317627</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G686" t="n">
-        <v>13.5800809860229</v>
+        <v>13.5800819396973</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G687" t="n">
-        <v>13.5528688430786</v>
+        <v>13.55286693573</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G688" t="n">
-        <v>13.4712228775024</v>
+        <v>13.4712247848511</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>13.4712228775024</v>
+        <v>13.4712247848511</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G690" t="n">
-        <v>13.5936880111694</v>
+        <v>13.5936899185181</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G691" t="n">
-        <v>13.5936880111694</v>
+        <v>13.5936899185181</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>13.6413145065308</v>
+        <v>13.6413154602051</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G693" t="n">
-        <v>13.8454236984253</v>
+        <v>13.8454256057739</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>13.9134607315063</v>
+        <v>13.9134616851807</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G695" t="n">
-        <v>14.0155143737793</v>
+        <v>14.0155181884766</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>21</v>
       </c>
       <c r="G697" t="n">
-        <v>14.2876605987549</v>
+        <v>14.2876625061035</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G698" t="n">
-        <v>14.3556995391846</v>
+        <v>14.3556985855103</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>21</v>
       </c>
       <c r="G700" t="n">
-        <v>14.2876605987549</v>
+        <v>14.2876625061035</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>20.75</v>
       </c>
       <c r="G701" t="n">
-        <v>14.1175708770752</v>
+        <v>14.1175699234009</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>20</v>
       </c>
       <c r="G703" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072969436646</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>14.0155143737793</v>
+        <v>14.0155181884766</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>20.5</v>
       </c>
       <c r="G705" t="n">
-        <v>13.9474782943726</v>
+        <v>13.9474773406982</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G706" t="n">
-        <v>13.5528688430786</v>
+        <v>13.55286693573</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G708" t="n">
-        <v>12.9949703216553</v>
+        <v>12.9949684143066</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G709" t="n">
-        <v>12.9813613891602</v>
+        <v>12.9813604354858</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G711" t="n">
-        <v>12.9541463851929</v>
+        <v>12.9541454315186</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G712" t="n">
-        <v>12.9541463851929</v>
+        <v>12.9541454315186</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G714" t="n">
-        <v>13.0221815109253</v>
+        <v>13.0221843719482</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G715" t="n">
-        <v>12.6683959960938</v>
+        <v>12.6683940887451</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G716" t="n">
-        <v>12.3009967803955</v>
+        <v>12.3009958267212</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G718" t="n">
-        <v>11.7022771835327</v>
+        <v>11.7022762298584</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G719" t="n">
-        <v>12.1785297393799</v>
+        <v>12.1785306930542</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G720" t="n">
-        <v>12.8997173309326</v>
+        <v>12.8997163772583</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>12.9949703216553</v>
+        <v>12.9949684143066</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G723" t="n">
-        <v>13.0357904434204</v>
+        <v>13.0357894897461</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>19.5</v>
       </c>
       <c r="G724" t="n">
-        <v>13.2671165466309</v>
+        <v>13.2671127319336</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G725" t="n">
-        <v>13.5256538391113</v>
+        <v>13.5256519317627</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>13.8794431686401</v>
+        <v>13.8794422149658</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>20</v>
       </c>
       <c r="G727" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072969436646</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>13.4712228775024</v>
+        <v>13.4712247848511</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G729" t="n">
-        <v>13.2535076141357</v>
+        <v>13.2535066604614</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G730" t="n">
-        <v>13.0766134262085</v>
+        <v>13.0766124725342</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G731" t="n">
-        <v>12.940541267395</v>
+        <v>12.9405393600464</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>12.5187139511108</v>
+        <v>12.5187129974365</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G735" t="n">
-        <v>12.6547880172729</v>
+        <v>12.6547861099243</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>12.6547880172729</v>
+        <v>12.6547861099243</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>12.7908592224121</v>
+        <v>12.7908582687378</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G738" t="n">
-        <v>12.4370698928833</v>
+        <v>12.4370708465576</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G739" t="n">
-        <v>12.5459289550781</v>
+        <v>12.5459280014038</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G740" t="n">
-        <v>12.5051040649414</v>
+        <v>12.50510597229</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>12.7908592224121</v>
+        <v>12.7908582687378</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G742" t="n">
-        <v>12.7364282608032</v>
+        <v>12.7364292144775</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>12.6547880172729</v>
+        <v>12.6547861099243</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G744" t="n">
-        <v>12.6003561019897</v>
+        <v>12.6003580093384</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G745" t="n">
-        <v>12.5459289550781</v>
+        <v>12.5459280014038</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>13.1310434341431</v>
+        <v>13.1310424804688</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G747" t="n">
-        <v>13.4440088272095</v>
+        <v>13.4440097808838</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G749" t="n">
-        <v>13.1582546234131</v>
+        <v>13.1582555770874</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G750" t="n">
-        <v>12.5731430053711</v>
+        <v>12.5731420516968</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>18.5</v>
       </c>
       <c r="G753" t="n">
-        <v>12.5867500305176</v>
+        <v>12.5867490768433</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G754" t="n">
-        <v>12.8452882766724</v>
+        <v>12.8452863693237</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>12.7908592224121</v>
+        <v>12.7908582687378</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G757" t="n">
-        <v>12.5459289550781</v>
+        <v>12.5459280014038</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G758" t="n">
-        <v>12.4370698928833</v>
+        <v>12.4370708465576</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G759" t="n">
-        <v>12.3554239273071</v>
+        <v>12.3554248809814</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G761" t="n">
-        <v>12.4098539352417</v>
+        <v>12.409854888916</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G762" t="n">
-        <v>12.1241016387939</v>
+        <v>12.1241025924683</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G763" t="n">
-        <v>12.5051040649414</v>
+        <v>12.50510597229</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G764" t="n">
-        <v>12.7364282608032</v>
+        <v>12.7364292144775</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G765" t="n">
-        <v>13.2126846313477</v>
+        <v>13.212685585022</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>19.5</v>
       </c>
       <c r="G766" t="n">
-        <v>13.2671165466309</v>
+        <v>13.2671127319336</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G767" t="n">
-        <v>13.2535076141357</v>
+        <v>13.2535066604614</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>13.063006401062</v>
+        <v>13.0630054473877</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G769" t="n">
-        <v>12.9949703216553</v>
+        <v>12.9949684143066</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G770" t="n">
-        <v>13.0221815109253</v>
+        <v>13.0221843719482</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G771" t="n">
-        <v>13.0085773468018</v>
+        <v>13.0085763931274</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G772" t="n">
-        <v>12.940541267395</v>
+        <v>12.9405393600464</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>13.1990785598755</v>
+        <v>13.1990776062012</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G775" t="n">
-        <v>13.3079347610474</v>
+        <v>13.3079357147217</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G776" t="n">
-        <v>13.2535076141357</v>
+        <v>13.2535066604614</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>13.063006401062</v>
+        <v>13.0630054473877</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G778" t="n">
-        <v>13.2398986816406</v>
+        <v>13.2398977279663</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G779" t="n">
-        <v>13.2943286895752</v>
+        <v>13.2943305969238</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>13.4712228775024</v>
+        <v>13.4712247848511</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G783" t="n">
-        <v>13.3623638153076</v>
+        <v>13.3623628616333</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G784" t="n">
-        <v>13.335150718689</v>
+        <v>13.3351516723633</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>13.1990785598755</v>
+        <v>13.1990776062012</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G786" t="n">
-        <v>13.2262926101685</v>
+        <v>13.2262945175171</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>13.8114061355591</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G790" t="n">
-        <v>13.5528688430786</v>
+        <v>13.55286693573</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G792" t="n">
-        <v>13.4440088272095</v>
+        <v>13.4440097808838</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>13.4712228775024</v>
+        <v>13.4712247848511</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G794" t="n">
-        <v>13.5256538391113</v>
+        <v>13.5256519317627</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G795" t="n">
-        <v>13.5256538391113</v>
+        <v>13.5256519317627</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G796" t="n">
-        <v>13.8114061355591</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>13.6753339767456</v>
+        <v>13.6753349304199</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>13.6753339767456</v>
+        <v>13.6753349304199</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>20</v>
       </c>
       <c r="G800" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072969436646</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>20</v>
       </c>
       <c r="G801" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072969436646</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G802" t="n">
-        <v>13.5528688430786</v>
+        <v>13.55286693573</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>13.6413145065308</v>
+        <v>13.6413154602051</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G807" t="n">
-        <v>13.5800809860229</v>
+        <v>13.5800819396973</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G809" t="n">
-        <v>13.4712228775024</v>
+        <v>13.4712247848511</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>20.5</v>
       </c>
       <c r="G810" t="n">
-        <v>13.9474782943726</v>
+        <v>13.9474773406982</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G811" t="n">
-        <v>13.8114061355591</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>13.6753339767456</v>
+        <v>13.6753349304199</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>20</v>
       </c>
       <c r="G813" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072969436646</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>20</v>
       </c>
       <c r="G815" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072969436646</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>13.6753339767456</v>
+        <v>13.6753349304199</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>13.743371963501</v>
+        <v>13.743369102478</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>14.0155143737793</v>
+        <v>14.0155181884766</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>20.5</v>
       </c>
       <c r="G820" t="n">
-        <v>13.9474782943726</v>
+        <v>13.9474773406982</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>13.8794431686401</v>
+        <v>13.8794422149658</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>13.743371963501</v>
+        <v>13.743369102478</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G823" t="n">
-        <v>13.6753339767456</v>
+        <v>13.6753349304199</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>13.8794431686401</v>
+        <v>13.8794422149658</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>13.8794431686401</v>
+        <v>13.8794422149658</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>13.8114061355591</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>13.8114061355591</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G830" t="n">
-        <v>13.8114061355591</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>13.8114061355591</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>13.8454236984253</v>
+        <v>13.8454256057739</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>13.8114061355591</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G834" t="n">
-        <v>13.743371963501</v>
+        <v>13.743369102478</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G837" t="n">
-        <v>13.6753339767456</v>
+        <v>13.6753349304199</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>20</v>
       </c>
       <c r="G841" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072969436646</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G842" t="n">
-        <v>13.2535076141357</v>
+        <v>13.2535066604614</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G843" t="n">
-        <v>13.335150718689</v>
+        <v>13.3351516723633</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G845" t="n">
-        <v>13.5664749145508</v>
+        <v>13.5664758682251</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>20</v>
       </c>
       <c r="G847" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072969436646</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>20</v>
       </c>
       <c r="G848" t="n">
-        <v>13.9920797348022</v>
+        <v>13.9920787811279</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G849" t="n">
-        <v>13.684250831604</v>
+        <v>13.6842517852783</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G850" t="n">
-        <v>13.4184045791626</v>
+        <v>13.418402671814</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G852" t="n">
-        <v>13.4603805541992</v>
+        <v>13.4603815078735</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G854" t="n">
-        <v>13.6702632904053</v>
+        <v>13.670262336731</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G856" t="n">
-        <v>13.7262296676636</v>
+        <v>13.7262287139893</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G857" t="n">
-        <v>13.8661489486694</v>
+        <v>13.8661518096924</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G858" t="n">
-        <v>13.950101852417</v>
+        <v>13.9501028060913</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G859" t="n">
-        <v>13.9221162796021</v>
+        <v>13.9221172332764</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G861" t="n">
-        <v>13.8661489486694</v>
+        <v>13.8661518096924</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G862" t="n">
-        <v>13.7961874008179</v>
+        <v>13.7961902618408</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G864" t="n">
-        <v>13.8521575927734</v>
+        <v>13.8521585464478</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>14.1320009231567</v>
+        <v>14.1319990158081</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G866" t="n">
-        <v>13.8801412582397</v>
+        <v>13.8801422119141</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>13.9221162796021</v>
+        <v>13.9221172332764</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G868" t="n">
-        <v>13.7262296676636</v>
+        <v>13.7262287139893</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G873" t="n">
-        <v>13.9361114501953</v>
+        <v>13.9361085891724</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G874" t="n">
-        <v>14.1320009231567</v>
+        <v>14.1319990158081</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G875" t="n">
-        <v>14.0620384216309</v>
+        <v>14.0620403289795</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G876" t="n">
-        <v>14.1320009231567</v>
+        <v>14.1319990158081</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>14.2719221115112</v>
+        <v>14.2719202041626</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>14.4118394851685</v>
+        <v>14.4118432998657</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G879" t="n">
-        <v>14.5517616271973</v>
+        <v>14.5517587661743</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G880" t="n">
-        <v>14.6217222213745</v>
+        <v>14.6217231750488</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G881" t="n">
-        <v>14.8316040039062</v>
+        <v>14.8316049575806</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G883" t="n">
-        <v>14.761643409729</v>
+        <v>14.7616424560547</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G885" t="n">
-        <v>14.7266635894775</v>
+        <v>14.7266607284546</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>14.8316040039062</v>
+        <v>14.8316049575806</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>21</v>
       </c>
       <c r="G889" t="n">
-        <v>14.6916837692261</v>
+        <v>14.6916828155518</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>21</v>
       </c>
       <c r="G890" t="n">
-        <v>14.6916837692261</v>
+        <v>14.6916828155518</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>14.6217222213745</v>
+        <v>14.6217231750488</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G892" t="n">
-        <v>15.0764656066895</v>
+        <v>15.0764636993408</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>21</v>
       </c>
       <c r="G893" t="n">
-        <v>14.6916837692261</v>
+        <v>14.6916828155518</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>21</v>
       </c>
       <c r="G894" t="n">
-        <v>14.6916837692261</v>
+        <v>14.6916828155518</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G895" t="n">
-        <v>14.6217222213745</v>
+        <v>14.6217231750488</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>21</v>
       </c>
       <c r="G896" t="n">
-        <v>14.6916837692261</v>
+        <v>14.6916828155518</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>21</v>
       </c>
       <c r="G897" t="n">
-        <v>14.6916837692261</v>
+        <v>14.6916828155518</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>21</v>
       </c>
       <c r="G898" t="n">
-        <v>14.6916837692261</v>
+        <v>14.6916828155518</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>21</v>
       </c>
       <c r="G900" t="n">
-        <v>14.6916837692261</v>
+        <v>14.6916828155518</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>20.75</v>
       </c>
       <c r="G902" t="n">
-        <v>14.5167837142944</v>
+        <v>14.5167818069458</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G905" t="n">
-        <v>14.2719221115112</v>
+        <v>14.2719202041626</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>14.4468202590942</v>
+        <v>14.4468212127686</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>14.4118394851685</v>
+        <v>14.4118432998657</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G909" t="n">
-        <v>14.4118394851685</v>
+        <v>14.4118432998657</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G910" t="n">
-        <v>14.0270586013794</v>
+        <v>14.0270595550537</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>14.1320009231567</v>
+        <v>14.1319990158081</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>14.201958656311</v>
+        <v>14.2019605636597</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G913" t="n">
-        <v>14.2719221115112</v>
+        <v>14.2719202041626</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G914" t="n">
-        <v>14.0970191955566</v>
+        <v>14.0970182418823</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>13.8521575927734</v>
+        <v>13.8521585464478</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G916" t="n">
-        <v>13.7262296676636</v>
+        <v>13.7262287139893</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G917" t="n">
-        <v>13.8241729736328</v>
+        <v>13.8241739273071</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G918" t="n">
-        <v>13.8661489486694</v>
+        <v>13.8661518096924</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G920" t="n">
-        <v>13.7262296676636</v>
+        <v>13.7262287139893</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G921" t="n">
-        <v>13.7961874008179</v>
+        <v>13.7961902618408</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G922" t="n">
-        <v>13.9780874252319</v>
+        <v>13.9780864715576</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G923" t="n">
-        <v>13.9081268310547</v>
+        <v>13.9081249237061</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G924" t="n">
-        <v>13.8661489486694</v>
+        <v>13.8661518096924</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G925" t="n">
-        <v>14.0270586013794</v>
+        <v>14.0270595550537</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G926" t="n">
-        <v>14.2719221115112</v>
+        <v>14.2719202041626</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G927" t="n">
-        <v>14.0620384216309</v>
+        <v>14.0620403289795</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G928" t="n">
-        <v>14.2719221115112</v>
+        <v>14.2719202041626</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G930" t="n">
-        <v>14.2369413375854</v>
+        <v>14.2369403839111</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G932" t="n">
-        <v>13.9780874252319</v>
+        <v>13.9780864715576</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G933" t="n">
-        <v>14.1320009231567</v>
+        <v>14.1319990158081</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>14.0270586013794</v>
+        <v>14.0270595550537</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>14.201958656311</v>
+        <v>14.2019605636597</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>20.5</v>
       </c>
       <c r="G936" t="n">
-        <v>14.3418827056885</v>
+        <v>14.3418798446655</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G937" t="n">
-        <v>14.4118394851685</v>
+        <v>14.4118432998657</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G939" t="n">
-        <v>14.5517616271973</v>
+        <v>14.5517587661743</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G941" t="n">
-        <v>14.4468202590942</v>
+        <v>14.4468212127686</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>14.6217222213745</v>
+        <v>14.6217231750488</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G943" t="n">
-        <v>14.5517616271973</v>
+        <v>14.5517587661743</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>21</v>
       </c>
       <c r="G946" t="n">
-        <v>14.6916837692261</v>
+        <v>14.6916828155518</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>21</v>
       </c>
       <c r="G949" t="n">
-        <v>14.6916837692261</v>
+        <v>14.6916828155518</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>21</v>
       </c>
       <c r="G950" t="n">
-        <v>14.6916837692261</v>
+        <v>14.6916828155518</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>21</v>
       </c>
       <c r="G951" t="n">
-        <v>14.6916837692261</v>
+        <v>14.6916828155518</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>21</v>
       </c>
       <c r="G952" t="n">
-        <v>14.6916837692261</v>
+        <v>14.6916828155518</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>21</v>
       </c>
       <c r="G953" t="n">
-        <v>14.6916837692261</v>
+        <v>14.6916828155518</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>21</v>
       </c>
       <c r="G954" t="n">
-        <v>14.6916837692261</v>
+        <v>14.6916828155518</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>14.6217222213745</v>
+        <v>14.6217231750488</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G956" t="n">
-        <v>14.7266635894775</v>
+        <v>14.7266607284546</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>22.5</v>
       </c>
       <c r="G958" t="n">
-        <v>15.7410898208618</v>
+        <v>15.7410879135132</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G964" t="n">
-        <v>16.1958312988281</v>
+        <v>16.1958293914795</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>16.1958312988281</v>
+        <v>16.1958293914795</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>15.950966835022</v>
+        <v>15.9509687423706</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G970" t="n">
-        <v>16.4057121276855</v>
+        <v>16.4057102203369</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>23.5</v>
       </c>
       <c r="G971" t="n">
-        <v>16.4406909942627</v>
+        <v>16.4406929016113</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G972" t="n">
-        <v>16.4057121276855</v>
+        <v>16.4057102203369</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>23.5</v>
       </c>
       <c r="G973" t="n">
-        <v>16.4406909942627</v>
+        <v>16.4406929016113</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>16.7555160522461</v>
+        <v>16.7555141448975</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>16.7555160522461</v>
+        <v>16.7555141448975</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>23.75</v>
       </c>
       <c r="G977" t="n">
-        <v>16.615592956543</v>
+        <v>16.6155910491943</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>24.5</v>
       </c>
       <c r="G979" t="n">
-        <v>17.1402969360352</v>
+        <v>17.1402950286865</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>17.070333480835</v>
+        <v>17.0703372955322</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>24.25</v>
       </c>
       <c r="G981" t="n">
-        <v>16.9653949737549</v>
+        <v>16.9653968811035</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G984" t="n">
-        <v>17.3851585388184</v>
+        <v>17.3851566314697</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G985" t="n">
-        <v>17.3851585388184</v>
+        <v>17.3851566314697</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G987" t="n">
-        <v>17.4201374053955</v>
+        <v>17.4201393127441</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G988" t="n">
-        <v>17.4201374053955</v>
+        <v>17.4201393127441</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G989" t="n">
-        <v>17.1752758026123</v>
+        <v>17.1752777099609</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G990" t="n">
-        <v>17.2802200317383</v>
+        <v>17.2802181243896</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G994" t="n">
-        <v>17.5950393676758</v>
+        <v>17.5950412750244</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>25.25</v>
       </c>
       <c r="G995" t="n">
-        <v>17.665002822876</v>
+        <v>17.6650009155273</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G996" t="n">
-        <v>17.7699413299561</v>
+        <v>17.7699375152588</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G997" t="n">
-        <v>17.8748817443848</v>
+        <v>17.8748798370361</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1000" t="n">
-        <v>17.2802200317383</v>
+        <v>17.2802181243896</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1003" t="n">
-        <v>17.5950393676758</v>
+        <v>17.5950412750244</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>25.25</v>
       </c>
       <c r="G1004" t="n">
-        <v>17.665002822876</v>
+        <v>17.6650009155273</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1005" t="n">
-        <v>17.5950393676758</v>
+        <v>17.5950412750244</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1007" t="n">
-        <v>17.4201374053955</v>
+        <v>17.4201393127441</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1008" t="n">
-        <v>17.3851585388184</v>
+        <v>17.3851566314697</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.3851585388184</v>
+        <v>17.3851566314697</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>17.2802200317383</v>
+        <v>17.2802181243896</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>24.5</v>
       </c>
       <c r="G1011" t="n">
-        <v>17.1402969360352</v>
+        <v>17.1402950286865</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1014" t="n">
-        <v>17.070333480835</v>
+        <v>17.0703372955322</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>24.5</v>
       </c>
       <c r="G1021" t="n">
-        <v>17.1402969360352</v>
+        <v>17.1402950286865</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>24.25</v>
       </c>
       <c r="G1022" t="n">
-        <v>16.9653949737549</v>
+        <v>16.9653968811035</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1025" t="n">
-        <v>17.2802200317383</v>
+        <v>17.2802181243896</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>17.2802200317383</v>
+        <v>17.2802181243896</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1027" t="n">
-        <v>17.3851585388184</v>
+        <v>17.3851566314697</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>25.25</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.665002822876</v>
+        <v>17.6650009155273</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1031" t="n">
-        <v>17.6999816894531</v>
+        <v>17.6999797821045</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1035" t="n">
-        <v>17.6300201416016</v>
+        <v>17.6300182342529</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>17.6999816894531</v>
+        <v>17.6999797821045</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>25.25</v>
       </c>
       <c r="G1038" t="n">
-        <v>17.665002822876</v>
+        <v>17.6650009155273</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1039" t="n">
-        <v>17.7699413299561</v>
+        <v>17.7699375152588</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>17.7699413299561</v>
+        <v>17.7699375152588</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G1042" t="n">
-        <v>17.8748817443848</v>
+        <v>17.8748798370361</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>25.25</v>
       </c>
       <c r="G1043" t="n">
-        <v>17.665002822876</v>
+        <v>17.6650009155273</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1044" t="n">
-        <v>17.6999816894531</v>
+        <v>17.6999797821045</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1045" t="n">
-        <v>17.9798221588135</v>
+        <v>17.9798202514648</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G1046" t="n">
-        <v>17.8748817443848</v>
+        <v>17.8748798370361</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>18.1197395324707</v>
+        <v>18.1197414398193</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>18.4695415496826</v>
+        <v>18.4695453643799</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>26.25</v>
       </c>
       <c r="G1050" t="n">
-        <v>18.3646030426025</v>
+        <v>18.3646049499512</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1051" t="n">
-        <v>18.4695415496826</v>
+        <v>18.4695453643799</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>26.5</v>
       </c>
       <c r="G1052" t="n">
-        <v>18.5395030975342</v>
+        <v>18.5395050048828</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>26.5</v>
       </c>
       <c r="G1054" t="n">
-        <v>18.5395030975342</v>
+        <v>18.5395050048828</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>26.5</v>
       </c>
       <c r="G1055" t="n">
-        <v>18.5395030975342</v>
+        <v>18.5395050048828</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>26.25</v>
       </c>
       <c r="G1057" t="n">
-        <v>18.3646030426025</v>
+        <v>18.3646049499512</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G1058" t="n">
-        <v>18.57448387146</v>
+        <v>18.5744857788086</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>26.5</v>
       </c>
       <c r="G1060" t="n">
-        <v>18.5395030975342</v>
+        <v>18.5395050048828</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1063" t="n">
-        <v>17.3851585388184</v>
+        <v>17.3851566314697</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1064" t="n">
-        <v>17.6300201416016</v>
+        <v>17.6300182342529</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>24.25</v>
       </c>
       <c r="G1067" t="n">
-        <v>16.9653949737549</v>
+        <v>16.9653968811035</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>23</v>
       </c>
       <c r="G1068" t="n">
-        <v>16.0908889770508</v>
+        <v>16.090892791748</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>15.8110513687134</v>
+        <v>15.8110494613647</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G1072" t="n">
-        <v>18.5045261383057</v>
+        <v>18.5045223236084</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1074" t="n">
-        <v>17.2802200317383</v>
+        <v>17.2802181243896</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1075" t="n">
-        <v>16.335750579834</v>
+        <v>16.3357543945312</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1076" t="n">
-        <v>16.6505756378174</v>
+        <v>16.6505737304688</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>17.3851585388184</v>
+        <v>17.3851566314697</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>25.5</v>
       </c>
       <c r="G1085" t="n">
-        <v>17.839900970459</v>
+        <v>17.8399028778076</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>18.4695415496826</v>
+        <v>18.4695453643799</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G1091" t="n">
-        <v>18.57448387146</v>
+        <v>18.5744857788086</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>18.4695415496826</v>
+        <v>18.4695453643799</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G1103" t="n">
-        <v>19.0617389678955</v>
+        <v>19.0617408752441</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G1107" t="n">
-        <v>19.0617389678955</v>
+        <v>19.0617408752441</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>19.1740894317627</v>
+        <v>19.1740856170654</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>25</v>
       </c>
       <c r="G1111" t="n">
-        <v>18.7246932983398</v>
+        <v>18.7246952056885</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1112" t="n">
-        <v>18.6123447418213</v>
+        <v>18.6123428344727</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>18.6123447418213</v>
+        <v>18.6123428344727</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1114" t="n">
-        <v>18.5748977661133</v>
+        <v>18.5748958587646</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G1115" t="n">
-        <v>19.0617389678955</v>
+        <v>19.0617408752441</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>19.2115364074707</v>
+        <v>19.2115345001221</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>19.3987808227539</v>
+        <v>19.3987846374512</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>25.75</v>
       </c>
       <c r="G1123" t="n">
-        <v>19.286434173584</v>
+        <v>19.2864360809326</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1124" t="n">
-        <v>20.3724689483643</v>
+        <v>20.372465133667</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1126" t="n">
-        <v>20.1477680206299</v>
+        <v>20.1477699279785</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>20.4848155975342</v>
+        <v>20.4848136901855</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>27</v>
       </c>
       <c r="G1128" t="n">
-        <v>20.2226696014404</v>
+        <v>20.2226676940918</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>19.9979705810547</v>
+        <v>19.9979724884033</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>20.2975673675537</v>
+        <v>20.2975692749023</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>20.9342079162598</v>
+        <v>20.9342098236084</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1134" t="n">
-        <v>21.1214561462402</v>
+        <v>21.1214542388916</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>27.75</v>
       </c>
       <c r="G1135" t="n">
-        <v>20.7844104766846</v>
+        <v>20.7844085693359</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1138" t="n">
-        <v>21.1963539123535</v>
+        <v>21.1963520050049</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1140" t="n">
-        <v>21.6831951141357</v>
+        <v>21.6831970214844</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>29.25</v>
       </c>
       <c r="G1143" t="n">
-        <v>21.9078903198242</v>
+        <v>21.9078922271729</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>22.6194305419922</v>
+        <v>22.6194324493408</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1150" t="n">
-        <v>23.0688209533691</v>
+        <v>23.0688228607178</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1151" t="n">
-        <v>23.4807662963867</v>
+        <v>23.4807643890381</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>31.75</v>
       </c>
       <c r="G1153" t="n">
-        <v>23.7803592681885</v>
+        <v>23.7803611755371</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>31.5</v>
       </c>
       <c r="G1154" t="n">
-        <v>23.5931148529053</v>
+        <v>23.5931129455566</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>23.8552627563477</v>
+        <v>23.855260848999</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1158" t="n">
-        <v>23.8178100585938</v>
+        <v>23.8178081512451</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1159" t="n">
-        <v>23.7054634094238</v>
+        <v>23.7054595947266</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G1160" t="n">
-        <v>23.256067276001</v>
+        <v>23.2560691833496</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1161" t="n">
-        <v>23.1062717437744</v>
+        <v>23.106273651123</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>29.25</v>
       </c>
       <c r="G1163" t="n">
-        <v>21.9078903198242</v>
+        <v>21.9078922271729</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>22.806676864624</v>
+        <v>22.8066787719727</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>22.806676864624</v>
+        <v>22.8066787719727</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>29.75</v>
       </c>
       <c r="G1170" t="n">
-        <v>22.2823867797852</v>
+        <v>22.2823829650879</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1171" t="n">
-        <v>22.9564743041992</v>
+        <v>22.9564723968506</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>30.5</v>
       </c>
       <c r="G1172" t="n">
-        <v>22.844123840332</v>
+        <v>22.8441276550293</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>30.5</v>
       </c>
       <c r="G1173" t="n">
-        <v>22.844123840332</v>
+        <v>22.8441276550293</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.9190235137939</v>
+        <v>22.9190254211426</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1176" t="n">
-        <v>22.9564743041992</v>
+        <v>22.9564723968506</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1177" t="n">
-        <v>22.9564743041992</v>
+        <v>22.9564723968506</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>30.5</v>
       </c>
       <c r="G1178" t="n">
-        <v>22.844123840332</v>
+        <v>22.8441276550293</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1179" t="n">
-        <v>22.5445327758789</v>
+        <v>22.5445308685303</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>30.5</v>
       </c>
       <c r="G1181" t="n">
-        <v>22.844123840332</v>
+        <v>22.8441276550293</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1183" t="n">
-        <v>23.1062717437744</v>
+        <v>23.106273651123</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>30.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>22.844123840332</v>
+        <v>22.8441276550293</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>30.0499992370605</v>
       </c>
       <c r="G1186" t="n">
-        <v>22.5070838928223</v>
+        <v>22.507080078125</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>30</v>
       </c>
       <c r="G1187" t="n">
-        <v>22.469633102417</v>
+        <v>22.4696311950684</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1189" t="n">
-        <v>22.13258934021</v>
+        <v>22.1325874328613</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>30</v>
       </c>
       <c r="G1190" t="n">
-        <v>22.469633102417</v>
+        <v>22.4696311950684</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1191" t="n">
-        <v>22.2449398040771</v>
+        <v>22.2449359893799</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1192" t="n">
-        <v>22.5445327758789</v>
+        <v>22.5445308685303</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>22.6194305419922</v>
+        <v>22.6194324493408</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>22.6194305419922</v>
+        <v>22.6194324493408</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1196" t="n">
-        <v>22.7317771911621</v>
+        <v>22.7317810058594</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1197" t="n">
-        <v>22.6194305419922</v>
+        <v>22.6194324493408</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1198" t="n">
-        <v>21.7580909729004</v>
+        <v>21.758092880249</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1199" t="n">
-        <v>20.9342079162598</v>
+        <v>20.9342098236084</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1203" t="n">
-        <v>21.4584980010986</v>
+        <v>21.4584999084473</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1204" t="n">
-        <v>20.9342079162598</v>
+        <v>20.9342098236084</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1209" t="n">
-        <v>22.3572864532471</v>
+        <v>22.3572845458984</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1210" t="n">
-        <v>22.0576877593994</v>
+        <v>22.057689666748</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1211" t="n">
-        <v>21.6831951141357</v>
+        <v>21.6831970214844</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1214" t="n">
-        <v>21.7580909729004</v>
+        <v>21.758092880249</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1218" t="n">
-        <v>21.3836002349854</v>
+        <v>21.383602142334</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1221" t="n">
-        <v>21.5708465576172</v>
+        <v>21.5708484649658</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1224" t="n">
-        <v>20.6720600128174</v>
+        <v>20.672061920166</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1228" t="n">
-        <v>20.7095108032227</v>
+        <v>20.7095127105713</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>27.75</v>
       </c>
       <c r="G1229" t="n">
-        <v>20.7844104766846</v>
+        <v>20.7844085693359</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>20.6720600128174</v>
+        <v>20.672061920166</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>21.1214561462402</v>
+        <v>21.1214542388916</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>21.1214561462402</v>
+        <v>21.1214542388916</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1234" t="n">
-        <v>20.8218574523926</v>
+        <v>20.8218612670898</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1235" t="n">
-        <v>20.9342079162598</v>
+        <v>20.9342098236084</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1239" t="n">
-        <v>20.7095108032227</v>
+        <v>20.7095127105713</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>27.75</v>
       </c>
       <c r="G1240" t="n">
-        <v>20.7844104766846</v>
+        <v>20.7844085693359</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>27.75</v>
       </c>
       <c r="G1242" t="n">
-        <v>20.7844104766846</v>
+        <v>20.7844085693359</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1244" t="n">
-        <v>20.8593082427979</v>
+        <v>20.8593101501465</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>21.4584980010986</v>
+        <v>21.4584999084473</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>21.3836002349854</v>
+        <v>21.383602142334</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>21.4584980010986</v>
+        <v>21.4584999084473</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1249" t="n">
-        <v>21.4584980010986</v>
+        <v>21.4584999084473</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1250" t="n">
-        <v>21.1963539123535</v>
+        <v>21.1963520050049</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1252" t="n">
-        <v>21.3836002349854</v>
+        <v>21.383602142334</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1257" t="n">
-        <v>21.1963539123535</v>
+        <v>21.1963520050049</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1258" t="n">
-        <v>21.1214561462402</v>
+        <v>21.1214542388916</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1259" t="n">
-        <v>21.4584980010986</v>
+        <v>21.4584999084473</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1261" t="n">
-        <v>21.7580909729004</v>
+        <v>21.758092880249</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>29.25</v>
       </c>
       <c r="G1262" t="n">
-        <v>21.9078903198242</v>
+        <v>21.9078922271729</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1263" t="n">
-        <v>21.7580909729004</v>
+        <v>21.758092880249</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>30</v>
       </c>
       <c r="G1266" t="n">
-        <v>22.469633102417</v>
+        <v>22.4696311950684</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>29.25</v>
       </c>
       <c r="G1268" t="n">
-        <v>21.9078903198242</v>
+        <v>21.9078922271729</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>21.7580909729004</v>
+        <v>21.758092880249</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1276" t="n">
-        <v>21.6082973480225</v>
+        <v>21.6082954406738</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>29.25</v>
       </c>
       <c r="G1278" t="n">
-        <v>21.9078903198242</v>
+        <v>21.9078922271729</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1279" t="n">
-        <v>21.7580909729004</v>
+        <v>21.758092880249</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>29.25</v>
       </c>
       <c r="G1282" t="n">
-        <v>21.9078903198242</v>
+        <v>21.9078922271729</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>29.25</v>
       </c>
       <c r="G1283" t="n">
-        <v>21.9078903198242</v>
+        <v>21.9078922271729</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1284" t="n">
-        <v>21.6082973480225</v>
+        <v>21.6082954406738</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>27.75</v>
       </c>
       <c r="G1287" t="n">
-        <v>20.7844104766846</v>
+        <v>20.7844085693359</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>27.25</v>
       </c>
       <c r="G1289" t="n">
-        <v>20.4099159240723</v>
+        <v>20.4099140167236</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1298" t="n">
-        <v>21.4584980010986</v>
+        <v>21.4584999084473</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1301" t="n">
-        <v>21.3836002349854</v>
+        <v>21.383602142334</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1302" t="n">
-        <v>21.1214561462402</v>
+        <v>21.1214542388916</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1303" t="n">
-        <v>20.8593082427979</v>
+        <v>20.8593101501465</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>27</v>
       </c>
       <c r="G1304" t="n">
-        <v>20.2226696014404</v>
+        <v>20.2226676940918</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.3724689483643</v>
+        <v>20.372465133667</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>27.25</v>
       </c>
       <c r="G1311" t="n">
-        <v>20.4099159240723</v>
+        <v>20.4099140167236</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>27.25</v>
       </c>
       <c r="G1313" t="n">
-        <v>20.4099159240723</v>
+        <v>20.4099140167236</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1316" t="n">
-        <v>21.6082973480225</v>
+        <v>21.6082954406738</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>29.75</v>
       </c>
       <c r="G1319" t="n">
-        <v>22.2823867797852</v>
+        <v>22.2823829650879</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1321" t="n">
-        <v>22.3572864532471</v>
+        <v>22.3572845458984</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>21.6082973480225</v>
+        <v>21.6082954406738</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1327" t="n">
-        <v>21.046558380127</v>
+        <v>21.0465564727783</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1330" t="n">
-        <v>21.7580909729004</v>
+        <v>21.758092880249</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1335" t="n">
-        <v>22.13258934021</v>
+        <v>22.1325874328613</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>29.25</v>
       </c>
       <c r="G1338" t="n">
-        <v>21.9078903198242</v>
+        <v>21.9078922271729</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1340" t="n">
-        <v>21.4584980010986</v>
+        <v>21.4584999084473</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1344" t="n">
-        <v>21.5708465576172</v>
+        <v>21.5708484649658</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1348" t="n">
-        <v>21.6082973480225</v>
+        <v>21.6082954406738</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1349" t="n">
-        <v>21.7580909729004</v>
+        <v>21.758092880249</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1360" t="n">
-        <v>21.9036731719971</v>
+        <v>21.9036750793457</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1361" t="n">
-        <v>22.171724319458</v>
+        <v>22.1717262268066</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1363" t="n">
-        <v>22.171724319458</v>
+        <v>22.1717262268066</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1365" t="n">
-        <v>22.1334285736084</v>
+        <v>22.133430480957</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1366" t="n">
-        <v>22.171724319458</v>
+        <v>22.1717262268066</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1367" t="n">
-        <v>22.3248958587646</v>
+        <v>22.3248977661133</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1368" t="n">
-        <v>22.171724319458</v>
+        <v>22.1717262268066</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1369" t="n">
-        <v>22.2483081817627</v>
+        <v>22.2483100891113</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1370" t="n">
-        <v>22.2866020202637</v>
+        <v>22.2866039276123</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1371" t="n">
-        <v>22.1334285736084</v>
+        <v>22.133430480957</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1373" t="n">
-        <v>22.6312427520752</v>
+        <v>22.6312408447266</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1374" t="n">
-        <v>23.0524673461914</v>
+        <v>23.0524654388428</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>30.25</v>
       </c>
       <c r="G1375" t="n">
-        <v>23.1673469543457</v>
+        <v>23.1673450469971</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1376" t="n">
-        <v>23.5119819641113</v>
+        <v>23.5119857788086</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>30.25</v>
       </c>
       <c r="G1379" t="n">
-        <v>23.1673469543457</v>
+        <v>23.1673450469971</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1383" t="n">
-        <v>23.5119819641113</v>
+        <v>23.5119857788086</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1385" t="n">
-        <v>23.9715023040771</v>
+        <v>23.9715003967285</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>23.6268615722656</v>
+        <v>23.6268634796143</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1387" t="n">
-        <v>23.8183288574219</v>
+        <v>23.8183269500732</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>30.5</v>
       </c>
       <c r="G1388" t="n">
-        <v>23.3588085174561</v>
+        <v>23.3588123321533</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>30.25</v>
       </c>
       <c r="G1390" t="n">
-        <v>23.1673469543457</v>
+        <v>23.1673450469971</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1391" t="n">
-        <v>23.0524673461914</v>
+        <v>23.0524654388428</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1393" t="n">
-        <v>23.5885696411133</v>
+        <v>23.5885715484619</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1395" t="n">
-        <v>23.5119819641113</v>
+        <v>23.5119857788086</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1400" t="n">
-        <v>23.473690032959</v>
+        <v>23.4736919403076</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1401" t="n">
-        <v>23.8183288574219</v>
+        <v>23.8183269500732</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1403" t="n">
-        <v>23.473690032959</v>
+        <v>23.4736919403076</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1405" t="n">
-        <v>23.8183288574219</v>
+        <v>23.8183269500732</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1406" t="n">
-        <v>23.7034511566162</v>
+        <v>23.7034492492676</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1408" t="n">
-        <v>23.473690032959</v>
+        <v>23.4736919403076</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>30.25</v>
       </c>
       <c r="G1410" t="n">
-        <v>23.1673469543457</v>
+        <v>23.1673450469971</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1412" t="n">
-        <v>23.6268615722656</v>
+        <v>23.6268634796143</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1413" t="n">
-        <v>23.5119819641113</v>
+        <v>23.5119857788086</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1415" t="n">
-        <v>23.5119819641113</v>
+        <v>23.5119857788086</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1420" t="n">
-        <v>24.2012615203857</v>
+        <v>24.2012596130371</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1421" t="n">
-        <v>24.2012615203857</v>
+        <v>24.2012596130371</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>32.25</v>
       </c>
       <c r="G1424" t="n">
-        <v>24.6990699768066</v>
+        <v>24.6990718841553</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1425" t="n">
-        <v>24.4310207366943</v>
+        <v>24.4310188293457</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1426" t="n">
-        <v>24.4310207366943</v>
+        <v>24.4310188293457</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G1428" t="n">
-        <v>24.0863819122314</v>
+        <v>24.0863800048828</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1430" t="n">
-        <v>23.9715023040771</v>
+        <v>23.9715003967285</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1434" t="n">
-        <v>23.9715023040771</v>
+        <v>23.9715003967285</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>23.6268615722656</v>
+        <v>23.6268634796143</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1438" t="n">
-        <v>23.7034511566162</v>
+        <v>23.7034492492676</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1439" t="n">
-        <v>23.7034511566162</v>
+        <v>23.7034492492676</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>23.5119819641113</v>
+        <v>23.5119857788086</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1442" t="n">
-        <v>24.4310207366943</v>
+        <v>24.4310188293457</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>32.5</v>
       </c>
       <c r="G1443" t="n">
-        <v>24.8905353546143</v>
+        <v>24.8905391693115</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>32.25</v>
       </c>
       <c r="G1444" t="n">
-        <v>24.6990699768066</v>
+        <v>24.6990718841553</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1445" t="n">
-        <v>24.4310207366943</v>
+        <v>24.4310188293457</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>31.5</v>
       </c>
       <c r="G1447" t="n">
-        <v>24.1246757507324</v>
+        <v>24.1246738433838</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>31.5</v>
       </c>
       <c r="G1449" t="n">
-        <v>24.1246757507324</v>
+        <v>24.1246738433838</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>31.5</v>
       </c>
       <c r="G1450" t="n">
-        <v>24.1246757507324</v>
+        <v>24.1246738433838</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>31.5</v>
       </c>
       <c r="G1451" t="n">
-        <v>24.1246757507324</v>
+        <v>24.1246738433838</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>23.5885696411133</v>
+        <v>23.5885715484619</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1456" t="n">
-        <v>23.6268615722656</v>
+        <v>23.6268634796143</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>30.5</v>
       </c>
       <c r="G1459" t="n">
-        <v>23.3588085174561</v>
+        <v>23.3588123321533</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1462" t="n">
-        <v>22.6312427520752</v>
+        <v>22.6312408447266</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1464" t="n">
-        <v>22.7461242675781</v>
+        <v>22.7461204528809</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1467" t="n">
-        <v>22.7461242675781</v>
+        <v>22.7461204528809</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1469" t="n">
-        <v>22.8992958068848</v>
+        <v>22.8992919921875</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>30.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>23.3588085174561</v>
+        <v>23.3588123321533</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1472" t="n">
-        <v>23.5885696411133</v>
+        <v>23.5885715484619</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1473" t="n">
-        <v>23.473690032959</v>
+        <v>23.4736919403076</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1474" t="n">
-        <v>23.7034511566162</v>
+        <v>23.7034492492676</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1477" t="n">
-        <v>23.8183288574219</v>
+        <v>23.8183269500732</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1480" t="n">
-        <v>23.5885696411133</v>
+        <v>23.5885715484619</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1484" t="n">
-        <v>23.7034511566162</v>
+        <v>23.7034492492676</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>32.25</v>
       </c>
       <c r="G1489" t="n">
-        <v>24.6990699768066</v>
+        <v>24.6990718841553</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1491" t="n">
-        <v>24.4310207366943</v>
+        <v>24.4310188293457</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1495" t="n">
-        <v>24.3544330596924</v>
+        <v>24.3544311523438</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1498" t="n">
-        <v>24.2012615203857</v>
+        <v>24.2012596130371</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1508" t="n">
-        <v>24.2778491973877</v>
+        <v>24.2778472900391</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1515" t="n">
-        <v>24.8139514923096</v>
+        <v>24.8139533996582</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>32.25</v>
       </c>
       <c r="G1516" t="n">
-        <v>24.6990699768066</v>
+        <v>24.6990718841553</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1518" t="n">
-        <v>24.2778491973877</v>
+        <v>24.2778472900391</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1519" t="n">
-        <v>24.4310207366943</v>
+        <v>24.4310188293457</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G1520" t="n">
-        <v>24.584192276001</v>
+        <v>24.5841903686523</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G1521" t="n">
-        <v>24.6224842071533</v>
+        <v>24.622486114502</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1523" t="n">
-        <v>24.8139514923096</v>
+        <v>24.8139533996582</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1524" t="n">
-        <v>24.8139514923096</v>
+        <v>24.8139533996582</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>32.5</v>
       </c>
       <c r="G1525" t="n">
-        <v>24.8905353546143</v>
+        <v>24.8905391693115</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>32.5</v>
       </c>
       <c r="G1526" t="n">
-        <v>24.8905353546143</v>
+        <v>24.8905391693115</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1528" t="n">
-        <v>24.9671211242676</v>
+        <v>24.9671230316162</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1530" t="n">
-        <v>25.1202964782715</v>
+        <v>25.1202945709229</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1531" t="n">
-        <v>24.9671211242676</v>
+        <v>24.9671230316162</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1532" t="n">
-        <v>24.8139514923096</v>
+        <v>24.8139533996582</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>32.5</v>
       </c>
       <c r="G1533" t="n">
-        <v>24.8905353546143</v>
+        <v>24.8905391693115</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>32.5</v>
       </c>
       <c r="G1534" t="n">
-        <v>24.8905353546143</v>
+        <v>24.8905391693115</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1535" t="n">
-        <v>25.1202964782715</v>
+        <v>25.1202945709229</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>32.5</v>
       </c>
       <c r="G1536" t="n">
-        <v>24.8905353546143</v>
+        <v>24.8905391693115</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G1539" t="n">
-        <v>24.7756538391113</v>
+        <v>24.77565574646</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>32.5</v>
       </c>
       <c r="G1540" t="n">
-        <v>24.8905353546143</v>
+        <v>24.8905391693115</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1541" t="n">
-        <v>24.4310207366943</v>
+        <v>24.4310188293457</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>30.5</v>
       </c>
       <c r="G1542" t="n">
-        <v>23.3588085174561</v>
+        <v>23.3588123321533</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1543" t="n">
-        <v>23.7034511566162</v>
+        <v>23.7034492492676</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1545" t="n">
-        <v>24.2778491973877</v>
+        <v>24.2778472900391</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1547" t="n">
-        <v>24.2778491973877</v>
+        <v>24.2778472900391</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G1548" t="n">
-        <v>24.7756538391113</v>
+        <v>24.77565574646</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1552" t="n">
-        <v>24.2012615203857</v>
+        <v>24.2012596130371</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1555" t="n">
-        <v>24.3544330596924</v>
+        <v>24.3544311523438</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>31.25</v>
       </c>
       <c r="G1557" t="n">
-        <v>23.9332084655762</v>
+        <v>23.9332065582275</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1558" t="n">
-        <v>24.2012615203857</v>
+        <v>24.2012596130371</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1559" t="n">
-        <v>24.2778491973877</v>
+        <v>24.2778472900391</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>31.25</v>
       </c>
       <c r="G1561" t="n">
-        <v>23.9332084655762</v>
+        <v>23.9332065582275</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>31.25</v>
       </c>
       <c r="G1562" t="n">
-        <v>23.9332084655762</v>
+        <v>23.9332065582275</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1563" t="n">
-        <v>23.8183288574219</v>
+        <v>23.8183269500732</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>30.5</v>
       </c>
       <c r="G1565" t="n">
-        <v>23.3588085174561</v>
+        <v>23.3588123321533</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1567" t="n">
-        <v>23.5119819641113</v>
+        <v>23.5119857788086</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1568" t="n">
-        <v>23.473690032959</v>
+        <v>23.4736919403076</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G1572" t="n">
-        <v>21.4824485778809</v>
+        <v>21.4824466705322</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1573" t="n">
-        <v>21.5207424163818</v>
+        <v>21.5207405090332</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1574" t="n">
-        <v>22.7461242675781</v>
+        <v>22.7461204528809</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>29</v>
       </c>
       <c r="G1575" t="n">
-        <v>22.2100162506104</v>
+        <v>22.210018157959</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1576" t="n">
-        <v>22.171724319458</v>
+        <v>22.1717262268066</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1578" t="n">
-        <v>22.0568447113037</v>
+        <v>22.0568466186523</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>29</v>
       </c>
       <c r="G1579" t="n">
-        <v>22.2100162506104</v>
+        <v>22.210018157959</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>22.4397754669189</v>
+        <v>22.4397773742676</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1586" t="n">
-        <v>22.5163612365723</v>
+        <v>22.5163593292236</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1587" t="n">
-        <v>22.5163612365723</v>
+        <v>22.5163593292236</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1588" t="n">
-        <v>22.6312427520752</v>
+        <v>22.6312408447266</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1590" t="n">
-        <v>22.1334285736084</v>
+        <v>22.133430480957</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>29</v>
       </c>
       <c r="G1591" t="n">
-        <v>22.2100162506104</v>
+        <v>22.210018157959</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G1592" t="n">
-        <v>22.2483081817627</v>
+        <v>22.2483100891113</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1595" t="n">
-        <v>22.171724319458</v>
+        <v>22.1717262268066</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1596" t="n">
-        <v>22.2866020202637</v>
+        <v>22.2866039276123</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1600" t="n">
-        <v>22.171724319458</v>
+        <v>22.1717262268066</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1601" t="n">
-        <v>22.171724319458</v>
+        <v>22.1717262268066</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1602" t="n">
-        <v>22.3248958587646</v>
+        <v>22.3248977661133</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>30.25</v>
       </c>
       <c r="G1605" t="n">
-        <v>23.1673469543457</v>
+        <v>23.1673450469971</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1607" t="n">
-        <v>22.8992958068848</v>
+        <v>22.8992919921875</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1625" t="n">
-        <v>23.4205551147461</v>
+        <v>23.4205570220947</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1638" t="n">
-        <v>22.7608222961426</v>
+        <v>22.7608203887939</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>26.75</v>
       </c>
       <c r="G1642" t="n">
-        <v>22.0598545074463</v>
+        <v>22.0598564147949</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>26.75</v>
       </c>
       <c r="G1646" t="n">
-        <v>22.0598545074463</v>
+        <v>22.0598564147949</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G1647" t="n">
-        <v>21.8949222564697</v>
+        <v>21.8949203491211</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G1648" t="n">
-        <v>21.8124542236328</v>
+        <v>21.8124561309814</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>26.75</v>
       </c>
       <c r="G1649" t="n">
-        <v>22.0598545074463</v>
+        <v>22.0598564147949</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>26.75</v>
       </c>
       <c r="G1655" t="n">
-        <v>22.0598545074463</v>
+        <v>22.0598564147949</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1659" t="n">
-        <v>22.7608222961426</v>
+        <v>22.7608203887939</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>26.8500003814697</v>
       </c>
       <c r="G1673" t="n">
-        <v>22.1423225402832</v>
+        <v>22.1423206329346</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1675" t="n">
-        <v>22.5134220123291</v>
+        <v>22.5134239196777</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1678" t="n">
-        <v>21.6062870025635</v>
+        <v>21.6062889099121</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>26.8500003814697</v>
       </c>
       <c r="G1681" t="n">
-        <v>22.1423225402832</v>
+        <v>22.1423206329346</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1683" t="n">
-        <v>22.5134220123291</v>
+        <v>22.5134239196777</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1689" t="n">
-        <v>21.6062870025635</v>
+        <v>21.6062889099121</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1696" t="n">
-        <v>22.8020572662354</v>
+        <v>22.8020553588867</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G1701" t="n">
-        <v>21.8949222564697</v>
+        <v>21.8949203491211</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1710" t="n">
-        <v>21.6062870025635</v>
+        <v>21.6062889099121</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>26</v>
       </c>
       <c r="G1712" t="n">
-        <v>21.4413547515869</v>
+        <v>21.4413528442383</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>23.25</v>
       </c>
       <c r="G1717" t="n">
-        <v>19.1735191345215</v>
+        <v>19.1735172271729</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>23.5</v>
       </c>
       <c r="G1718" t="n">
-        <v>19.3796863555908</v>
+        <v>19.3796844482422</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1722" t="n">
-        <v>19.8744869232178</v>
+        <v>19.8744850158691</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1727" t="n">
-        <v>19.8744869232178</v>
+        <v>19.8744850158691</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1730" t="n">
-        <v>20.781623840332</v>
+        <v>20.7816219329834</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1734" t="n">
-        <v>20.5342197418213</v>
+        <v>20.5342178344727</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>26</v>
       </c>
       <c r="G1738" t="n">
-        <v>21.4413547515869</v>
+        <v>21.4413528442383</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G1740" t="n">
-        <v>21.4001216888428</v>
+        <v>21.4001197814941</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1742" t="n">
-        <v>20.864086151123</v>
+        <v>20.8640880584717</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1746" t="n">
-        <v>20.781623840332</v>
+        <v>20.7816219329834</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>26</v>
       </c>
       <c r="G1749" t="n">
-        <v>21.4413547515869</v>
+        <v>21.4413528442383</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G1757" t="n">
-        <v>21.4001216888428</v>
+        <v>21.4001197814941</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G1759" t="n">
-        <v>21.8124542236328</v>
+        <v>21.8124561309814</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>25.75</v>
       </c>
       <c r="G1760" t="n">
-        <v>21.2351875305176</v>
+        <v>21.2351856231689</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G1761" t="n">
-        <v>21.1527194976807</v>
+        <v>21.1527214050293</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>25.5</v>
       </c>
       <c r="G1762" t="n">
-        <v>21.0290203094482</v>
+        <v>21.0290222167969</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>25.75</v>
       </c>
       <c r="G1763" t="n">
-        <v>21.2351875305176</v>
+        <v>21.2351856231689</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1776" t="n">
-        <v>20.864086151123</v>
+        <v>20.8640880584717</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1777" t="n">
-        <v>20.781623840332</v>
+        <v>20.7816219329834</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1778" t="n">
-        <v>20.781623840332</v>
+        <v>20.7816219329834</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>25.75</v>
       </c>
       <c r="G1779" t="n">
-        <v>21.2351875305176</v>
+        <v>21.2351856231689</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>25.75</v>
       </c>
       <c r="G1780" t="n">
-        <v>21.2351875305176</v>
+        <v>21.2351856231689</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>25.5</v>
       </c>
       <c r="G1781" t="n">
-        <v>21.0290203094482</v>
+        <v>21.0290222167969</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G1786" t="n">
-        <v>21.1527194976807</v>
+        <v>21.1527214050293</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1787" t="n">
-        <v>20.864086151123</v>
+        <v>20.8640880584717</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1788" t="n">
-        <v>20.864086151123</v>
+        <v>20.8640880584717</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1789" t="n">
-        <v>20.7403869628906</v>
+        <v>20.740385055542</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1790" t="n">
-        <v>20.5342197418213</v>
+        <v>20.5342178344727</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G1791" t="n">
-        <v>20.245584487915</v>
+        <v>20.2455863952637</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1792" t="n">
-        <v>20.1218872070312</v>
+        <v>20.1218852996826</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1805" t="n">
-        <v>20.1218872070312</v>
+        <v>20.1218852996826</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G1810" t="n">
-        <v>20.245584487915</v>
+        <v>20.2455863952637</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1812" t="n">
-        <v>19.420919418335</v>
+        <v>19.4209175109863</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1818" t="n">
-        <v>20.781623840332</v>
+        <v>20.7816219329834</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G1835" t="n">
-        <v>20.245584487915</v>
+        <v>20.2455863952637</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1842" t="n">
-        <v>20.7403869628906</v>
+        <v>20.740385055542</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1845" t="n">
-        <v>20.781623840332</v>
+        <v>20.7816219329834</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1846" t="n">
-        <v>20.864086151123</v>
+        <v>20.8640880584717</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G1848" t="n">
-        <v>21.1527194976807</v>
+        <v>21.1527214050293</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>25.5</v>
       </c>
       <c r="G1852" t="n">
-        <v>21.0290203094482</v>
+        <v>21.0290222167969</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G1861" t="n">
-        <v>21.1527194976807</v>
+        <v>21.1527214050293</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>26</v>
       </c>
       <c r="G1864" t="n">
-        <v>21.4413547515869</v>
+        <v>21.4413528442383</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>24.6000003814697</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>8756</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>24.7999992370605</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>24.7000007629395</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>24.6499996185303</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>24.6499996185303</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ITM.MI.xlsx
+++ b/data/ITM.MI.xlsx
@@ -456,7 +456,7 @@
         <v>21</v>
       </c>
       <c r="G3" t="n">
-        <v>13.5263547897339</v>
+        <v>13.5263538360596</v>
       </c>
       <c r="H3" t="n">
         <v>1396</v>
@@ -485,7 +485,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>13.4297370910645</v>
+        <v>13.4297351837158</v>
       </c>
       <c r="H4" t="n">
         <v>2916</v>
@@ -514,7 +514,7 @@
         <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>12.8822412490845</v>
+        <v>12.8822393417358</v>
       </c>
       <c r="H5" t="n">
         <v>17682</v>
@@ -572,7 +572,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G7" t="n">
-        <v>12.3669528961182</v>
+        <v>12.3669538497925</v>
       </c>
       <c r="H7" t="n">
         <v>14254</v>
@@ -601,7 +601,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G8" t="n">
-        <v>12.463568687439</v>
+        <v>12.4635677337646</v>
       </c>
       <c r="H8" t="n">
         <v>3936</v>
@@ -630,7 +630,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>12.1415138244629</v>
+        <v>12.1415128707886</v>
       </c>
       <c r="H9" t="n">
         <v>28796</v>
@@ -688,7 +688,7 @@
         <v>18.5</v>
       </c>
       <c r="G11" t="n">
-        <v>11.9160737991333</v>
+        <v>11.916072845459</v>
       </c>
       <c r="H11" t="n">
         <v>23968</v>
@@ -717,7 +717,7 @@
         <v>17.75</v>
       </c>
       <c r="G12" t="n">
-        <v>11.4329891204834</v>
+        <v>11.4329881668091</v>
       </c>
       <c r="H12" t="n">
         <v>13928</v>
@@ -746,7 +746,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G13" t="n">
-        <v>11.2912855148315</v>
+        <v>11.2912836074829</v>
       </c>
       <c r="H13" t="n">
         <v>4978</v>
@@ -833,7 +833,7 @@
         <v>16.7749996185303</v>
       </c>
       <c r="G16" t="n">
-        <v>10.8049793243408</v>
+        <v>10.8049783706665</v>
       </c>
       <c r="H16" t="n">
         <v>30614</v>
@@ -862,7 +862,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G17" t="n">
-        <v>10.7953195571899</v>
+        <v>10.7953176498413</v>
       </c>
       <c r="H17" t="n">
         <v>12646</v>
@@ -978,7 +978,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>11.1753454208374</v>
+        <v>11.1753435134888</v>
       </c>
       <c r="H21" t="n">
         <v>17744</v>
@@ -1007,7 +1007,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G22" t="n">
-        <v>11.2397556304932</v>
+        <v>11.2397546768188</v>
       </c>
       <c r="H22" t="n">
         <v>7706</v>
@@ -1036,7 +1036,7 @@
         <v>17.25</v>
       </c>
       <c r="G23" t="n">
-        <v>11.110933303833</v>
+        <v>11.1109323501587</v>
       </c>
       <c r="H23" t="n">
         <v>10312</v>
@@ -1065,7 +1065,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G24" t="n">
-        <v>10.9177007675171</v>
+        <v>10.9176988601685</v>
       </c>
       <c r="H24" t="n">
         <v>8206</v>
@@ -1094,7 +1094,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G25" t="n">
-        <v>10.8854942321777</v>
+        <v>10.8854932785034</v>
       </c>
       <c r="H25" t="n">
         <v>14658</v>
@@ -1210,7 +1210,7 @@
         <v>16.5</v>
       </c>
       <c r="G29" t="n">
-        <v>10.6278486251831</v>
+        <v>10.6278476715088</v>
       </c>
       <c r="H29" t="n">
         <v>20210</v>
@@ -1268,7 +1268,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G31" t="n">
-        <v>10.0159425735474</v>
+        <v>10.015941619873</v>
       </c>
       <c r="H31" t="n">
         <v>43836</v>
@@ -1297,7 +1297,7 @@
         <v>16.5</v>
       </c>
       <c r="G32" t="n">
-        <v>10.6278486251831</v>
+        <v>10.6278476715088</v>
       </c>
       <c r="H32" t="n">
         <v>11984</v>
@@ -1355,7 +1355,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>11.2655210494995</v>
+        <v>11.2655200958252</v>
       </c>
       <c r="H34" t="n">
         <v>9068</v>
@@ -1384,7 +1384,7 @@
         <v>17.5</v>
       </c>
       <c r="G35" t="n">
-        <v>11.2719621658325</v>
+        <v>11.2719612121582</v>
       </c>
       <c r="H35" t="n">
         <v>29628</v>
@@ -1413,7 +1413,7 @@
         <v>17.5</v>
       </c>
       <c r="G36" t="n">
-        <v>11.2719621658325</v>
+        <v>11.2719612121582</v>
       </c>
       <c r="H36" t="n">
         <v>17360</v>
@@ -1442,7 +1442,7 @@
         <v>18</v>
       </c>
       <c r="G37" t="n">
-        <v>11.59401512146</v>
+        <v>11.5940170288086</v>
       </c>
       <c r="H37" t="n">
         <v>8122</v>
@@ -1500,7 +1500,7 @@
         <v>17.5450000762939</v>
       </c>
       <c r="G39" t="n">
-        <v>11.3009471893311</v>
+        <v>11.3009452819824</v>
       </c>
       <c r="H39" t="n">
         <v>2866</v>
@@ -1558,7 +1558,7 @@
         <v>18.25</v>
       </c>
       <c r="G41" t="n">
-        <v>11.7550458908081</v>
+        <v>11.7550449371338</v>
       </c>
       <c r="H41" t="n">
         <v>8368</v>
@@ -1587,7 +1587,7 @@
         <v>18.4750003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>11.8999700546265</v>
+        <v>11.8999691009521</v>
       </c>
       <c r="H42" t="n">
         <v>10588</v>
@@ -1616,7 +1616,7 @@
         <v>19</v>
       </c>
       <c r="G43" t="n">
-        <v>12.2381296157837</v>
+        <v>12.2381277084351</v>
       </c>
       <c r="H43" t="n">
         <v>4550</v>
@@ -1645,7 +1645,7 @@
         <v>19.1650009155273</v>
       </c>
       <c r="G44" t="n">
-        <v>12.3444080352783</v>
+        <v>12.3444089889526</v>
       </c>
       <c r="H44" t="n">
         <v>3776</v>
@@ -1674,7 +1674,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G45" t="n">
-        <v>12.5279817581177</v>
+        <v>12.527982711792</v>
       </c>
       <c r="H45" t="n">
         <v>4546</v>
@@ -1703,7 +1703,7 @@
         <v>19.75</v>
       </c>
       <c r="G46" t="n">
-        <v>12.721212387085</v>
+        <v>12.7212133407593</v>
       </c>
       <c r="H46" t="n">
         <v>8052</v>
@@ -1732,7 +1732,7 @@
         <v>19.9950008392334</v>
       </c>
       <c r="G47" t="n">
-        <v>12.879020690918</v>
+        <v>12.8790216445923</v>
       </c>
       <c r="H47" t="n">
         <v>6056</v>
@@ -1761,7 +1761,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>12.5923900604248</v>
+        <v>12.5923919677734</v>
       </c>
       <c r="H48" t="n">
         <v>3476</v>
@@ -1790,7 +1790,7 @@
         <v>19.5</v>
       </c>
       <c r="G49" t="n">
-        <v>12.5601854324341</v>
+        <v>12.5601844787598</v>
       </c>
       <c r="H49" t="n">
         <v>2252</v>
@@ -1819,7 +1819,7 @@
         <v>19.75</v>
       </c>
       <c r="G50" t="n">
-        <v>12.721212387085</v>
+        <v>12.7212133407593</v>
       </c>
       <c r="H50" t="n">
         <v>4290</v>
@@ -1848,7 +1848,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G51" t="n">
-        <v>12.8307123184204</v>
+        <v>12.830714225769</v>
       </c>
       <c r="H51" t="n">
         <v>8720</v>
@@ -1877,7 +1877,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G52" t="n">
-        <v>12.8113889694214</v>
+        <v>12.8113880157471</v>
       </c>
       <c r="H52" t="n">
         <v>5124</v>
@@ -1906,7 +1906,7 @@
         <v>19.5049991607666</v>
       </c>
       <c r="G53" t="n">
-        <v>12.563404083252</v>
+        <v>12.5634059906006</v>
       </c>
       <c r="H53" t="n">
         <v>2036</v>
@@ -1935,7 +1935,7 @@
         <v>19.7350006103516</v>
       </c>
       <c r="G54" t="n">
-        <v>12.7115497589111</v>
+        <v>12.7115526199341</v>
       </c>
       <c r="H54" t="n">
         <v>856</v>
@@ -1964,7 +1964,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G55" t="n">
-        <v>12.3798351287842</v>
+        <v>12.3798332214355</v>
       </c>
       <c r="H55" t="n">
         <v>1246</v>
@@ -1993,7 +1993,7 @@
         <v>20</v>
       </c>
       <c r="G56" t="n">
-        <v>12.8822412490845</v>
+        <v>12.8822393417358</v>
       </c>
       <c r="H56" t="n">
         <v>7320</v>
@@ -2051,7 +2051,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>12.7856245040894</v>
+        <v>12.785626411438</v>
       </c>
       <c r="H58" t="n">
         <v>1224</v>
@@ -2080,7 +2080,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G59" t="n">
-        <v>12.3411884307861</v>
+        <v>12.3411865234375</v>
       </c>
       <c r="H59" t="n">
         <v>5714</v>
@@ -2109,7 +2109,7 @@
         <v>19.3950004577637</v>
       </c>
       <c r="G60" t="n">
-        <v>12.4925527572632</v>
+        <v>12.4925537109375</v>
       </c>
       <c r="H60" t="n">
         <v>2324</v>
@@ -2138,7 +2138,7 @@
         <v>19.2749996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>12.4152593612671</v>
+        <v>12.4152612686157</v>
       </c>
       <c r="H61" t="n">
         <v>1308</v>
@@ -2167,7 +2167,7 @@
         <v>19.7749996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>12.7373161315918</v>
+        <v>12.7373151779175</v>
       </c>
       <c r="H62" t="n">
         <v>1552</v>
@@ -2196,7 +2196,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G63" t="n">
-        <v>12.6696844100952</v>
+        <v>12.6696834564209</v>
       </c>
       <c r="H63" t="n">
         <v>3922</v>
@@ -2254,7 +2254,7 @@
         <v>19.5650005340576</v>
       </c>
       <c r="G65" t="n">
-        <v>12.6020526885986</v>
+        <v>12.6020545959473</v>
       </c>
       <c r="H65" t="n">
         <v>2648</v>
@@ -2283,7 +2283,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G66" t="n">
-        <v>12.0320129394531</v>
+        <v>12.0320138931274</v>
       </c>
       <c r="H66" t="n">
         <v>6576</v>
@@ -2312,7 +2312,7 @@
         <v>19.1350002288818</v>
       </c>
       <c r="G67" t="n">
-        <v>12.3250827789307</v>
+        <v>12.3250856399536</v>
       </c>
       <c r="H67" t="n">
         <v>4074</v>
@@ -2370,7 +2370,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G69" t="n">
-        <v>12.225245475769</v>
+        <v>12.2252473831177</v>
       </c>
       <c r="H69" t="n">
         <v>5524</v>
@@ -2428,7 +2428,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>12.1415138244629</v>
+        <v>12.1415128707886</v>
       </c>
       <c r="H71" t="n">
         <v>3504</v>
@@ -2457,7 +2457,7 @@
         <v>19.2950000762939</v>
       </c>
       <c r="G72" t="n">
-        <v>12.4281415939331</v>
+        <v>12.4281425476074</v>
       </c>
       <c r="H72" t="n">
         <v>9348</v>
@@ -2486,7 +2486,7 @@
         <v>19.4650001525879</v>
       </c>
       <c r="G73" t="n">
-        <v>12.5376415252686</v>
+        <v>12.5376396179199</v>
       </c>
       <c r="H73" t="n">
         <v>3934</v>
@@ -2660,7 +2660,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>12.0835418701172</v>
+        <v>12.0835409164429</v>
       </c>
       <c r="H79" t="n">
         <v>1966</v>
@@ -2718,7 +2718,7 @@
         <v>19.1749992370605</v>
       </c>
       <c r="G81" t="n">
-        <v>12.3508491516113</v>
+        <v>12.3508472442627</v>
       </c>
       <c r="H81" t="n">
         <v>2112</v>
@@ -2747,7 +2747,7 @@
         <v>19.1949996948242</v>
       </c>
       <c r="G82" t="n">
-        <v>12.363730430603</v>
+        <v>12.3637313842773</v>
       </c>
       <c r="H82" t="n">
         <v>668</v>
@@ -2776,7 +2776,7 @@
         <v>19.1149997711182</v>
       </c>
       <c r="G83" t="n">
-        <v>12.312201499939</v>
+        <v>12.3122024536133</v>
       </c>
       <c r="H83" t="n">
         <v>248</v>
@@ -2805,7 +2805,7 @@
         <v>19</v>
       </c>
       <c r="G84" t="n">
-        <v>12.2381296157837</v>
+        <v>12.2381277084351</v>
       </c>
       <c r="H84" t="n">
         <v>1040</v>
@@ -2834,7 +2834,7 @@
         <v>19.1149997711182</v>
       </c>
       <c r="G85" t="n">
-        <v>12.312201499939</v>
+        <v>12.3122024536133</v>
       </c>
       <c r="H85" t="n">
         <v>10484</v>
@@ -2863,7 +2863,7 @@
         <v>18.7250003814697</v>
       </c>
       <c r="G86" t="n">
-        <v>12.060998916626</v>
+        <v>12.0609979629517</v>
       </c>
       <c r="H86" t="n">
         <v>3980</v>
@@ -2892,7 +2892,7 @@
         <v>19.0900001525879</v>
       </c>
       <c r="G87" t="n">
-        <v>12.2961006164551</v>
+        <v>12.2960987091064</v>
       </c>
       <c r="H87" t="n">
         <v>2216</v>
@@ -2921,7 +2921,7 @@
         <v>19.0750007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>12.2864389419556</v>
+        <v>12.2864379882812</v>
       </c>
       <c r="H88" t="n">
         <v>1134</v>
@@ -2950,7 +2950,7 @@
         <v>19</v>
       </c>
       <c r="G89" t="n">
-        <v>12.2381296157837</v>
+        <v>12.2381277084351</v>
       </c>
       <c r="H89" t="n">
         <v>5438</v>
@@ -2979,7 +2979,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>12.30322265625</v>
+        <v>12.3032255172729</v>
       </c>
       <c r="H90" t="n">
         <v>14190</v>
@@ -3037,7 +3037,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>12.1730327606201</v>
+        <v>12.1730346679688</v>
       </c>
       <c r="H92" t="n">
         <v>1024</v>
@@ -3066,7 +3066,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>12.2706785202026</v>
+        <v>12.2706756591797</v>
       </c>
       <c r="H93" t="n">
         <v>20154</v>
@@ -3124,7 +3124,7 @@
         <v>18.4750003814697</v>
       </c>
       <c r="G95" t="n">
-        <v>12.0265655517578</v>
+        <v>12.0265626907349</v>
       </c>
       <c r="H95" t="n">
         <v>5774</v>
@@ -3182,7 +3182,7 @@
         <v>18.5</v>
       </c>
       <c r="G97" t="n">
-        <v>12.0428409576416</v>
+        <v>12.042839050293</v>
       </c>
       <c r="H97" t="n">
         <v>7122</v>
@@ -3211,7 +3211,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>11.8150014877319</v>
+        <v>11.8150024414062</v>
       </c>
       <c r="H98" t="n">
         <v>4082</v>
@@ -3240,7 +3240,7 @@
         <v>17.8349990844727</v>
       </c>
       <c r="G99" t="n">
-        <v>11.6099462509155</v>
+        <v>11.6099481582642</v>
       </c>
       <c r="H99" t="n">
         <v>1882</v>
@@ -3269,7 +3269,7 @@
         <v>18</v>
       </c>
       <c r="G100" t="n">
-        <v>11.7173557281494</v>
+        <v>11.717357635498</v>
       </c>
       <c r="H100" t="n">
         <v>3832</v>
@@ -3298,7 +3298,7 @@
         <v>18</v>
       </c>
       <c r="G101" t="n">
-        <v>11.7173557281494</v>
+        <v>11.717357635498</v>
       </c>
       <c r="H101" t="n">
         <v>4770</v>
@@ -3356,7 +3356,7 @@
         <v>18</v>
       </c>
       <c r="G103" t="n">
-        <v>11.7173557281494</v>
+        <v>11.717357635498</v>
       </c>
       <c r="H103" t="n">
         <v>24096</v>
@@ -3414,7 +3414,7 @@
         <v>17.8349990844727</v>
       </c>
       <c r="G105" t="n">
-        <v>11.6099462509155</v>
+        <v>11.6099481582642</v>
       </c>
       <c r="H105" t="n">
         <v>15744</v>
@@ -3472,7 +3472,7 @@
         <v>18</v>
       </c>
       <c r="G107" t="n">
-        <v>11.7173557281494</v>
+        <v>11.717357635498</v>
       </c>
       <c r="H107" t="n">
         <v>16344</v>
@@ -3501,7 +3501,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>11.6685361862183</v>
+        <v>11.6685342788696</v>
       </c>
       <c r="H108" t="n">
         <v>800</v>
@@ -3530,7 +3530,7 @@
         <v>17.9249992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>11.6685361862183</v>
+        <v>11.6685342788696</v>
       </c>
       <c r="H109" t="n">
         <v>11030</v>
@@ -3559,7 +3559,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G110" t="n">
-        <v>11.5285768508911</v>
+        <v>11.5285778045654</v>
       </c>
       <c r="H110" t="n">
         <v>3178</v>
@@ -3588,7 +3588,7 @@
         <v>18.5</v>
       </c>
       <c r="G111" t="n">
-        <v>12.0428409576416</v>
+        <v>12.042839050293</v>
       </c>
       <c r="H111" t="n">
         <v>6194</v>
@@ -3617,7 +3617,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G112" t="n">
-        <v>12.2641677856445</v>
+        <v>12.2641668319702</v>
       </c>
       <c r="H112" t="n">
         <v>6612</v>
@@ -3646,7 +3646,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G113" t="n">
-        <v>12.1795406341553</v>
+        <v>12.1795415878296</v>
       </c>
       <c r="H113" t="n">
         <v>1218</v>
@@ -3675,7 +3675,7 @@
         <v>18.2150001525879</v>
       </c>
       <c r="G114" t="n">
-        <v>11.8573150634766</v>
+        <v>11.8573141098022</v>
       </c>
       <c r="H114" t="n">
         <v>4928</v>
@@ -3704,7 +3704,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G115" t="n">
-        <v>11.2551736831665</v>
+        <v>11.2551727294922</v>
       </c>
       <c r="H115" t="n">
         <v>7678</v>
@@ -3733,7 +3733,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G116" t="n">
-        <v>11.3332891464233</v>
+        <v>11.3332872390747</v>
       </c>
       <c r="H116" t="n">
         <v>3278</v>
@@ -3762,7 +3762,7 @@
         <v>16.6149997711182</v>
       </c>
       <c r="G117" t="n">
-        <v>10.8157720565796</v>
+        <v>10.815770149231</v>
       </c>
       <c r="H117" t="n">
         <v>10432</v>
@@ -3820,7 +3820,7 @@
         <v>15.75</v>
       </c>
       <c r="G119" t="n">
-        <v>10.2526874542236</v>
+        <v>10.2526865005493</v>
       </c>
       <c r="H119" t="n">
         <v>17316</v>
@@ -3907,7 +3907,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G122" t="n">
-        <v>10.9752588272095</v>
+        <v>10.9752569198608</v>
       </c>
       <c r="H122" t="n">
         <v>20142</v>
@@ -3936,7 +3936,7 @@
         <v>17.0349998474121</v>
       </c>
       <c r="G123" t="n">
-        <v>11.0891771316528</v>
+        <v>11.0891761779785</v>
       </c>
       <c r="H123" t="n">
         <v>10366</v>
@@ -3965,7 +3965,7 @@
         <v>15.7650003433228</v>
       </c>
       <c r="G124" t="n">
-        <v>10.2624540328979</v>
+        <v>10.2624530792236</v>
       </c>
       <c r="H124" t="n">
         <v>17230</v>
@@ -4023,7 +4023,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>10.1875915527344</v>
+        <v>10.1875905990601</v>
       </c>
       <c r="H126" t="n">
         <v>9822</v>
@@ -4052,7 +4052,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G127" t="n">
-        <v>10.1875915527344</v>
+        <v>10.1875905990601</v>
       </c>
       <c r="H127" t="n">
         <v>10306</v>
@@ -4110,7 +4110,7 @@
         <v>17.5</v>
       </c>
       <c r="G129" t="n">
-        <v>11.3918752670288</v>
+        <v>11.3918743133545</v>
       </c>
       <c r="H129" t="n">
         <v>31784</v>
@@ -4139,7 +4139,7 @@
         <v>19.2450008392334</v>
       </c>
       <c r="G130" t="n">
-        <v>12.5278081893921</v>
+        <v>12.5278091430664</v>
       </c>
       <c r="H130" t="n">
         <v>189558</v>
@@ -4226,7 +4226,7 @@
         <v>19.5</v>
       </c>
       <c r="G133" t="n">
-        <v>12.6938037872314</v>
+        <v>12.6938047409058</v>
       </c>
       <c r="H133" t="n">
         <v>28906</v>
@@ -4255,7 +4255,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G134" t="n">
-        <v>12.9867372512817</v>
+        <v>12.9867391586304</v>
       </c>
       <c r="H134" t="n">
         <v>39342</v>
@@ -4284,7 +4284,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G135" t="n">
-        <v>12.9606971740723</v>
+        <v>12.9606981277466</v>
       </c>
       <c r="H135" t="n">
         <v>21036</v>
@@ -4400,7 +4400,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>12.7914476394653</v>
+        <v>12.7914485931396</v>
       </c>
       <c r="H139" t="n">
         <v>32444</v>
@@ -4429,7 +4429,7 @@
         <v>19.6749992370605</v>
       </c>
       <c r="G140" t="n">
-        <v>12.8077201843262</v>
+        <v>12.8077220916748</v>
       </c>
       <c r="H140" t="n">
         <v>63578</v>
@@ -4516,7 +4516,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G143" t="n">
-        <v>12.5440826416016</v>
+        <v>12.5440807342529</v>
       </c>
       <c r="H143" t="n">
         <v>56280</v>
@@ -4574,7 +4574,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G145" t="n">
-        <v>12.4594564437866</v>
+        <v>12.4594573974609</v>
       </c>
       <c r="H145" t="n">
         <v>33614</v>
@@ -4603,7 +4603,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G146" t="n">
-        <v>12.4920053482056</v>
+        <v>12.4920034408569</v>
       </c>
       <c r="H146" t="n">
         <v>41564</v>
@@ -4690,7 +4690,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G149" t="n">
-        <v>12.5766286849976</v>
+        <v>12.5766305923462</v>
       </c>
       <c r="H149" t="n">
         <v>47726</v>
@@ -4719,7 +4719,7 @@
         <v>19.2099990844727</v>
       </c>
       <c r="G150" t="n">
-        <v>12.5050230026245</v>
+        <v>12.5050239562988</v>
       </c>
       <c r="H150" t="n">
         <v>32882</v>
@@ -4748,7 +4748,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G151" t="n">
-        <v>12.3715763092041</v>
+        <v>12.3715772628784</v>
       </c>
       <c r="H151" t="n">
         <v>28882</v>
@@ -4777,7 +4777,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G152" t="n">
-        <v>12.6156883239746</v>
+        <v>12.6156873703003</v>
       </c>
       <c r="H152" t="n">
         <v>39370</v>
@@ -4806,7 +4806,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>12.6287069320679</v>
+        <v>12.6287078857422</v>
       </c>
       <c r="H153" t="n">
         <v>19286</v>
@@ -4835,7 +4835,7 @@
         <v>19.4850006103516</v>
       </c>
       <c r="G154" t="n">
-        <v>12.6840400695801</v>
+        <v>12.6840410232544</v>
       </c>
       <c r="H154" t="n">
         <v>113148</v>
@@ -4864,7 +4864,7 @@
         <v>19.3050003051758</v>
       </c>
       <c r="G155" t="n">
-        <v>12.5668668746948</v>
+        <v>12.5668659210205</v>
       </c>
       <c r="H155" t="n">
         <v>68354</v>
@@ -4922,7 +4922,7 @@
         <v>19.8250007629395</v>
       </c>
       <c r="G157" t="n">
-        <v>12.9053688049316</v>
+        <v>12.9053678512573</v>
       </c>
       <c r="H157" t="n">
         <v>81578</v>
@@ -4951,7 +4951,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G158" t="n">
-        <v>12.9867372512817</v>
+        <v>12.9867391586304</v>
       </c>
       <c r="H158" t="n">
         <v>247824</v>
@@ -4980,7 +4980,7 @@
         <v>20.0550003051758</v>
       </c>
       <c r="G159" t="n">
-        <v>13.0550899505615</v>
+        <v>13.0550880432129</v>
       </c>
       <c r="H159" t="n">
         <v>211488</v>
@@ -5154,7 +5154,7 @@
         <v>19.9750003814697</v>
       </c>
       <c r="G165" t="n">
-        <v>13.0030136108398</v>
+        <v>13.0030117034912</v>
       </c>
       <c r="H165" t="n">
         <v>154012</v>
@@ -5183,7 +5183,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G166" t="n">
-        <v>13.1885375976562</v>
+        <v>13.1885366439819</v>
       </c>
       <c r="H166" t="n">
         <v>58196</v>
@@ -5241,7 +5241,7 @@
         <v>21.0049991607666</v>
       </c>
       <c r="G168" t="n">
-        <v>13.6735038757324</v>
+        <v>13.6735029220581</v>
       </c>
       <c r="H168" t="n">
         <v>66210</v>
@@ -5270,7 +5270,7 @@
         <v>21.3700008392334</v>
       </c>
       <c r="G169" t="n">
-        <v>13.9111061096191</v>
+        <v>13.9111070632935</v>
       </c>
       <c r="H169" t="n">
         <v>64212</v>
@@ -5299,7 +5299,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G170" t="n">
-        <v>14.1975317001343</v>
+        <v>14.19753074646</v>
       </c>
       <c r="H170" t="n">
         <v>137152</v>
@@ -5328,7 +5328,7 @@
         <v>22</v>
       </c>
       <c r="G171" t="n">
-        <v>14.321213722229</v>
+        <v>14.3212156295776</v>
       </c>
       <c r="H171" t="n">
         <v>220546</v>
@@ -5415,7 +5415,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>14.4188594818115</v>
+        <v>14.4188604354858</v>
       </c>
       <c r="H174" t="n">
         <v>91208</v>
@@ -5473,7 +5473,7 @@
         <v>23.1550006866455</v>
       </c>
       <c r="G176" t="n">
-        <v>15.0730781555176</v>
+        <v>15.0730762481689</v>
       </c>
       <c r="H176" t="n">
         <v>87322</v>
@@ -5502,7 +5502,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>14.7117929458618</v>
+        <v>14.7117938995361</v>
       </c>
       <c r="H177" t="n">
         <v>33274</v>
@@ -5531,7 +5531,7 @@
         <v>22</v>
       </c>
       <c r="G178" t="n">
-        <v>14.321213722229</v>
+        <v>14.3212156295776</v>
       </c>
       <c r="H178" t="n">
         <v>41526</v>
@@ -5560,7 +5560,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G179" t="n">
-        <v>14.2691373825073</v>
+        <v>14.2691383361816</v>
       </c>
       <c r="H179" t="n">
         <v>42866</v>
@@ -5589,7 +5589,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G180" t="n">
-        <v>14.2691373825073</v>
+        <v>14.2691383361816</v>
       </c>
       <c r="H180" t="n">
         <v>29042</v>
@@ -5647,7 +5647,7 @@
         <v>22</v>
       </c>
       <c r="G182" t="n">
-        <v>14.321213722229</v>
+        <v>14.3212156295776</v>
       </c>
       <c r="H182" t="n">
         <v>13224</v>
@@ -5676,7 +5676,7 @@
         <v>21.8349990844727</v>
       </c>
       <c r="G183" t="n">
-        <v>14.2138061523438</v>
+        <v>14.2138042449951</v>
       </c>
       <c r="H183" t="n">
         <v>22588</v>
@@ -5705,7 +5705,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>14.3863105773926</v>
+        <v>14.3863115310669</v>
       </c>
       <c r="H184" t="n">
         <v>12058</v>
@@ -5734,7 +5734,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G185" t="n">
-        <v>14.1910209655762</v>
+        <v>14.1910228729248</v>
       </c>
       <c r="H185" t="n">
         <v>50322</v>
@@ -5763,7 +5763,7 @@
         <v>21.7549991607666</v>
       </c>
       <c r="G186" t="n">
-        <v>14.1617298126221</v>
+        <v>14.1617269515991</v>
       </c>
       <c r="H186" t="n">
         <v>6260</v>
@@ -5850,7 +5850,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G189" t="n">
-        <v>14.2691373825073</v>
+        <v>14.2691383361816</v>
       </c>
       <c r="H189" t="n">
         <v>17864</v>
@@ -5879,7 +5879,7 @@
         <v>22.1350002288818</v>
       </c>
       <c r="G190" t="n">
-        <v>14.4090929031372</v>
+        <v>14.4090967178345</v>
       </c>
       <c r="H190" t="n">
         <v>25086</v>
@@ -5908,7 +5908,7 @@
         <v>22</v>
       </c>
       <c r="G191" t="n">
-        <v>14.321213722229</v>
+        <v>14.3212156295776</v>
       </c>
       <c r="H191" t="n">
         <v>36948</v>
@@ -5937,7 +5937,7 @@
         <v>22.0249996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>14.3374872207642</v>
+        <v>14.3374891281128</v>
       </c>
       <c r="H192" t="n">
         <v>22350</v>
@@ -5966,7 +5966,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G193" t="n">
-        <v>14.6271705627441</v>
+        <v>14.6271657943726</v>
       </c>
       <c r="H193" t="n">
         <v>46744</v>
@@ -6024,7 +6024,7 @@
         <v>21.9249992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>14.2723922729492</v>
+        <v>14.2723932266235</v>
       </c>
       <c r="H195" t="n">
         <v>13614</v>
@@ -6053,7 +6053,7 @@
         <v>22.1700000762939</v>
       </c>
       <c r="G196" t="n">
-        <v>14.4318780899048</v>
+        <v>14.4318771362305</v>
       </c>
       <c r="H196" t="n">
         <v>18412</v>
@@ -6082,7 +6082,7 @@
         <v>22.0450000762939</v>
       </c>
       <c r="G197" t="n">
-        <v>14.3505077362061</v>
+        <v>14.3505096435547</v>
       </c>
       <c r="H197" t="n">
         <v>21466</v>
@@ -6111,7 +6111,7 @@
         <v>22.0650005340576</v>
       </c>
       <c r="G198" t="n">
-        <v>14.3635272979736</v>
+        <v>14.3635282516479</v>
       </c>
       <c r="H198" t="n">
         <v>8748</v>
@@ -6169,7 +6169,7 @@
         <v>21.7849998474121</v>
       </c>
       <c r="G200" t="n">
-        <v>14.1812582015991</v>
+        <v>14.1812572479248</v>
       </c>
       <c r="H200" t="n">
         <v>24498</v>
@@ -6198,7 +6198,7 @@
         <v>21.7649993896484</v>
       </c>
       <c r="G201" t="n">
-        <v>14.1682386398315</v>
+        <v>14.1682405471802</v>
       </c>
       <c r="H201" t="n">
         <v>18992</v>
@@ -6256,7 +6256,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G203" t="n">
-        <v>13.8980875015259</v>
+        <v>13.8980894088745</v>
       </c>
       <c r="H203" t="n">
         <v>49890</v>
@@ -6314,7 +6314,7 @@
         <v>22.3850002288818</v>
       </c>
       <c r="G205" t="n">
-        <v>14.571834564209</v>
+        <v>14.5718364715576</v>
       </c>
       <c r="H205" t="n">
         <v>25584</v>
@@ -6372,7 +6372,7 @@
         <v>22.1049995422363</v>
       </c>
       <c r="G207" t="n">
-        <v>14.3895645141602</v>
+        <v>14.3895664215088</v>
       </c>
       <c r="H207" t="n">
         <v>20240</v>
@@ -6401,7 +6401,7 @@
         <v>22.3050003051758</v>
       </c>
       <c r="G208" t="n">
-        <v>14.5197591781616</v>
+        <v>14.519757270813</v>
       </c>
       <c r="H208" t="n">
         <v>10540</v>
@@ -6430,7 +6430,7 @@
         <v>22.4950008392334</v>
       </c>
       <c r="G209" t="n">
-        <v>14.6434421539307</v>
+        <v>14.643440246582</v>
       </c>
       <c r="H209" t="n">
         <v>27014</v>
@@ -6459,7 +6459,7 @@
         <v>22.0450000762939</v>
       </c>
       <c r="G210" t="n">
-        <v>14.3505077362061</v>
+        <v>14.3505096435547</v>
       </c>
       <c r="H210" t="n">
         <v>6092</v>
@@ -6488,7 +6488,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>14.2235689163208</v>
+        <v>14.2235717773438</v>
       </c>
       <c r="H211" t="n">
         <v>8700</v>
@@ -6517,7 +6517,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G212" t="n">
-        <v>14.1910209655762</v>
+        <v>14.1910228729248</v>
       </c>
       <c r="H212" t="n">
         <v>13912</v>
@@ -6546,7 +6546,7 @@
         <v>21.6849994659424</v>
       </c>
       <c r="G213" t="n">
-        <v>14.1161584854126</v>
+        <v>14.1161613464355</v>
       </c>
       <c r="H213" t="n">
         <v>8712</v>
@@ -6575,7 +6575,7 @@
         <v>21.6049995422363</v>
       </c>
       <c r="G214" t="n">
-        <v>14.0640850067139</v>
+        <v>14.0640840530396</v>
       </c>
       <c r="H214" t="n">
         <v>11304</v>
@@ -6604,7 +6604,7 @@
         <v>21.25</v>
       </c>
       <c r="G215" t="n">
-        <v>13.8329916000366</v>
+        <v>13.8329906463623</v>
       </c>
       <c r="H215" t="n">
         <v>5380</v>
@@ -6633,7 +6633,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G216" t="n">
-        <v>13.624683380127</v>
+        <v>13.6246814727783</v>
       </c>
       <c r="H216" t="n">
         <v>19648</v>
@@ -6691,7 +6691,7 @@
         <v>20.7549991607666</v>
       </c>
       <c r="G218" t="n">
-        <v>13.510763168335</v>
+        <v>13.5107622146606</v>
       </c>
       <c r="H218" t="n">
         <v>18326</v>
@@ -6749,7 +6749,7 @@
         <v>20.75</v>
       </c>
       <c r="G220" t="n">
-        <v>13.5075101852417</v>
+        <v>13.5075082778931</v>
       </c>
       <c r="H220" t="n">
         <v>5834</v>
@@ -6778,7 +6778,7 @@
         <v>20.9050006866455</v>
       </c>
       <c r="G221" t="n">
-        <v>13.6084108352661</v>
+        <v>13.6084098815918</v>
       </c>
       <c r="H221" t="n">
         <v>13536</v>
@@ -6807,7 +6807,7 @@
         <v>20.9050006866455</v>
       </c>
       <c r="G222" t="n">
-        <v>13.6084108352661</v>
+        <v>13.6084098815918</v>
       </c>
       <c r="H222" t="n">
         <v>6744</v>
@@ -6836,7 +6836,7 @@
         <v>20.9750003814697</v>
       </c>
       <c r="G223" t="n">
-        <v>13.6539754867554</v>
+        <v>13.653977394104</v>
       </c>
       <c r="H223" t="n">
         <v>7836</v>
@@ -6865,7 +6865,7 @@
         <v>21.2150001525879</v>
       </c>
       <c r="G224" t="n">
-        <v>13.810206413269</v>
+        <v>13.8102083206177</v>
       </c>
       <c r="H224" t="n">
         <v>2630</v>
@@ -6894,7 +6894,7 @@
         <v>21</v>
       </c>
       <c r="G225" t="n">
-        <v>13.6702527999878</v>
+        <v>13.6702499389648</v>
       </c>
       <c r="H225" t="n">
         <v>5534</v>
@@ -6952,7 +6952,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G227" t="n">
-        <v>13.891580581665</v>
+        <v>13.8915777206421</v>
       </c>
       <c r="H227" t="n">
         <v>7440</v>
@@ -6981,7 +6981,7 @@
         <v>21.2450008392334</v>
       </c>
       <c r="G228" t="n">
-        <v>13.829737663269</v>
+        <v>13.8297367095947</v>
       </c>
       <c r="H228" t="n">
         <v>7056</v>
@@ -7010,7 +7010,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>13.7678956985474</v>
+        <v>13.767894744873</v>
       </c>
       <c r="H229" t="n">
         <v>3674</v>
@@ -7039,7 +7039,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>13.7027988433838</v>
+        <v>13.7028007507324</v>
       </c>
       <c r="H230" t="n">
         <v>16826</v>
@@ -7068,7 +7068,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G231" t="n">
-        <v>13.891580581665</v>
+        <v>13.8915777206421</v>
       </c>
       <c r="H231" t="n">
         <v>9990</v>
@@ -7126,7 +7126,7 @@
         <v>21.0650005340576</v>
       </c>
       <c r="G233" t="n">
-        <v>13.7125635147095</v>
+        <v>13.7125644683838</v>
       </c>
       <c r="H233" t="n">
         <v>16098</v>
@@ -7155,7 +7155,7 @@
         <v>20.9099998474121</v>
       </c>
       <c r="G234" t="n">
-        <v>13.6116666793823</v>
+        <v>13.6116638183594</v>
       </c>
       <c r="H234" t="n">
         <v>68376</v>
@@ -7184,7 +7184,7 @@
         <v>20.7549991607666</v>
       </c>
       <c r="G235" t="n">
-        <v>13.510763168335</v>
+        <v>13.5107622146606</v>
       </c>
       <c r="H235" t="n">
         <v>41964</v>
@@ -7213,7 +7213,7 @@
         <v>21</v>
       </c>
       <c r="G236" t="n">
-        <v>13.6702527999878</v>
+        <v>13.6702499389648</v>
       </c>
       <c r="H236" t="n">
         <v>35850</v>
@@ -7242,7 +7242,7 @@
         <v>21</v>
       </c>
       <c r="G237" t="n">
-        <v>13.6702527999878</v>
+        <v>13.6702499389648</v>
       </c>
       <c r="H237" t="n">
         <v>84360</v>
@@ -7271,7 +7271,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G238" t="n">
-        <v>13.5726051330566</v>
+        <v>13.572606086731</v>
       </c>
       <c r="H238" t="n">
         <v>66252</v>
@@ -7300,7 +7300,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G239" t="n">
-        <v>13.5856246948242</v>
+        <v>13.5856256484985</v>
       </c>
       <c r="H239" t="n">
         <v>9438</v>
@@ -7329,7 +7329,7 @@
         <v>20.9099998474121</v>
       </c>
       <c r="G240" t="n">
-        <v>13.6116666793823</v>
+        <v>13.6116638183594</v>
       </c>
       <c r="H240" t="n">
         <v>18714</v>
@@ -7416,7 +7416,7 @@
         <v>21.0949993133545</v>
       </c>
       <c r="G243" t="n">
-        <v>13.7320890426636</v>
+        <v>13.7320919036865</v>
       </c>
       <c r="H243" t="n">
         <v>10122</v>
@@ -7445,7 +7445,7 @@
         <v>20.7549991607666</v>
       </c>
       <c r="G244" t="n">
-        <v>13.510763168335</v>
+        <v>13.5107622146606</v>
       </c>
       <c r="H244" t="n">
         <v>12350</v>
@@ -7474,7 +7474,7 @@
         <v>20.9150009155273</v>
       </c>
       <c r="G245" t="n">
-        <v>13.6149168014526</v>
+        <v>13.614917755127</v>
       </c>
       <c r="H245" t="n">
         <v>38432</v>
@@ -7503,7 +7503,7 @@
         <v>20.8050003051758</v>
       </c>
       <c r="G246" t="n">
-        <v>13.5433101654053</v>
+        <v>13.5433120727539</v>
       </c>
       <c r="H246" t="n">
         <v>16216</v>
@@ -7532,7 +7532,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G247" t="n">
-        <v>13.540057182312</v>
+        <v>13.5400581359863</v>
       </c>
       <c r="H247" t="n">
         <v>127586</v>
@@ -7561,7 +7561,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>13.7353467941284</v>
+        <v>13.7353477478027</v>
       </c>
       <c r="H248" t="n">
         <v>25352</v>
@@ -7590,7 +7590,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>13.7027988433838</v>
+        <v>13.7028007507324</v>
       </c>
       <c r="H249" t="n">
         <v>22656</v>
@@ -7619,7 +7619,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G250" t="n">
-        <v>13.6311912536621</v>
+        <v>13.6311950683594</v>
       </c>
       <c r="H250" t="n">
         <v>18460</v>
@@ -7648,7 +7648,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>13.7353467941284</v>
+        <v>13.7353477478027</v>
       </c>
       <c r="H251" t="n">
         <v>74574</v>
@@ -7677,7 +7677,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>13.9306354522705</v>
+        <v>13.9306364059448</v>
       </c>
       <c r="H252" t="n">
         <v>64676</v>
@@ -7735,7 +7735,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G254" t="n">
-        <v>14.1975317001343</v>
+        <v>14.19753074646</v>
       </c>
       <c r="H254" t="n">
         <v>25026</v>
@@ -7764,7 +7764,7 @@
         <v>21.8050003051758</v>
       </c>
       <c r="G255" t="n">
-        <v>14.1942758560181</v>
+        <v>14.1942777633667</v>
       </c>
       <c r="H255" t="n">
         <v>20198</v>
@@ -7793,7 +7793,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G256" t="n">
-        <v>14.2561178207397</v>
+        <v>14.2561197280884</v>
       </c>
       <c r="H256" t="n">
         <v>18434</v>
@@ -7851,7 +7851,7 @@
         <v>22.2950000762939</v>
       </c>
       <c r="G258" t="n">
-        <v>14.5132484436035</v>
+        <v>14.5132503509521</v>
       </c>
       <c r="H258" t="n">
         <v>10234</v>
@@ -7880,7 +7880,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>14.6141500473022</v>
+        <v>14.6141510009766</v>
       </c>
       <c r="H259" t="n">
         <v>45754</v>
@@ -7909,7 +7909,7 @@
         <v>22.3449993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>14.5457983016968</v>
+        <v>14.5457963943481</v>
       </c>
       <c r="H260" t="n">
         <v>32816</v>
@@ -7938,7 +7938,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>14.5816011428833</v>
+        <v>14.5815992355347</v>
       </c>
       <c r="H261" t="n">
         <v>20284</v>
@@ -7967,7 +7967,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>14.5816011428833</v>
+        <v>14.5815992355347</v>
       </c>
       <c r="H262" t="n">
         <v>5190</v>
@@ -7996,7 +7996,7 @@
         <v>22.6149997711182</v>
       </c>
       <c r="G263" t="n">
-        <v>14.7215557098389</v>
+        <v>14.7215585708618</v>
       </c>
       <c r="H263" t="n">
         <v>50738</v>
@@ -8025,7 +8025,7 @@
         <v>22.875</v>
       </c>
       <c r="G264" t="n">
-        <v>14.8908061981201</v>
+        <v>14.8908081054688</v>
       </c>
       <c r="H264" t="n">
         <v>57140</v>
@@ -8083,7 +8083,7 @@
         <v>22.75</v>
       </c>
       <c r="G266" t="n">
-        <v>14.80943775177</v>
+        <v>14.8094367980957</v>
       </c>
       <c r="H266" t="n">
         <v>24354</v>
@@ -8112,7 +8112,7 @@
         <v>22.8950004577637</v>
       </c>
       <c r="G267" t="n">
-        <v>14.9038276672363</v>
+        <v>14.903826713562</v>
       </c>
       <c r="H267" t="n">
         <v>22992</v>
@@ -8141,7 +8141,7 @@
         <v>22.1700000762939</v>
       </c>
       <c r="G268" t="n">
-        <v>14.4318780899048</v>
+        <v>14.4318771362305</v>
       </c>
       <c r="H268" t="n">
         <v>41962</v>
@@ -8170,7 +8170,7 @@
         <v>22.3850002288818</v>
       </c>
       <c r="G269" t="n">
-        <v>14.571834564209</v>
+        <v>14.5718364715576</v>
       </c>
       <c r="H269" t="n">
         <v>32808</v>
@@ -8199,7 +8199,7 @@
         <v>22.4249992370605</v>
       </c>
       <c r="G270" t="n">
-        <v>14.5978727340698</v>
+        <v>14.5978775024414</v>
       </c>
       <c r="H270" t="n">
         <v>20018</v>
@@ -8228,7 +8228,7 @@
         <v>22.3449993133545</v>
       </c>
       <c r="G271" t="n">
-        <v>14.5457983016968</v>
+        <v>14.5457963943481</v>
       </c>
       <c r="H271" t="n">
         <v>22194</v>
@@ -8257,7 +8257,7 @@
         <v>22.4950008392334</v>
       </c>
       <c r="G272" t="n">
-        <v>14.6434421539307</v>
+        <v>14.643440246582</v>
       </c>
       <c r="H272" t="n">
         <v>31032</v>
@@ -8286,7 +8286,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G273" t="n">
-        <v>14.5295209884644</v>
+        <v>14.5295219421387</v>
       </c>
       <c r="H273" t="n">
         <v>16324</v>
@@ -8344,7 +8344,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G275" t="n">
-        <v>14.7378330230713</v>
+        <v>14.737829208374</v>
       </c>
       <c r="H275" t="n">
         <v>35890</v>
@@ -8373,7 +8373,7 @@
         <v>22.6350002288818</v>
       </c>
       <c r="G276" t="n">
-        <v>14.7345771789551</v>
+        <v>14.7345743179321</v>
       </c>
       <c r="H276" t="n">
         <v>24202</v>
@@ -8402,7 +8402,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G277" t="n">
-        <v>14.8354778289795</v>
+        <v>14.8354787826538</v>
       </c>
       <c r="H277" t="n">
         <v>9504</v>
@@ -8460,7 +8460,7 @@
         <v>22.9650001525879</v>
       </c>
       <c r="G279" t="n">
-        <v>14.9493970870972</v>
+        <v>14.9493951797485</v>
       </c>
       <c r="H279" t="n">
         <v>16440</v>
@@ -8489,7 +8489,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G280" t="n">
-        <v>15.0828428268433</v>
+        <v>15.0828409194946</v>
       </c>
       <c r="H280" t="n">
         <v>10836</v>
@@ -8518,7 +8518,7 @@
         <v>23.125</v>
       </c>
       <c r="G281" t="n">
-        <v>15.0535497665405</v>
+        <v>15.0535488128662</v>
       </c>
       <c r="H281" t="n">
         <v>13704</v>
@@ -8547,7 +8547,7 @@
         <v>23.25</v>
       </c>
       <c r="G282" t="n">
-        <v>15.1349172592163</v>
+        <v>15.1349191665649</v>
       </c>
       <c r="H282" t="n">
         <v>9462</v>
@@ -8576,7 +8576,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>15.0698251724243</v>
+        <v>15.0698213577271</v>
       </c>
       <c r="H283" t="n">
         <v>7688</v>
@@ -8605,7 +8605,7 @@
         <v>23.1350002288818</v>
       </c>
       <c r="G284" t="n">
-        <v>15.0600566864014</v>
+        <v>15.0600576400757</v>
       </c>
       <c r="H284" t="n">
         <v>4340</v>
@@ -8634,7 +8634,7 @@
         <v>23.25</v>
       </c>
       <c r="G285" t="n">
-        <v>15.1349172592163</v>
+        <v>15.1349191665649</v>
       </c>
       <c r="H285" t="n">
         <v>16248</v>
@@ -8692,7 +8692,7 @@
         <v>23.0049991607666</v>
       </c>
       <c r="G287" t="n">
-        <v>14.9754343032837</v>
+        <v>14.9754323959351</v>
       </c>
       <c r="H287" t="n">
         <v>4200</v>
@@ -8721,7 +8721,7 @@
         <v>22.9650001525879</v>
       </c>
       <c r="G288" t="n">
-        <v>14.9493970870972</v>
+        <v>14.9493951797485</v>
       </c>
       <c r="H288" t="n">
         <v>8644</v>
@@ -8750,7 +8750,7 @@
         <v>22.7749996185303</v>
       </c>
       <c r="G289" t="n">
-        <v>14.8257102966309</v>
+        <v>14.8257131576538</v>
       </c>
       <c r="H289" t="n">
         <v>6026</v>
@@ -8779,7 +8779,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G290" t="n">
-        <v>15.0502948760986</v>
+        <v>15.0502958297729</v>
       </c>
       <c r="H290" t="n">
         <v>16462</v>
@@ -8808,7 +8808,7 @@
         <v>23.2099990844727</v>
       </c>
       <c r="G291" t="n">
-        <v>15.1088809967041</v>
+        <v>15.1088781356812</v>
       </c>
       <c r="H291" t="n">
         <v>10812</v>
@@ -8837,7 +8837,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G292" t="n">
-        <v>14.9461402893066</v>
+        <v>14.9461393356323</v>
       </c>
       <c r="H292" t="n">
         <v>8778</v>
@@ -8866,7 +8866,7 @@
         <v>23.1450004577637</v>
       </c>
       <c r="G293" t="n">
-        <v>15.0665702819824</v>
+        <v>15.0665683746338</v>
       </c>
       <c r="H293" t="n">
         <v>8410</v>
@@ -8895,7 +8895,7 @@
         <v>22.7749996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>14.8257102966309</v>
+        <v>14.8257131576538</v>
       </c>
       <c r="H294" t="n">
         <v>11182</v>
@@ -8924,7 +8924,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>15.0698251724243</v>
+        <v>15.0698213577271</v>
       </c>
       <c r="H295" t="n">
         <v>11234</v>
@@ -8953,7 +8953,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G296" t="n">
-        <v>14.8745374679565</v>
+        <v>14.8745336532593</v>
       </c>
       <c r="H296" t="n">
         <v>13602</v>
@@ -8982,7 +8982,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G297" t="n">
-        <v>14.9982194900513</v>
+        <v>14.998218536377</v>
       </c>
       <c r="H297" t="n">
         <v>11658</v>
@@ -9011,7 +9011,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G298" t="n">
-        <v>15.0633115768433</v>
+        <v>15.0633144378662</v>
       </c>
       <c r="H298" t="n">
         <v>8944</v>
@@ -9040,7 +9040,7 @@
         <v>23.2399997711182</v>
       </c>
       <c r="G299" t="n">
-        <v>15.1284122467041</v>
+        <v>15.1284103393555</v>
       </c>
       <c r="H299" t="n">
         <v>151122</v>
@@ -9069,7 +9069,7 @@
         <v>24.1450004577637</v>
       </c>
       <c r="G300" t="n">
-        <v>15.7175321578979</v>
+        <v>15.7175302505493</v>
       </c>
       <c r="H300" t="n">
         <v>54210</v>
@@ -9127,7 +9127,7 @@
         <v>24.25</v>
       </c>
       <c r="G302" t="n">
-        <v>15.7858848571777</v>
+        <v>15.7858839035034</v>
       </c>
       <c r="H302" t="n">
         <v>104308</v>
@@ -9156,7 +9156,7 @@
         <v>24.25</v>
       </c>
       <c r="G303" t="n">
-        <v>15.7858848571777</v>
+        <v>15.7858839035034</v>
       </c>
       <c r="H303" t="n">
         <v>69780</v>
@@ -9185,7 +9185,7 @@
         <v>24.25</v>
       </c>
       <c r="G304" t="n">
-        <v>15.7858848571777</v>
+        <v>15.7858839035034</v>
       </c>
       <c r="H304" t="n">
         <v>77186</v>
@@ -9214,7 +9214,7 @@
         <v>24.2450008392334</v>
       </c>
       <c r="G305" t="n">
-        <v>15.7826280593872</v>
+        <v>15.7826309204102</v>
       </c>
       <c r="H305" t="n">
         <v>31296</v>
@@ -9243,7 +9243,7 @@
         <v>24.2700004577637</v>
       </c>
       <c r="G306" t="n">
-        <v>15.798903465271</v>
+        <v>15.7989025115967</v>
       </c>
       <c r="H306" t="n">
         <v>45686</v>
@@ -9272,7 +9272,7 @@
         <v>24.6749992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>16.0625400543213</v>
+        <v>16.0625438690186</v>
       </c>
       <c r="H307" t="n">
         <v>46158</v>
@@ -9330,7 +9330,7 @@
         <v>25.125</v>
       </c>
       <c r="G309" t="n">
-        <v>16.3554801940918</v>
+        <v>16.3554782867432</v>
       </c>
       <c r="H309" t="n">
         <v>23980</v>
@@ -9359,7 +9359,7 @@
         <v>25.375</v>
       </c>
       <c r="G310" t="n">
-        <v>16.518217086792</v>
+        <v>16.5182189941406</v>
       </c>
       <c r="H310" t="n">
         <v>20208</v>
@@ -9388,7 +9388,7 @@
         <v>25.75</v>
       </c>
       <c r="G311" t="n">
-        <v>16.7623310089111</v>
+        <v>16.7623291015625</v>
       </c>
       <c r="H311" t="n">
         <v>27682</v>
@@ -9417,7 +9417,7 @@
         <v>25.9249992370605</v>
       </c>
       <c r="G312" t="n">
-        <v>16.8762454986572</v>
+        <v>16.8762493133545</v>
       </c>
       <c r="H312" t="n">
         <v>42832</v>
@@ -9504,7 +9504,7 @@
         <v>25.125</v>
       </c>
       <c r="G315" t="n">
-        <v>16.3554801940918</v>
+        <v>16.3554782867432</v>
       </c>
       <c r="H315" t="n">
         <v>72436</v>
@@ -9591,7 +9591,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H318" t="n">
         <v>25486</v>
@@ -9649,7 +9649,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>16.8599758148193</v>
+        <v>16.859977722168</v>
       </c>
       <c r="H320" t="n">
         <v>28130</v>
@@ -9765,7 +9765,7 @@
         <v>26.3250007629395</v>
       </c>
       <c r="G324" t="n">
-        <v>17.1366367340088</v>
+        <v>17.1366348266602</v>
       </c>
       <c r="H324" t="n">
         <v>36860</v>
@@ -9794,7 +9794,7 @@
         <v>26.1749992370605</v>
       </c>
       <c r="G325" t="n">
-        <v>17.038990020752</v>
+        <v>17.0389881134033</v>
       </c>
       <c r="H325" t="n">
         <v>35182</v>
@@ -9823,7 +9823,7 @@
         <v>26.25</v>
       </c>
       <c r="G326" t="n">
-        <v>17.0878143310547</v>
+        <v>17.0878124237061</v>
       </c>
       <c r="H326" t="n">
         <v>15382</v>
@@ -9997,7 +9997,7 @@
         <v>25.625</v>
       </c>
       <c r="G332" t="n">
-        <v>16.6809616088867</v>
+        <v>16.6809597015381</v>
       </c>
       <c r="H332" t="n">
         <v>33596</v>
@@ -10026,7 +10026,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H333" t="n">
         <v>58100</v>
@@ -10113,7 +10113,7 @@
         <v>25.5</v>
       </c>
       <c r="G336" t="n">
-        <v>16.5995903015137</v>
+        <v>16.599588394165</v>
       </c>
       <c r="H336" t="n">
         <v>60470</v>
@@ -10200,7 +10200,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G339" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H339" t="n">
         <v>23298</v>
@@ -10229,7 +10229,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H340" t="n">
         <v>13570</v>
@@ -10258,7 +10258,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H341" t="n">
         <v>39956</v>
@@ -10287,7 +10287,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G342" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H342" t="n">
         <v>17724</v>
@@ -10316,7 +10316,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H343" t="n">
         <v>28384</v>
@@ -10345,7 +10345,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>16.7297821044922</v>
+        <v>16.7297840118408</v>
       </c>
       <c r="H344" t="n">
         <v>26542</v>
@@ -10374,7 +10374,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>16.7961711883545</v>
+        <v>16.7961692810059</v>
       </c>
       <c r="H345" t="n">
         <v>23604</v>
@@ -10461,7 +10461,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>16.895751953125</v>
+        <v>16.8957538604736</v>
       </c>
       <c r="H348" t="n">
         <v>27102</v>
@@ -10490,7 +10490,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>17.0285301208496</v>
+        <v>17.0285263061523</v>
       </c>
       <c r="H349" t="n">
         <v>20320</v>
@@ -10519,7 +10519,7 @@
         <v>25.3199996948242</v>
       </c>
       <c r="G350" t="n">
-        <v>16.8094482421875</v>
+        <v>16.8094463348389</v>
       </c>
       <c r="H350" t="n">
         <v>8615</v>
@@ -10780,7 +10780,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G359" t="n">
-        <v>16.1986789703369</v>
+        <v>16.1986808776855</v>
       </c>
       <c r="H359" t="n">
         <v>25146</v>
@@ -10809,7 +10809,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G360" t="n">
-        <v>16.2119579315186</v>
+        <v>16.2119560241699</v>
       </c>
       <c r="H360" t="n">
         <v>11671</v>
@@ -11012,7 +11012,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G367" t="n">
-        <v>16.2982597351074</v>
+        <v>16.2982578277588</v>
       </c>
       <c r="H367" t="n">
         <v>15045</v>
@@ -11041,7 +11041,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G368" t="n">
-        <v>16.5040645599365</v>
+        <v>16.5040626525879</v>
       </c>
       <c r="H368" t="n">
         <v>31880</v>
@@ -11099,7 +11099,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>16.0327091217041</v>
+        <v>16.0327072143555</v>
       </c>
       <c r="H370" t="n">
         <v>15481</v>
@@ -11157,7 +11157,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G372" t="n">
-        <v>15.9397640228271</v>
+        <v>15.9397649765015</v>
       </c>
       <c r="H372" t="n">
         <v>11455</v>
@@ -11186,7 +11186,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G373" t="n">
-        <v>15.88001537323</v>
+        <v>15.8800163269043</v>
       </c>
       <c r="H373" t="n">
         <v>13704</v>
@@ -11215,7 +11215,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G374" t="n">
-        <v>16.2252311706543</v>
+        <v>16.2252349853516</v>
       </c>
       <c r="H374" t="n">
         <v>114656</v>
@@ -11244,7 +11244,7 @@
         <v>24.5</v>
       </c>
       <c r="G375" t="n">
-        <v>16.2650661468506</v>
+        <v>16.265064239502</v>
       </c>
       <c r="H375" t="n">
         <v>16852</v>
@@ -11273,7 +11273,7 @@
         <v>24.5</v>
       </c>
       <c r="G376" t="n">
-        <v>16.2650661468506</v>
+        <v>16.265064239502</v>
       </c>
       <c r="H376" t="n">
         <v>28911</v>
@@ -11302,7 +11302,7 @@
         <v>24.5</v>
       </c>
       <c r="G377" t="n">
-        <v>16.2650661468506</v>
+        <v>16.265064239502</v>
       </c>
       <c r="H377" t="n">
         <v>10222</v>
@@ -11331,7 +11331,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>16.1654872894287</v>
+        <v>16.1654853820801</v>
       </c>
       <c r="H378" t="n">
         <v>24957</v>
@@ -11418,7 +11418,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G381" t="n">
-        <v>16.2252311706543</v>
+        <v>16.2252349853516</v>
       </c>
       <c r="H381" t="n">
         <v>12500</v>
@@ -11447,7 +11447,7 @@
         <v>23.9699993133545</v>
       </c>
       <c r="G382" t="n">
-        <v>15.9132118225098</v>
+        <v>15.9132080078125</v>
       </c>
       <c r="H382" t="n">
         <v>28284</v>
@@ -11505,7 +11505,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>15.8667392730713</v>
+        <v>15.8667373657227</v>
       </c>
       <c r="H384" t="n">
         <v>21612</v>
@@ -11534,7 +11534,7 @@
         <v>23.5400009155273</v>
       </c>
       <c r="G385" t="n">
-        <v>15.6277408599854</v>
+        <v>15.6277418136597</v>
       </c>
       <c r="H385" t="n">
         <v>19567</v>
@@ -11563,7 +11563,7 @@
         <v>23.6299991607666</v>
       </c>
       <c r="G386" t="n">
-        <v>15.6874914169312</v>
+        <v>15.6874895095825</v>
       </c>
       <c r="H386" t="n">
         <v>10996</v>
@@ -11592,7 +11592,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>15.6343784332275</v>
+        <v>15.6343803405762</v>
       </c>
       <c r="H387" t="n">
         <v>7768</v>
@@ -11621,7 +11621,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G388" t="n">
-        <v>15.5148820877075</v>
+        <v>15.5148830413818</v>
       </c>
       <c r="H388" t="n">
         <v>13226</v>
@@ -11650,7 +11650,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G389" t="n">
-        <v>15.574631690979</v>
+        <v>15.5746297836304</v>
       </c>
       <c r="H389" t="n">
         <v>5900</v>
@@ -11679,7 +11679,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G390" t="n">
-        <v>15.5480766296387</v>
+        <v>15.5480756759644</v>
       </c>
       <c r="H390" t="n">
         <v>9311</v>
@@ -11708,7 +11708,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G391" t="n">
-        <v>15.5480766296387</v>
+        <v>15.5480756759644</v>
       </c>
       <c r="H391" t="n">
         <v>10546</v>
@@ -11737,7 +11737,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G392" t="n">
-        <v>15.906569480896</v>
+        <v>15.9065713882446</v>
       </c>
       <c r="H392" t="n">
         <v>9012</v>
@@ -11766,7 +11766,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G393" t="n">
-        <v>15.8667392730713</v>
+        <v>15.8667373657227</v>
       </c>
       <c r="H393" t="n">
         <v>17506</v>
@@ -11795,7 +11795,7 @@
         <v>23.6100006103516</v>
       </c>
       <c r="G394" t="n">
-        <v>15.6742134094238</v>
+        <v>15.6742124557495</v>
       </c>
       <c r="H394" t="n">
         <v>8077</v>
@@ -11824,7 +11824,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>15.7007675170898</v>
+        <v>15.7007703781128</v>
       </c>
       <c r="H395" t="n">
         <v>6337</v>
@@ -11853,7 +11853,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G396" t="n">
-        <v>15.919849395752</v>
+        <v>15.919846534729</v>
       </c>
       <c r="H396" t="n">
         <v>8675</v>
@@ -11911,7 +11911,7 @@
         <v>23.8600006103516</v>
       </c>
       <c r="G398" t="n">
-        <v>15.8401823043823</v>
+        <v>15.8401832580566</v>
       </c>
       <c r="H398" t="n">
         <v>8288</v>
@@ -11940,7 +11940,7 @@
         <v>23.6700000762939</v>
       </c>
       <c r="G399" t="n">
-        <v>15.7140455245972</v>
+        <v>15.7140483856201</v>
       </c>
       <c r="H399" t="n">
         <v>8103</v>
@@ -11998,7 +11998,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G401" t="n">
-        <v>15.8667392730713</v>
+        <v>15.8667373657227</v>
       </c>
       <c r="H401" t="n">
         <v>12169</v>
@@ -12027,7 +12027,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G402" t="n">
-        <v>15.919849395752</v>
+        <v>15.919846534729</v>
       </c>
       <c r="H402" t="n">
         <v>8314</v>
@@ -12056,7 +12056,7 @@
         <v>23.5400009155273</v>
       </c>
       <c r="G403" t="n">
-        <v>15.6277408599854</v>
+        <v>15.6277418136597</v>
       </c>
       <c r="H403" t="n">
         <v>20370</v>
@@ -12143,7 +12143,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G406" t="n">
-        <v>16.0659008026123</v>
+        <v>16.0659027099609</v>
       </c>
       <c r="H406" t="n">
         <v>12017</v>
@@ -12172,7 +12172,7 @@
         <v>23.75</v>
       </c>
       <c r="G407" t="n">
-        <v>15.7671566009521</v>
+        <v>15.7671575546265</v>
       </c>
       <c r="H407" t="n">
         <v>8223</v>
@@ -12201,7 +12201,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G408" t="n">
-        <v>15.826904296875</v>
+        <v>15.8269033432007</v>
       </c>
       <c r="H408" t="n">
         <v>6226</v>
@@ -12259,7 +12259,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>15.88001537323</v>
+        <v>15.8800163269043</v>
       </c>
       <c r="H410" t="n">
         <v>8776</v>
@@ -12317,7 +12317,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G412" t="n">
-        <v>15.8667392730713</v>
+        <v>15.8667373657227</v>
       </c>
       <c r="H412" t="n">
         <v>15726</v>
@@ -12404,7 +12404,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G415" t="n">
-        <v>15.8136301040649</v>
+        <v>15.8136281967163</v>
       </c>
       <c r="H415" t="n">
         <v>5865</v>
@@ -12433,7 +12433,7 @@
         <v>23.7600002288818</v>
       </c>
       <c r="G416" t="n">
-        <v>15.7737970352173</v>
+        <v>15.7737941741943</v>
       </c>
       <c r="H416" t="n">
         <v>7772</v>
@@ -12462,7 +12462,7 @@
         <v>23.9099998474121</v>
       </c>
       <c r="G417" t="n">
-        <v>15.8733787536621</v>
+        <v>15.8733777999878</v>
       </c>
       <c r="H417" t="n">
         <v>4176</v>
@@ -12491,7 +12491,7 @@
         <v>23.75</v>
       </c>
       <c r="G418" t="n">
-        <v>15.7671566009521</v>
+        <v>15.7671575546265</v>
       </c>
       <c r="H418" t="n">
         <v>6090</v>
@@ -12520,7 +12520,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>15.8999319076538</v>
+        <v>15.8999328613281</v>
       </c>
       <c r="H419" t="n">
         <v>6802</v>
@@ -12549,7 +12549,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G420" t="n">
-        <v>15.919849395752</v>
+        <v>15.919846534729</v>
       </c>
       <c r="H420" t="n">
         <v>14928</v>
@@ -12578,7 +12578,7 @@
         <v>23.7700004577637</v>
       </c>
       <c r="G421" t="n">
-        <v>15.7804317474365</v>
+        <v>15.7804327011108</v>
       </c>
       <c r="H421" t="n">
         <v>5725</v>
@@ -12607,7 +12607,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G422" t="n">
-        <v>15.8335447311401</v>
+        <v>15.8335418701172</v>
       </c>
       <c r="H422" t="n">
         <v>6283</v>
@@ -12636,7 +12636,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G423" t="n">
-        <v>15.919849395752</v>
+        <v>15.919846534729</v>
       </c>
       <c r="H423" t="n">
         <v>6748</v>
@@ -12665,7 +12665,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>15.7007675170898</v>
+        <v>15.7007703781128</v>
       </c>
       <c r="H424" t="n">
         <v>8677</v>
@@ -12723,7 +12723,7 @@
         <v>23.6100006103516</v>
       </c>
       <c r="G426" t="n">
-        <v>15.6742134094238</v>
+        <v>15.6742124557495</v>
       </c>
       <c r="H426" t="n">
         <v>8092</v>
@@ -12752,7 +12752,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>15.6675748825073</v>
+        <v>15.667573928833</v>
       </c>
       <c r="H427" t="n">
         <v>14917</v>
@@ -12781,7 +12781,7 @@
         <v>23.9899997711182</v>
       </c>
       <c r="G428" t="n">
-        <v>15.9264860153198</v>
+        <v>15.9264869689941</v>
       </c>
       <c r="H428" t="n">
         <v>11566</v>
@@ -12810,7 +12810,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>15.7007675170898</v>
+        <v>15.7007703781128</v>
       </c>
       <c r="H429" t="n">
         <v>14093</v>
@@ -12839,7 +12839,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>15.7007675170898</v>
+        <v>15.7007703781128</v>
       </c>
       <c r="H430" t="n">
         <v>7861</v>
@@ -12897,7 +12897,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G432" t="n">
-        <v>15.5945472717285</v>
+        <v>15.5945463180542</v>
       </c>
       <c r="H432" t="n">
         <v>12196</v>
@@ -12926,7 +12926,7 @@
         <v>23.4699993133545</v>
       </c>
       <c r="G433" t="n">
-        <v>15.5812673568726</v>
+        <v>15.5812692642212</v>
       </c>
       <c r="H433" t="n">
         <v>13201</v>
@@ -12955,7 +12955,7 @@
         <v>23.4099998474121</v>
       </c>
       <c r="G434" t="n">
-        <v>15.5414352416992</v>
+        <v>15.5414371490479</v>
       </c>
       <c r="H434" t="n">
         <v>16603</v>
@@ -12984,7 +12984,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G435" t="n">
-        <v>15.3024387359619</v>
+        <v>15.3024396896362</v>
       </c>
       <c r="H435" t="n">
         <v>46306</v>
@@ -13013,7 +13013,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>14.970498085022</v>
+        <v>14.9704990386963</v>
       </c>
       <c r="H436" t="n">
         <v>52172</v>
@@ -13042,7 +13042,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G437" t="n">
-        <v>14.9107465744019</v>
+        <v>14.9107513427734</v>
       </c>
       <c r="H437" t="n">
         <v>33551</v>
@@ -13071,7 +13071,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G438" t="n">
-        <v>15.3356342315674</v>
+        <v>15.3356332778931</v>
       </c>
       <c r="H438" t="n">
         <v>110457</v>
@@ -13100,7 +13100,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G439" t="n">
-        <v>15.1829433441162</v>
+        <v>15.1829395294189</v>
       </c>
       <c r="H439" t="n">
         <v>18187</v>
@@ -13129,7 +13129,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>15.1696653366089</v>
+        <v>15.1696662902832</v>
       </c>
       <c r="H440" t="n">
         <v>39653</v>
@@ -13187,7 +13187,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G442" t="n">
-        <v>14.970498085022</v>
+        <v>14.9704990386963</v>
       </c>
       <c r="H442" t="n">
         <v>18027</v>
@@ -13216,7 +13216,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G443" t="n">
-        <v>15.3754653930664</v>
+        <v>15.375467300415</v>
       </c>
       <c r="H443" t="n">
         <v>17814</v>
@@ -13245,7 +13245,7 @@
         <v>23.0900001525879</v>
       </c>
       <c r="G444" t="n">
-        <v>15.3289928436279</v>
+        <v>15.3289947509766</v>
       </c>
       <c r="H444" t="n">
         <v>17345</v>
@@ -13274,7 +13274,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G445" t="n">
-        <v>15.1099157333374</v>
+        <v>15.1099138259888</v>
       </c>
       <c r="H445" t="n">
         <v>17341</v>
@@ -13303,7 +13303,7 @@
         <v>22.6800003051758</v>
       </c>
       <c r="G446" t="n">
-        <v>15.0568037033081</v>
+        <v>15.0568046569824</v>
       </c>
       <c r="H446" t="n">
         <v>16263</v>
@@ -13332,7 +13332,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G447" t="n">
-        <v>15.2426910400391</v>
+        <v>15.2426891326904</v>
       </c>
       <c r="H447" t="n">
         <v>12788</v>
@@ -13361,7 +13361,7 @@
         <v>22.8299999237061</v>
       </c>
       <c r="G448" t="n">
-        <v>15.1563873291016</v>
+        <v>15.1563844680786</v>
       </c>
       <c r="H448" t="n">
         <v>5443</v>
@@ -13390,7 +13390,7 @@
         <v>23</v>
       </c>
       <c r="G449" t="n">
-        <v>15.2692451477051</v>
+        <v>15.2692432403564</v>
       </c>
       <c r="H449" t="n">
         <v>10905</v>
@@ -13419,7 +13419,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G450" t="n">
-        <v>15.2626094818115</v>
+        <v>15.2626066207886</v>
       </c>
       <c r="H450" t="n">
         <v>6370</v>
@@ -13448,7 +13448,7 @@
         <v>23.2299995422363</v>
       </c>
       <c r="G451" t="n">
-        <v>15.4219379425049</v>
+        <v>15.4219350814819</v>
       </c>
       <c r="H451" t="n">
         <v>11134</v>
@@ -13477,7 +13477,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G452" t="n">
-        <v>15.2958040237427</v>
+        <v>15.2958011627197</v>
       </c>
       <c r="H452" t="n">
         <v>4454</v>
@@ -13506,7 +13506,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>15.0368909835815</v>
+        <v>15.03688621521</v>
       </c>
       <c r="H453" t="n">
         <v>10838</v>
@@ -13535,7 +13535,7 @@
         <v>22.7800006866455</v>
       </c>
       <c r="G454" t="n">
-        <v>15.1231927871704</v>
+        <v>15.1231899261475</v>
       </c>
       <c r="H454" t="n">
         <v>5729</v>
@@ -13564,7 +13564,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G455" t="n">
-        <v>14.943943977356</v>
+        <v>14.9439420700073</v>
       </c>
       <c r="H455" t="n">
         <v>25180</v>
@@ -13593,7 +13593,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G456" t="n">
-        <v>14.9173917770386</v>
+        <v>14.9173879623413</v>
       </c>
       <c r="H456" t="n">
         <v>20855</v>
@@ -13680,7 +13680,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G459" t="n">
-        <v>14.7381420135498</v>
+        <v>14.7381401062012</v>
       </c>
       <c r="H459" t="n">
         <v>21908</v>
@@ -13767,7 +13767,7 @@
         <v>22.2900009155273</v>
       </c>
       <c r="G462" t="n">
-        <v>14.7978916168213</v>
+        <v>14.7978925704956</v>
       </c>
       <c r="H462" t="n">
         <v>15915</v>
@@ -13796,7 +13796,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G463" t="n">
-        <v>14.6850318908691</v>
+        <v>14.6850309371948</v>
       </c>
       <c r="H463" t="n">
         <v>16157</v>
@@ -13854,7 +13854,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G465" t="n">
-        <v>14.943943977356</v>
+        <v>14.9439420700073</v>
       </c>
       <c r="H465" t="n">
         <v>24851</v>
@@ -13912,7 +13912,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>14.9041137695312</v>
+        <v>14.9041147232056</v>
       </c>
       <c r="H467" t="n">
         <v>30696</v>
@@ -13941,7 +13941,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G468" t="n">
-        <v>15.348913192749</v>
+        <v>15.3489122390747</v>
       </c>
       <c r="H468" t="n">
         <v>57177</v>
@@ -13970,7 +13970,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G469" t="n">
-        <v>15.2626094818115</v>
+        <v>15.2626066207886</v>
       </c>
       <c r="H469" t="n">
         <v>33384</v>
@@ -13999,7 +13999,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G470" t="n">
-        <v>15.3356342315674</v>
+        <v>15.3356332778931</v>
       </c>
       <c r="H470" t="n">
         <v>47635</v>
@@ -14028,7 +14028,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G471" t="n">
-        <v>15.3688287734985</v>
+        <v>15.3688259124756</v>
       </c>
       <c r="H471" t="n">
         <v>16442</v>
@@ -14057,7 +14057,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G472" t="n">
-        <v>15.3821077346802</v>
+        <v>15.3821058273315</v>
       </c>
       <c r="H472" t="n">
         <v>8948</v>
@@ -14086,7 +14086,7 @@
         <v>23.25</v>
       </c>
       <c r="G473" t="n">
-        <v>15.4352130889893</v>
+        <v>15.4352178573608</v>
       </c>
       <c r="H473" t="n">
         <v>6803</v>
@@ -14115,7 +14115,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G474" t="n">
-        <v>15.3688287734985</v>
+        <v>15.3688259124756</v>
       </c>
       <c r="H474" t="n">
         <v>12512</v>
@@ -14144,7 +14144,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G475" t="n">
-        <v>15.2559671401978</v>
+        <v>15.255970954895</v>
       </c>
       <c r="H475" t="n">
         <v>16295</v>
@@ -14173,7 +14173,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G476" t="n">
-        <v>15.2626094818115</v>
+        <v>15.2626066207886</v>
       </c>
       <c r="H476" t="n">
         <v>26453</v>
@@ -14202,7 +14202,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G477" t="n">
-        <v>15.1962184906006</v>
+        <v>15.1962175369263</v>
       </c>
       <c r="H477" t="n">
         <v>17563</v>
@@ -14231,7 +14231,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G478" t="n">
-        <v>14.8908338546753</v>
+        <v>14.8908348083496</v>
       </c>
       <c r="H478" t="n">
         <v>19273</v>
@@ -14260,7 +14260,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G479" t="n">
-        <v>14.7381420135498</v>
+        <v>14.7381401062012</v>
       </c>
       <c r="H479" t="n">
         <v>22795</v>
@@ -14289,7 +14289,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G480" t="n">
-        <v>14.7115869522095</v>
+        <v>14.7115850448608</v>
       </c>
       <c r="H480" t="n">
         <v>26646</v>
@@ -14318,7 +14318,7 @@
         <v>22</v>
       </c>
       <c r="G481" t="n">
-        <v>14.6053647994995</v>
+        <v>14.6053667068481</v>
       </c>
       <c r="H481" t="n">
         <v>16602</v>
@@ -14347,7 +14347,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G482" t="n">
-        <v>14.6319236755371</v>
+        <v>14.6319208145142</v>
       </c>
       <c r="H482" t="n">
         <v>25240</v>
@@ -14376,7 +14376,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G483" t="n">
-        <v>14.8178062438965</v>
+        <v>14.8178091049194</v>
       </c>
       <c r="H483" t="n">
         <v>24247</v>
@@ -14434,7 +14434,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G485" t="n">
-        <v>14.7381420135498</v>
+        <v>14.7381401062012</v>
       </c>
       <c r="H485" t="n">
         <v>18997</v>
@@ -14463,7 +14463,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>14.7381420135498</v>
+        <v>14.7381401062012</v>
       </c>
       <c r="H486" t="n">
         <v>28390</v>
@@ -14492,7 +14492,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G487" t="n">
-        <v>14.7248630523682</v>
+        <v>14.7248649597168</v>
       </c>
       <c r="H487" t="n">
         <v>13749</v>
@@ -14521,7 +14521,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G488" t="n">
-        <v>14.8310852050781</v>
+        <v>14.8310842514038</v>
       </c>
       <c r="H488" t="n">
         <v>6401</v>
@@ -14579,7 +14579,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G490" t="n">
-        <v>15.0435256958008</v>
+        <v>15.0435266494751</v>
       </c>
       <c r="H490" t="n">
         <v>21194</v>
@@ -14608,7 +14608,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G491" t="n">
-        <v>15.348913192749</v>
+        <v>15.3489122390747</v>
       </c>
       <c r="H491" t="n">
         <v>20648</v>
@@ -14695,7 +14695,7 @@
         <v>23.8899993896484</v>
       </c>
       <c r="G494" t="n">
-        <v>15.8601007461548</v>
+        <v>15.8600969314575</v>
       </c>
       <c r="H494" t="n">
         <v>16818</v>
@@ -14724,7 +14724,7 @@
         <v>24.0699996948242</v>
       </c>
       <c r="G495" t="n">
-        <v>15.9795951843262</v>
+        <v>15.9795970916748</v>
       </c>
       <c r="H495" t="n">
         <v>50455</v>
@@ -14869,7 +14869,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G500" t="n">
-        <v>15.88001537323</v>
+        <v>15.8800163269043</v>
       </c>
       <c r="H500" t="n">
         <v>17468</v>
@@ -14898,7 +14898,7 @@
         <v>23.7900009155273</v>
       </c>
       <c r="G501" t="n">
-        <v>15.7937097549438</v>
+        <v>15.7937107086182</v>
       </c>
       <c r="H501" t="n">
         <v>11019</v>
@@ -14927,7 +14927,7 @@
         <v>23.7600002288818</v>
       </c>
       <c r="G502" t="n">
-        <v>15.7737970352173</v>
+        <v>15.7737941741943</v>
       </c>
       <c r="H502" t="n">
         <v>8775</v>
@@ -14956,7 +14956,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>15.3688287734985</v>
+        <v>15.3688259124756</v>
       </c>
       <c r="H503" t="n">
         <v>119066</v>
@@ -15101,7 +15101,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G508" t="n">
-        <v>15.906569480896</v>
+        <v>15.9065713882446</v>
       </c>
       <c r="H508" t="n">
         <v>17818</v>
@@ -15130,7 +15130,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G509" t="n">
-        <v>15.8534603118896</v>
+        <v>15.853458404541</v>
       </c>
       <c r="H509" t="n">
         <v>11692</v>
@@ -15159,7 +15159,7 @@
         <v>24.2800006866455</v>
       </c>
       <c r="G510" t="n">
-        <v>16.1190128326416</v>
+        <v>16.1190147399902</v>
       </c>
       <c r="H510" t="n">
         <v>19973</v>
@@ -15188,7 +15188,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G511" t="n">
-        <v>15.8335447311401</v>
+        <v>15.8335418701172</v>
       </c>
       <c r="H511" t="n">
         <v>12033</v>
@@ -15217,7 +15217,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G512" t="n">
-        <v>16.0194301605225</v>
+        <v>16.0194282531738</v>
       </c>
       <c r="H512" t="n">
         <v>12723</v>
@@ -15246,7 +15246,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>15.9995136260986</v>
+        <v>15.9995145797729</v>
       </c>
       <c r="H513" t="n">
         <v>3702</v>
@@ -15275,7 +15275,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>16.3978404998779</v>
+        <v>16.3978443145752</v>
       </c>
       <c r="H514" t="n">
         <v>22570</v>
@@ -15304,7 +15304,7 @@
         <v>24.5</v>
       </c>
       <c r="G515" t="n">
-        <v>16.2650661468506</v>
+        <v>16.265064239502</v>
       </c>
       <c r="H515" t="n">
         <v>31126</v>
@@ -15333,7 +15333,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G516" t="n">
-        <v>16.3978404998779</v>
+        <v>16.3978443145752</v>
       </c>
       <c r="H516" t="n">
         <v>32674</v>
@@ -15362,7 +15362,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G517" t="n">
-        <v>16.7961711883545</v>
+        <v>16.7961692810059</v>
       </c>
       <c r="H517" t="n">
         <v>39018</v>
@@ -15391,7 +15391,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G518" t="n">
-        <v>16.3978404998779</v>
+        <v>16.3978443145752</v>
       </c>
       <c r="H518" t="n">
         <v>52183</v>
@@ -15420,7 +15420,7 @@
         <v>24.5</v>
       </c>
       <c r="G519" t="n">
-        <v>16.2650661468506</v>
+        <v>16.265064239502</v>
       </c>
       <c r="H519" t="n">
         <v>38433</v>
@@ -15478,7 +15478,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>16.4642295837402</v>
+        <v>16.4642314910889</v>
       </c>
       <c r="H521" t="n">
         <v>7941</v>
@@ -15536,7 +15536,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>16.4642295837402</v>
+        <v>16.4642314910889</v>
       </c>
       <c r="H523" t="n">
         <v>11626</v>
@@ -15594,7 +15594,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G525" t="n">
-        <v>16.3978404998779</v>
+        <v>16.3978443145752</v>
       </c>
       <c r="H525" t="n">
         <v>8639</v>
@@ -15623,7 +15623,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G526" t="n">
-        <v>16.4974269866943</v>
+        <v>16.4974250793457</v>
       </c>
       <c r="H526" t="n">
         <v>17036</v>
@@ -15681,7 +15681,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G528" t="n">
-        <v>16.4642295837402</v>
+        <v>16.4642314910889</v>
       </c>
       <c r="H528" t="n">
         <v>5663</v>
@@ -15739,7 +15739,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>16.4642295837402</v>
+        <v>16.4642314910889</v>
       </c>
       <c r="H530" t="n">
         <v>7522</v>
@@ -15768,7 +15768,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>16.5306167602539</v>
+        <v>16.5306186676025</v>
       </c>
       <c r="H531" t="n">
         <v>11927</v>
@@ -15913,7 +15913,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>15.7007675170898</v>
+        <v>15.7007703781128</v>
       </c>
       <c r="H536" t="n">
         <v>35919</v>
@@ -15942,7 +15942,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G537" t="n">
-        <v>15.4020204544067</v>
+        <v>15.402024269104</v>
       </c>
       <c r="H537" t="n">
         <v>27608</v>
@@ -15971,7 +15971,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>15.6343784332275</v>
+        <v>15.6343803405762</v>
       </c>
       <c r="H538" t="n">
         <v>4181</v>
@@ -16029,7 +16029,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>15.3024387359619</v>
+        <v>15.3024396896362</v>
       </c>
       <c r="H540" t="n">
         <v>10526</v>
@@ -16116,7 +16116,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>15.8335447311401</v>
+        <v>15.8335418701172</v>
       </c>
       <c r="H543" t="n">
         <v>4994</v>
@@ -16145,7 +16145,7 @@
         <v>23.5</v>
       </c>
       <c r="G544" t="n">
-        <v>15.601185798645</v>
+        <v>15.6011848449707</v>
       </c>
       <c r="H544" t="n">
         <v>9277</v>
@@ -16203,7 +16203,7 @@
         <v>23.5</v>
       </c>
       <c r="G546" t="n">
-        <v>15.601185798645</v>
+        <v>15.6011848449707</v>
       </c>
       <c r="H546" t="n">
         <v>3051</v>
@@ -16232,7 +16232,7 @@
         <v>23.75</v>
       </c>
       <c r="G547" t="n">
-        <v>15.7671566009521</v>
+        <v>15.7671575546265</v>
       </c>
       <c r="H547" t="n">
         <v>8467</v>
@@ -16261,7 +16261,7 @@
         <v>23.5</v>
       </c>
       <c r="G548" t="n">
-        <v>15.601185798645</v>
+        <v>15.6011848449707</v>
       </c>
       <c r="H548" t="n">
         <v>9610</v>
@@ -16319,7 +16319,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G550" t="n">
-        <v>15.3024387359619</v>
+        <v>15.3024396896362</v>
       </c>
       <c r="H550" t="n">
         <v>5907</v>
@@ -16377,7 +16377,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>15.3688287734985</v>
+        <v>15.3688259124756</v>
       </c>
       <c r="H552" t="n">
         <v>12251</v>
@@ -16464,7 +16464,7 @@
         <v>23</v>
       </c>
       <c r="G555" t="n">
-        <v>15.2692451477051</v>
+        <v>15.2692432403564</v>
       </c>
       <c r="H555" t="n">
         <v>23218</v>
@@ -16493,7 +16493,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>15.0036945343018</v>
+        <v>15.0036935806274</v>
       </c>
       <c r="H556" t="n">
         <v>7780</v>
@@ -16522,7 +16522,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G557" t="n">
-        <v>15.0368909835815</v>
+        <v>15.03688621521</v>
       </c>
       <c r="H557" t="n">
         <v>11934</v>
@@ -16551,7 +16551,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>15.3356342315674</v>
+        <v>15.3356332778931</v>
       </c>
       <c r="H558" t="n">
         <v>10714</v>
@@ -16580,7 +16580,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>15.4020204544067</v>
+        <v>15.402024269104</v>
       </c>
       <c r="H559" t="n">
         <v>4229</v>
@@ -16667,7 +16667,7 @@
         <v>23.5</v>
       </c>
       <c r="G562" t="n">
-        <v>15.601185798645</v>
+        <v>15.6011848449707</v>
       </c>
       <c r="H562" t="n">
         <v>15956</v>
@@ -16696,7 +16696,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>15.4020204544067</v>
+        <v>15.402024269104</v>
       </c>
       <c r="H563" t="n">
         <v>9704</v>
@@ -16725,7 +16725,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>15.6343784332275</v>
+        <v>15.6343803405762</v>
       </c>
       <c r="H564" t="n">
         <v>4747</v>
@@ -16754,7 +16754,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G565" t="n">
-        <v>15.0036945343018</v>
+        <v>15.0036935806274</v>
       </c>
       <c r="H565" t="n">
         <v>29225</v>
@@ -16783,7 +16783,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>15.1696653366089</v>
+        <v>15.1696662902832</v>
       </c>
       <c r="H566" t="n">
         <v>9826</v>
@@ -16812,7 +16812,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G567" t="n">
-        <v>15.0700836181641</v>
+        <v>15.0700845718384</v>
       </c>
       <c r="H567" t="n">
         <v>4537</v>
@@ -16841,7 +16841,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G568" t="n">
-        <v>14.970498085022</v>
+        <v>14.9704990386963</v>
       </c>
       <c r="H568" t="n">
         <v>5053</v>
@@ -16899,7 +16899,7 @@
         <v>21.75</v>
       </c>
       <c r="G570" t="n">
-        <v>14.4393949508667</v>
+        <v>14.439395904541</v>
       </c>
       <c r="H570" t="n">
         <v>27107</v>
@@ -16928,7 +16928,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>14.1738433837891</v>
+        <v>14.1738443374634</v>
       </c>
       <c r="H571" t="n">
         <v>4936</v>
@@ -16986,7 +16986,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G573" t="n">
-        <v>14.4062023162842</v>
+        <v>14.4062013626099</v>
       </c>
       <c r="H573" t="n">
         <v>5424</v>
@@ -17015,7 +17015,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G574" t="n">
-        <v>15.1696653366089</v>
+        <v>15.1696662902832</v>
       </c>
       <c r="H574" t="n">
         <v>40605</v>
@@ -17044,7 +17044,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G575" t="n">
-        <v>14.8709173202515</v>
+        <v>14.8709182739258</v>
       </c>
       <c r="H575" t="n">
         <v>23295</v>
@@ -17073,7 +17073,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>14.5389785766602</v>
+        <v>14.5389776229858</v>
       </c>
       <c r="H576" t="n">
         <v>7219</v>
@@ -17131,7 +17131,7 @@
         <v>22</v>
       </c>
       <c r="G578" t="n">
-        <v>14.6053647994995</v>
+        <v>14.6053667068481</v>
       </c>
       <c r="H578" t="n">
         <v>12126</v>
@@ -17160,7 +17160,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G579" t="n">
-        <v>14.4725894927979</v>
+        <v>14.4725875854492</v>
       </c>
       <c r="H579" t="n">
         <v>5333</v>
@@ -17189,7 +17189,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>14.5389785766602</v>
+        <v>14.5389776229858</v>
       </c>
       <c r="H580" t="n">
         <v>8533</v>
@@ -17218,7 +17218,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>14.5389785766602</v>
+        <v>14.5389776229858</v>
       </c>
       <c r="H581" t="n">
         <v>8868</v>
@@ -17305,7 +17305,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>14.4725894927979</v>
+        <v>14.4725875854492</v>
       </c>
       <c r="H584" t="n">
         <v>5163</v>
@@ -17363,7 +17363,7 @@
         <v>22</v>
       </c>
       <c r="G586" t="n">
-        <v>14.6053647994995</v>
+        <v>14.6053667068481</v>
       </c>
       <c r="H586" t="n">
         <v>13137</v>
@@ -17392,7 +17392,7 @@
         <v>22.25</v>
       </c>
       <c r="G587" t="n">
-        <v>14.7713356018066</v>
+        <v>14.7713346481323</v>
       </c>
       <c r="H587" t="n">
         <v>13227</v>
@@ -17421,7 +17421,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>15.0368909835815</v>
+        <v>15.03688621521</v>
       </c>
       <c r="H588" t="n">
         <v>12952</v>
@@ -17450,7 +17450,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>14.837721824646</v>
+        <v>14.8377237319946</v>
       </c>
       <c r="H589" t="n">
         <v>3650</v>
@@ -17479,7 +17479,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>15.0368909835815</v>
+        <v>15.03688621521</v>
       </c>
       <c r="H590" t="n">
         <v>5693</v>
@@ -17508,7 +17508,7 @@
         <v>22.5</v>
       </c>
       <c r="G591" t="n">
-        <v>14.9373064041138</v>
+        <v>14.9373073577881</v>
       </c>
       <c r="H591" t="n">
         <v>4490</v>
@@ -17537,7 +17537,7 @@
         <v>22.25</v>
       </c>
       <c r="G592" t="n">
-        <v>14.7713356018066</v>
+        <v>14.7713346481323</v>
       </c>
       <c r="H592" t="n">
         <v>2424</v>
@@ -17595,7 +17595,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G594" t="n">
-        <v>14.9041137695312</v>
+        <v>14.9041147232056</v>
       </c>
       <c r="H594" t="n">
         <v>8464</v>
@@ -17624,7 +17624,7 @@
         <v>22.75</v>
       </c>
       <c r="G595" t="n">
-        <v>15.1032743453979</v>
+        <v>15.1032752990723</v>
       </c>
       <c r="H595" t="n">
         <v>16551</v>
@@ -17653,7 +17653,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>15.0700836181641</v>
+        <v>15.0700845718384</v>
       </c>
       <c r="H596" t="n">
         <v>6396</v>
@@ -17682,7 +17682,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>15.0700836181641</v>
+        <v>15.0700845718384</v>
       </c>
       <c r="H597" t="n">
         <v>14617</v>
@@ -17711,7 +17711,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G598" t="n">
-        <v>15.4102649688721</v>
+        <v>15.4102621078491</v>
       </c>
       <c r="H598" t="n">
         <v>16028</v>
@@ -17740,7 +17740,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>15.27419090271</v>
+        <v>15.2741937637329</v>
       </c>
       <c r="H599" t="n">
         <v>19211</v>
@@ -17769,7 +17769,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>15.4102649688721</v>
+        <v>15.4102621078491</v>
       </c>
       <c r="H600" t="n">
         <v>14727</v>
@@ -17798,7 +17798,7 @@
         <v>22</v>
       </c>
       <c r="G601" t="n">
-        <v>14.9680271148682</v>
+        <v>14.9680280685425</v>
       </c>
       <c r="H601" t="n">
         <v>4999</v>
@@ -17827,7 +17827,7 @@
         <v>22.25</v>
       </c>
       <c r="G602" t="n">
-        <v>15.1381187438965</v>
+        <v>15.1381168365479</v>
       </c>
       <c r="H602" t="n">
         <v>7512</v>
@@ -17856,7 +17856,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G603" t="n">
-        <v>15.27419090271</v>
+        <v>15.2741937637329</v>
       </c>
       <c r="H603" t="n">
         <v>20144</v>
@@ -17914,7 +17914,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>14.7639198303223</v>
+        <v>14.7639169692993</v>
       </c>
       <c r="H605" t="n">
         <v>23055</v>
@@ -17943,7 +17943,7 @@
         <v>21.75</v>
       </c>
       <c r="G606" t="n">
-        <v>14.7979345321655</v>
+        <v>14.7979354858398</v>
       </c>
       <c r="H606" t="n">
         <v>16355</v>
@@ -18030,7 +18030,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G609" t="n">
-        <v>13.9814987182617</v>
+        <v>13.9814958572388</v>
       </c>
       <c r="H609" t="n">
         <v>7918</v>
@@ -18059,7 +18059,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G610" t="n">
-        <v>13.913462638855</v>
+        <v>13.9134616851807</v>
       </c>
       <c r="H610" t="n">
         <v>11316</v>
@@ -18088,7 +18088,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>13.9814987182617</v>
+        <v>13.9814958572388</v>
       </c>
       <c r="H611" t="n">
         <v>4858</v>
@@ -18117,7 +18117,7 @@
         <v>20.5</v>
       </c>
       <c r="G612" t="n">
-        <v>13.9474792480469</v>
+        <v>13.9474782943726</v>
       </c>
       <c r="H612" t="n">
         <v>11649</v>
@@ -18146,7 +18146,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G613" t="n">
-        <v>13.3623638153076</v>
+        <v>13.3623647689819</v>
       </c>
       <c r="H613" t="n">
         <v>26842</v>
@@ -18175,7 +18175,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G614" t="n">
-        <v>13.5800809860229</v>
+        <v>13.5800828933716</v>
       </c>
       <c r="H614" t="n">
         <v>28796</v>
@@ -18204,7 +18204,7 @@
         <v>20.25</v>
       </c>
       <c r="G615" t="n">
-        <v>13.7773866653442</v>
+        <v>13.7773885726929</v>
       </c>
       <c r="H615" t="n">
         <v>15960</v>
@@ -18262,7 +18262,7 @@
         <v>21.25</v>
       </c>
       <c r="G617" t="n">
-        <v>14.4577541351318</v>
+        <v>14.4577522277832</v>
       </c>
       <c r="H617" t="n">
         <v>16848</v>
@@ -18291,7 +18291,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>14.4917726516724</v>
+        <v>14.4917707443237</v>
       </c>
       <c r="H618" t="n">
         <v>7999</v>
@@ -18320,7 +18320,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G619" t="n">
-        <v>14.3897171020508</v>
+        <v>14.3897151947021</v>
       </c>
       <c r="H619" t="n">
         <v>11170</v>
@@ -18349,7 +18349,7 @@
         <v>21</v>
       </c>
       <c r="G620" t="n">
-        <v>14.2876615524292</v>
+        <v>14.2876634597778</v>
       </c>
       <c r="H620" t="n">
         <v>8044</v>
@@ -18407,7 +18407,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>14.1515865325928</v>
+        <v>14.1515884399414</v>
       </c>
       <c r="H622" t="n">
         <v>15992</v>
@@ -18436,7 +18436,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>14.593825340271</v>
+        <v>14.5938282012939</v>
       </c>
       <c r="H623" t="n">
         <v>4744</v>
@@ -18465,7 +18465,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>14.593825340271</v>
+        <v>14.5938282012939</v>
       </c>
       <c r="H624" t="n">
         <v>7265</v>
@@ -18494,7 +18494,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G625" t="n">
-        <v>14.7639198303223</v>
+        <v>14.7639169692993</v>
       </c>
       <c r="H625" t="n">
         <v>17666</v>
@@ -18523,7 +18523,7 @@
         <v>21.5</v>
       </c>
       <c r="G626" t="n">
-        <v>14.6278457641602</v>
+        <v>14.6278448104858</v>
       </c>
       <c r="H626" t="n">
         <v>19418</v>
@@ -18552,7 +18552,7 @@
         <v>21.5</v>
       </c>
       <c r="G627" t="n">
-        <v>14.6278457641602</v>
+        <v>14.6278448104858</v>
       </c>
       <c r="H627" t="n">
         <v>23517</v>
@@ -18610,7 +18610,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G629" t="n">
-        <v>14.0155153274536</v>
+        <v>14.0155162811279</v>
       </c>
       <c r="H629" t="n">
         <v>20951</v>
@@ -18639,7 +18639,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>14.0835523605347</v>
+        <v>14.083553314209</v>
       </c>
       <c r="H630" t="n">
         <v>18193</v>
@@ -18697,7 +18697,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G632" t="n">
-        <v>13.5528688430786</v>
+        <v>13.5528659820557</v>
       </c>
       <c r="H632" t="n">
         <v>379624</v>
@@ -18726,7 +18726,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G633" t="n">
-        <v>14.0155153274536</v>
+        <v>14.0155162811279</v>
       </c>
       <c r="H633" t="n">
         <v>21168</v>
@@ -18755,7 +18755,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>14.1515865325928</v>
+        <v>14.1515884399414</v>
       </c>
       <c r="H634" t="n">
         <v>8297</v>
@@ -18784,7 +18784,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>14.0155153274536</v>
+        <v>14.0155162811279</v>
       </c>
       <c r="H635" t="n">
         <v>22823</v>
@@ -18813,7 +18813,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G636" t="n">
-        <v>14.0155153274536</v>
+        <v>14.0155162811279</v>
       </c>
       <c r="H636" t="n">
         <v>12487</v>
@@ -18842,7 +18842,7 @@
         <v>21</v>
       </c>
       <c r="G637" t="n">
-        <v>14.2876615524292</v>
+        <v>14.2876634597778</v>
       </c>
       <c r="H637" t="n">
         <v>11238</v>
@@ -18871,7 +18871,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G638" t="n">
-        <v>14.2536430358887</v>
+        <v>14.2536449432373</v>
       </c>
       <c r="H638" t="n">
         <v>5536</v>
@@ -18900,7 +18900,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>14.1515865325928</v>
+        <v>14.1515884399414</v>
       </c>
       <c r="H639" t="n">
         <v>6786</v>
@@ -18929,7 +18929,7 @@
         <v>20.5</v>
       </c>
       <c r="G640" t="n">
-        <v>13.9474792480469</v>
+        <v>13.9474782943726</v>
       </c>
       <c r="H640" t="n">
         <v>9505</v>
@@ -18958,7 +18958,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G641" t="n">
-        <v>13.9814987182617</v>
+        <v>13.9814958572388</v>
       </c>
       <c r="H641" t="n">
         <v>15674</v>
@@ -18987,7 +18987,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G642" t="n">
-        <v>13.8114051818848</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H642" t="n">
         <v>11109</v>
@@ -19074,7 +19074,7 @@
         <v>20.5</v>
       </c>
       <c r="G645" t="n">
-        <v>13.9474792480469</v>
+        <v>13.9474782943726</v>
       </c>
       <c r="H645" t="n">
         <v>7529</v>
@@ -19248,7 +19248,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G651" t="n">
-        <v>14.2536430358887</v>
+        <v>14.2536449432373</v>
       </c>
       <c r="H651" t="n">
         <v>6625</v>
@@ -19277,7 +19277,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G652" t="n">
-        <v>14.1515865325928</v>
+        <v>14.1515884399414</v>
       </c>
       <c r="H652" t="n">
         <v>2755</v>
@@ -19306,7 +19306,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>13.913462638855</v>
+        <v>13.9134616851807</v>
       </c>
       <c r="H653" t="n">
         <v>2488</v>
@@ -19335,7 +19335,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>13.8114051818848</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H654" t="n">
         <v>8673</v>
@@ -19364,7 +19364,7 @@
         <v>20</v>
       </c>
       <c r="G655" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072959899902</v>
       </c>
       <c r="H655" t="n">
         <v>12516</v>
@@ -19393,7 +19393,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>13.6413154602051</v>
+        <v>13.6413145065308</v>
       </c>
       <c r="H656" t="n">
         <v>10534</v>
@@ -19451,7 +19451,7 @@
         <v>20.25</v>
       </c>
       <c r="G658" t="n">
-        <v>13.7773866653442</v>
+        <v>13.7773885726929</v>
       </c>
       <c r="H658" t="n">
         <v>3800</v>
@@ -19480,7 +19480,7 @@
         <v>20.5</v>
       </c>
       <c r="G659" t="n">
-        <v>13.9474792480469</v>
+        <v>13.9474782943726</v>
       </c>
       <c r="H659" t="n">
         <v>11358</v>
@@ -19509,7 +19509,7 @@
         <v>20.5</v>
       </c>
       <c r="G660" t="n">
-        <v>13.9474792480469</v>
+        <v>13.9474782943726</v>
       </c>
       <c r="H660" t="n">
         <v>5113</v>
@@ -19625,7 +19625,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G664" t="n">
-        <v>13.7093505859375</v>
+        <v>13.7093515396118</v>
       </c>
       <c r="H664" t="n">
         <v>5119</v>
@@ -19683,7 +19683,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G666" t="n">
-        <v>13.5800809860229</v>
+        <v>13.5800828933716</v>
       </c>
       <c r="H666" t="n">
         <v>6907</v>
@@ -19712,7 +19712,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>13.6413154602051</v>
+        <v>13.6413145065308</v>
       </c>
       <c r="H667" t="n">
         <v>20238</v>
@@ -19741,7 +19741,7 @@
         <v>20.25</v>
       </c>
       <c r="G668" t="n">
-        <v>13.7773866653442</v>
+        <v>13.7773885726929</v>
       </c>
       <c r="H668" t="n">
         <v>11504</v>
@@ -19799,7 +19799,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G670" t="n">
-        <v>13.4167947769165</v>
+        <v>13.4167957305908</v>
       </c>
       <c r="H670" t="n">
         <v>19548</v>
@@ -19828,7 +19828,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G671" t="n">
-        <v>13.3487577438354</v>
+        <v>13.3487596511841</v>
       </c>
       <c r="H671" t="n">
         <v>9198</v>
@@ -19857,7 +19857,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G672" t="n">
-        <v>13.2943286895752</v>
+        <v>13.2943315505981</v>
       </c>
       <c r="H672" t="n">
         <v>4957</v>
@@ -19886,7 +19886,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G673" t="n">
-        <v>13.7093505859375</v>
+        <v>13.7093515396118</v>
       </c>
       <c r="H673" t="n">
         <v>1601</v>
@@ -19915,7 +19915,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G674" t="n">
-        <v>13.335150718689</v>
+        <v>13.3351516723633</v>
       </c>
       <c r="H674" t="n">
         <v>3740</v>
@@ -19944,7 +19944,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G675" t="n">
-        <v>13.4848318099976</v>
+        <v>13.4848299026489</v>
       </c>
       <c r="H675" t="n">
         <v>4571</v>
@@ -19973,7 +19973,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G676" t="n">
-        <v>13.40318775177</v>
+        <v>13.4031887054443</v>
       </c>
       <c r="H676" t="n">
         <v>5717</v>
@@ -20031,7 +20031,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G678" t="n">
-        <v>13.5664749145508</v>
+        <v>13.5664777755737</v>
       </c>
       <c r="H678" t="n">
         <v>1643</v>
@@ -20089,7 +20089,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G680" t="n">
-        <v>13.4440097808838</v>
+        <v>13.4440078735352</v>
       </c>
       <c r="H680" t="n">
         <v>10139</v>
@@ -20147,7 +20147,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G682" t="n">
-        <v>13.4440097808838</v>
+        <v>13.4440078735352</v>
       </c>
       <c r="H682" t="n">
         <v>14935</v>
@@ -20176,7 +20176,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G683" t="n">
-        <v>13.4440097808838</v>
+        <v>13.4440078735352</v>
       </c>
       <c r="H683" t="n">
         <v>3125</v>
@@ -20234,7 +20234,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G685" t="n">
-        <v>13.5256538391113</v>
+        <v>13.525652885437</v>
       </c>
       <c r="H685" t="n">
         <v>9234</v>
@@ -20263,7 +20263,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G686" t="n">
-        <v>13.5800809860229</v>
+        <v>13.5800828933716</v>
       </c>
       <c r="H686" t="n">
         <v>3064</v>
@@ -20292,7 +20292,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G687" t="n">
-        <v>13.5528688430786</v>
+        <v>13.5528659820557</v>
       </c>
       <c r="H687" t="n">
         <v>9495</v>
@@ -20379,7 +20379,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G690" t="n">
-        <v>13.5936899185181</v>
+        <v>13.5936880111694</v>
       </c>
       <c r="H690" t="n">
         <v>4539</v>
@@ -20408,7 +20408,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G691" t="n">
-        <v>13.5936899185181</v>
+        <v>13.5936880111694</v>
       </c>
       <c r="H691" t="n">
         <v>5469</v>
@@ -20437,7 +20437,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>13.6413154602051</v>
+        <v>13.6413145065308</v>
       </c>
       <c r="H692" t="n">
         <v>2884</v>
@@ -20495,7 +20495,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>13.913462638855</v>
+        <v>13.9134616851807</v>
       </c>
       <c r="H694" t="n">
         <v>6276</v>
@@ -20524,7 +20524,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G695" t="n">
-        <v>14.0155153274536</v>
+        <v>14.0155162811279</v>
       </c>
       <c r="H695" t="n">
         <v>6632</v>
@@ -20582,7 +20582,7 @@
         <v>21</v>
       </c>
       <c r="G697" t="n">
-        <v>14.2876615524292</v>
+        <v>14.2876634597778</v>
       </c>
       <c r="H697" t="n">
         <v>10247</v>
@@ -20669,7 +20669,7 @@
         <v>21</v>
       </c>
       <c r="G700" t="n">
-        <v>14.2876615524292</v>
+        <v>14.2876634597778</v>
       </c>
       <c r="H700" t="n">
         <v>7346</v>
@@ -20727,7 +20727,7 @@
         <v>20.25</v>
       </c>
       <c r="G702" t="n">
-        <v>13.7773866653442</v>
+        <v>13.7773885726929</v>
       </c>
       <c r="H702" t="n">
         <v>12159</v>
@@ -20756,7 +20756,7 @@
         <v>20</v>
       </c>
       <c r="G703" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072959899902</v>
       </c>
       <c r="H703" t="n">
         <v>13989</v>
@@ -20785,7 +20785,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>14.0155153274536</v>
+        <v>14.0155162811279</v>
       </c>
       <c r="H704" t="n">
         <v>11866</v>
@@ -20814,7 +20814,7 @@
         <v>20.5</v>
       </c>
       <c r="G705" t="n">
-        <v>13.9474792480469</v>
+        <v>13.9474782943726</v>
       </c>
       <c r="H705" t="n">
         <v>10779</v>
@@ -20843,7 +20843,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G706" t="n">
-        <v>13.5528688430786</v>
+        <v>13.5528659820557</v>
       </c>
       <c r="H706" t="n">
         <v>12267</v>
@@ -20872,7 +20872,7 @@
         <v>19</v>
       </c>
       <c r="G707" t="n">
-        <v>12.9269323348999</v>
+        <v>12.9269313812256</v>
       </c>
       <c r="H707" t="n">
         <v>14565</v>
@@ -20901,7 +20901,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G708" t="n">
-        <v>12.9949684143066</v>
+        <v>12.994969367981</v>
       </c>
       <c r="H708" t="n">
         <v>14071</v>
@@ -20959,7 +20959,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G710" t="n">
-        <v>12.872501373291</v>
+        <v>12.8725023269653</v>
       </c>
       <c r="H710" t="n">
         <v>18510</v>
@@ -21104,7 +21104,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G715" t="n">
-        <v>12.6683950424194</v>
+        <v>12.6683940887451</v>
       </c>
       <c r="H715" t="n">
         <v>14884</v>
@@ -21133,7 +21133,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G716" t="n">
-        <v>12.3009977340698</v>
+        <v>12.3009948730469</v>
       </c>
       <c r="H716" t="n">
         <v>5527</v>
@@ -21162,7 +21162,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G717" t="n">
-        <v>12.2057466506958</v>
+        <v>12.2057476043701</v>
       </c>
       <c r="H717" t="n">
         <v>5563</v>
@@ -21191,7 +21191,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G718" t="n">
-        <v>11.7022762298584</v>
+        <v>11.7022771835327</v>
       </c>
       <c r="H718" t="n">
         <v>25559</v>
@@ -21220,7 +21220,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G719" t="n">
-        <v>12.1785306930542</v>
+        <v>12.1785287857056</v>
       </c>
       <c r="H719" t="n">
         <v>25164</v>
@@ -21249,7 +21249,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G720" t="n">
-        <v>12.899715423584</v>
+        <v>12.8997173309326</v>
       </c>
       <c r="H720" t="n">
         <v>22967</v>
@@ -21278,7 +21278,7 @@
         <v>19</v>
       </c>
       <c r="G721" t="n">
-        <v>12.9269323348999</v>
+        <v>12.9269313812256</v>
       </c>
       <c r="H721" t="n">
         <v>29595</v>
@@ -21307,7 +21307,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>12.9949684143066</v>
+        <v>12.994969367981</v>
       </c>
       <c r="H722" t="n">
         <v>8271</v>
@@ -21336,7 +21336,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G723" t="n">
-        <v>13.0357904434204</v>
+        <v>13.0357885360718</v>
       </c>
       <c r="H723" t="n">
         <v>5000</v>
@@ -21365,7 +21365,7 @@
         <v>19.5</v>
       </c>
       <c r="G724" t="n">
-        <v>13.2671146392822</v>
+        <v>13.2671136856079</v>
       </c>
       <c r="H724" t="n">
         <v>10744</v>
@@ -21394,7 +21394,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G725" t="n">
-        <v>13.5256538391113</v>
+        <v>13.525652885437</v>
       </c>
       <c r="H725" t="n">
         <v>4378</v>
@@ -21452,7 +21452,7 @@
         <v>20</v>
       </c>
       <c r="G727" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072959899902</v>
       </c>
       <c r="H727" t="n">
         <v>6999</v>
@@ -21510,7 +21510,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G729" t="n">
-        <v>13.2535066604614</v>
+        <v>13.2535057067871</v>
       </c>
       <c r="H729" t="n">
         <v>13027</v>
@@ -21539,7 +21539,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G730" t="n">
-        <v>13.0766124725342</v>
+        <v>13.0766134262085</v>
       </c>
       <c r="H730" t="n">
         <v>2953</v>
@@ -21568,7 +21568,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G731" t="n">
-        <v>12.9405393600464</v>
+        <v>12.9405384063721</v>
       </c>
       <c r="H731" t="n">
         <v>10131</v>
@@ -21597,7 +21597,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G732" t="n">
-        <v>12.8044662475586</v>
+        <v>12.8044672012329</v>
       </c>
       <c r="H732" t="n">
         <v>3593</v>
@@ -21626,7 +21626,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G733" t="n">
-        <v>12.8861103057861</v>
+        <v>12.8861112594604</v>
       </c>
       <c r="H733" t="n">
         <v>7040</v>
@@ -21742,7 +21742,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>12.7908573150635</v>
+        <v>12.7908582687378</v>
       </c>
       <c r="H737" t="n">
         <v>1733</v>
@@ -21771,7 +21771,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G738" t="n">
-        <v>12.4370708465576</v>
+        <v>12.4370698928833</v>
       </c>
       <c r="H738" t="n">
         <v>18297</v>
@@ -21800,7 +21800,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G739" t="n">
-        <v>12.5459280014038</v>
+        <v>12.5459299087524</v>
       </c>
       <c r="H739" t="n">
         <v>7939</v>
@@ -21829,7 +21829,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G740" t="n">
-        <v>12.50510597229</v>
+        <v>12.5051050186157</v>
       </c>
       <c r="H740" t="n">
         <v>6113</v>
@@ -21858,7 +21858,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>12.7908573150635</v>
+        <v>12.7908582687378</v>
       </c>
       <c r="H741" t="n">
         <v>4136</v>
@@ -21887,7 +21887,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G742" t="n">
-        <v>12.7364282608032</v>
+        <v>12.7364311218262</v>
       </c>
       <c r="H742" t="n">
         <v>3101</v>
@@ -21945,7 +21945,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G744" t="n">
-        <v>12.6003570556641</v>
+        <v>12.6003561019897</v>
       </c>
       <c r="H744" t="n">
         <v>5675</v>
@@ -21974,7 +21974,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G745" t="n">
-        <v>12.5459280014038</v>
+        <v>12.5459299087524</v>
       </c>
       <c r="H745" t="n">
         <v>2760</v>
@@ -22003,7 +22003,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>13.1310405731201</v>
+        <v>13.1310415267944</v>
       </c>
       <c r="H746" t="n">
         <v>13155</v>
@@ -22032,7 +22032,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G747" t="n">
-        <v>13.4440097808838</v>
+        <v>13.4440078735352</v>
       </c>
       <c r="H747" t="n">
         <v>9190</v>
@@ -22061,7 +22061,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G748" t="n">
-        <v>13.3487577438354</v>
+        <v>13.3487596511841</v>
       </c>
       <c r="H748" t="n">
         <v>4721</v>
@@ -22090,7 +22090,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G749" t="n">
-        <v>13.1582565307617</v>
+        <v>13.158257484436</v>
       </c>
       <c r="H749" t="n">
         <v>4134</v>
@@ -22119,7 +22119,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G750" t="n">
-        <v>12.5731430053711</v>
+        <v>12.5731420516968</v>
       </c>
       <c r="H750" t="n">
         <v>9432</v>
@@ -22148,7 +22148,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G751" t="n">
-        <v>12.750036239624</v>
+        <v>12.7500352859497</v>
       </c>
       <c r="H751" t="n">
         <v>6797</v>
@@ -22177,7 +22177,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G752" t="n">
-        <v>12.7092142105103</v>
+        <v>12.7092170715332</v>
       </c>
       <c r="H752" t="n">
         <v>6487</v>
@@ -22206,7 +22206,7 @@
         <v>18.5</v>
       </c>
       <c r="G753" t="n">
-        <v>12.5867500305176</v>
+        <v>12.5867509841919</v>
       </c>
       <c r="H753" t="n">
         <v>6629</v>
@@ -22235,7 +22235,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G754" t="n">
-        <v>12.845287322998</v>
+        <v>12.8452882766724</v>
       </c>
       <c r="H754" t="n">
         <v>3908</v>
@@ -22264,7 +22264,7 @@
         <v>19</v>
       </c>
       <c r="G755" t="n">
-        <v>12.9269323348999</v>
+        <v>12.9269313812256</v>
       </c>
       <c r="H755" t="n">
         <v>21246</v>
@@ -22293,7 +22293,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>12.7908573150635</v>
+        <v>12.7908582687378</v>
       </c>
       <c r="H756" t="n">
         <v>5719</v>
@@ -22322,7 +22322,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G757" t="n">
-        <v>12.5459280014038</v>
+        <v>12.5459299087524</v>
       </c>
       <c r="H757" t="n">
         <v>9266</v>
@@ -22351,7 +22351,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G758" t="n">
-        <v>12.4370708465576</v>
+        <v>12.4370698928833</v>
       </c>
       <c r="H758" t="n">
         <v>3451</v>
@@ -22380,7 +22380,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G759" t="n">
-        <v>12.3554277420044</v>
+        <v>12.3554258346558</v>
       </c>
       <c r="H759" t="n">
         <v>3958</v>
@@ -22409,7 +22409,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G760" t="n">
-        <v>12.0560655593872</v>
+        <v>12.0560636520386</v>
       </c>
       <c r="H760" t="n">
         <v>11340</v>
@@ -22438,7 +22438,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G761" t="n">
-        <v>12.409854888916</v>
+        <v>12.4098539352417</v>
       </c>
       <c r="H761" t="n">
         <v>12308</v>
@@ -22467,7 +22467,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G762" t="n">
-        <v>12.1241016387939</v>
+        <v>12.1241025924683</v>
       </c>
       <c r="H762" t="n">
         <v>9512</v>
@@ -22496,7 +22496,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G763" t="n">
-        <v>12.50510597229</v>
+        <v>12.5051050186157</v>
       </c>
       <c r="H763" t="n">
         <v>8786</v>
@@ -22525,7 +22525,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G764" t="n">
-        <v>12.7364282608032</v>
+        <v>12.7364311218262</v>
       </c>
       <c r="H764" t="n">
         <v>3194</v>
@@ -22583,7 +22583,7 @@
         <v>19.5</v>
       </c>
       <c r="G766" t="n">
-        <v>13.2671146392822</v>
+        <v>13.2671136856079</v>
       </c>
       <c r="H766" t="n">
         <v>2748</v>
@@ -22612,7 +22612,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G767" t="n">
-        <v>13.2535066604614</v>
+        <v>13.2535057067871</v>
       </c>
       <c r="H767" t="n">
         <v>7585</v>
@@ -22641,7 +22641,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>13.063006401062</v>
+        <v>13.0630054473877</v>
       </c>
       <c r="H768" t="n">
         <v>10243</v>
@@ -22670,7 +22670,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G769" t="n">
-        <v>12.9949684143066</v>
+        <v>12.994969367981</v>
       </c>
       <c r="H769" t="n">
         <v>1967</v>
@@ -22728,7 +22728,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G771" t="n">
-        <v>13.0085763931274</v>
+        <v>13.0085754394531</v>
       </c>
       <c r="H771" t="n">
         <v>8938</v>
@@ -22757,7 +22757,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G772" t="n">
-        <v>12.9405393600464</v>
+        <v>12.9405384063721</v>
       </c>
       <c r="H772" t="n">
         <v>7124</v>
@@ -22786,7 +22786,7 @@
         <v>19</v>
       </c>
       <c r="G773" t="n">
-        <v>12.9269323348999</v>
+        <v>12.9269313812256</v>
       </c>
       <c r="H773" t="n">
         <v>5860</v>
@@ -22844,7 +22844,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G775" t="n">
-        <v>13.307936668396</v>
+        <v>13.3079357147217</v>
       </c>
       <c r="H775" t="n">
         <v>31745</v>
@@ -22873,7 +22873,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G776" t="n">
-        <v>13.2535066604614</v>
+        <v>13.2535057067871</v>
       </c>
       <c r="H776" t="n">
         <v>14674</v>
@@ -22902,7 +22902,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>13.063006401062</v>
+        <v>13.0630054473877</v>
       </c>
       <c r="H777" t="n">
         <v>15881</v>
@@ -22931,7 +22931,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G778" t="n">
-        <v>13.2398996353149</v>
+        <v>13.2399005889893</v>
       </c>
       <c r="H778" t="n">
         <v>12951</v>
@@ -22960,7 +22960,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G779" t="n">
-        <v>13.2943286895752</v>
+        <v>13.2943315505981</v>
       </c>
       <c r="H779" t="n">
         <v>11175</v>
@@ -23018,7 +23018,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G781" t="n">
-        <v>13.40318775177</v>
+        <v>13.4031887054443</v>
       </c>
       <c r="H781" t="n">
         <v>15004</v>
@@ -23047,7 +23047,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G782" t="n">
-        <v>13.3895826339722</v>
+        <v>13.3895816802979</v>
       </c>
       <c r="H782" t="n">
         <v>18293</v>
@@ -23076,7 +23076,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G783" t="n">
-        <v>13.3623638153076</v>
+        <v>13.3623647689819</v>
       </c>
       <c r="H783" t="n">
         <v>3220</v>
@@ -23105,7 +23105,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G784" t="n">
-        <v>13.335150718689</v>
+        <v>13.3351516723633</v>
       </c>
       <c r="H784" t="n">
         <v>6776</v>
@@ -23163,7 +23163,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G786" t="n">
-        <v>13.2262935638428</v>
+        <v>13.2262945175171</v>
       </c>
       <c r="H786" t="n">
         <v>125814</v>
@@ -23221,7 +23221,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G788" t="n">
-        <v>13.7093505859375</v>
+        <v>13.7093515396118</v>
       </c>
       <c r="H788" t="n">
         <v>29299</v>
@@ -23250,7 +23250,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>13.8114051818848</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H789" t="n">
         <v>11021</v>
@@ -23279,7 +23279,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G790" t="n">
-        <v>13.5528688430786</v>
+        <v>13.5528659820557</v>
       </c>
       <c r="H790" t="n">
         <v>9686</v>
@@ -23308,7 +23308,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G791" t="n">
-        <v>13.40318775177</v>
+        <v>13.4031887054443</v>
       </c>
       <c r="H791" t="n">
         <v>4527</v>
@@ -23337,7 +23337,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G792" t="n">
-        <v>13.4440097808838</v>
+        <v>13.4440078735352</v>
       </c>
       <c r="H792" t="n">
         <v>8314</v>
@@ -23395,7 +23395,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G794" t="n">
-        <v>13.5256538391113</v>
+        <v>13.525652885437</v>
       </c>
       <c r="H794" t="n">
         <v>16042</v>
@@ -23424,7 +23424,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G795" t="n">
-        <v>13.5256538391113</v>
+        <v>13.525652885437</v>
       </c>
       <c r="H795" t="n">
         <v>6107</v>
@@ -23453,7 +23453,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G796" t="n">
-        <v>13.8114051818848</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H796" t="n">
         <v>15602</v>
@@ -23482,7 +23482,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>13.7093505859375</v>
+        <v>13.7093515396118</v>
       </c>
       <c r="H797" t="n">
         <v>10680</v>
@@ -23569,7 +23569,7 @@
         <v>20</v>
       </c>
       <c r="G800" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072959899902</v>
       </c>
       <c r="H800" t="n">
         <v>16793</v>
@@ -23598,7 +23598,7 @@
         <v>20</v>
       </c>
       <c r="G801" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072959899902</v>
       </c>
       <c r="H801" t="n">
         <v>5455</v>
@@ -23627,7 +23627,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G802" t="n">
-        <v>13.5528688430786</v>
+        <v>13.5528659820557</v>
       </c>
       <c r="H802" t="n">
         <v>9311</v>
@@ -23714,7 +23714,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G805" t="n">
-        <v>13.7093505859375</v>
+        <v>13.7093515396118</v>
       </c>
       <c r="H805" t="n">
         <v>16584</v>
@@ -23743,7 +23743,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>13.6413154602051</v>
+        <v>13.6413145065308</v>
       </c>
       <c r="H806" t="n">
         <v>26645</v>
@@ -23772,7 +23772,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G807" t="n">
-        <v>13.5800809860229</v>
+        <v>13.5800828933716</v>
       </c>
       <c r="H807" t="n">
         <v>15665</v>
@@ -23859,7 +23859,7 @@
         <v>20.5</v>
       </c>
       <c r="G810" t="n">
-        <v>13.9474792480469</v>
+        <v>13.9474782943726</v>
       </c>
       <c r="H810" t="n">
         <v>106638</v>
@@ -23888,7 +23888,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G811" t="n">
-        <v>13.8114051818848</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H811" t="n">
         <v>14418</v>
@@ -23946,7 +23946,7 @@
         <v>20</v>
       </c>
       <c r="G813" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072959899902</v>
       </c>
       <c r="H813" t="n">
         <v>6595</v>
@@ -24004,7 +24004,7 @@
         <v>20</v>
       </c>
       <c r="G815" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072959899902</v>
       </c>
       <c r="H815" t="n">
         <v>5510</v>
@@ -24091,7 +24091,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>13.9814987182617</v>
+        <v>13.9814958572388</v>
       </c>
       <c r="H818" t="n">
         <v>23978</v>
@@ -24120,7 +24120,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>14.0155153274536</v>
+        <v>14.0155162811279</v>
       </c>
       <c r="H819" t="n">
         <v>17236</v>
@@ -24149,7 +24149,7 @@
         <v>20.5</v>
       </c>
       <c r="G820" t="n">
-        <v>13.9474792480469</v>
+        <v>13.9474782943726</v>
       </c>
       <c r="H820" t="n">
         <v>16940</v>
@@ -24323,7 +24323,7 @@
         <v>20.25</v>
       </c>
       <c r="G826" t="n">
-        <v>13.7773866653442</v>
+        <v>13.7773885726929</v>
       </c>
       <c r="H826" t="n">
         <v>24955</v>
@@ -24352,7 +24352,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>13.8114051818848</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H827" t="n">
         <v>10700</v>
@@ -24381,7 +24381,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>13.8114051818848</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H828" t="n">
         <v>31017</v>
@@ -24410,7 +24410,7 @@
         <v>20.25</v>
       </c>
       <c r="G829" t="n">
-        <v>13.7773866653442</v>
+        <v>13.7773885726929</v>
       </c>
       <c r="H829" t="n">
         <v>21941</v>
@@ -24439,7 +24439,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G830" t="n">
-        <v>13.8114051818848</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H830" t="n">
         <v>50936</v>
@@ -24468,7 +24468,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>13.8114051818848</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H831" t="n">
         <v>30207</v>
@@ -24526,7 +24526,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>13.8114051818848</v>
+        <v>13.8114070892334</v>
       </c>
       <c r="H833" t="n">
         <v>11899</v>
@@ -24584,7 +24584,7 @@
         <v>20.25</v>
       </c>
       <c r="G835" t="n">
-        <v>13.7773866653442</v>
+        <v>13.7773885726929</v>
       </c>
       <c r="H835" t="n">
         <v>24738</v>
@@ -24613,7 +24613,7 @@
         <v>20.25</v>
       </c>
       <c r="G836" t="n">
-        <v>13.7773866653442</v>
+        <v>13.7773885726929</v>
       </c>
       <c r="H836" t="n">
         <v>38572</v>
@@ -24671,7 +24671,7 @@
         <v>20.25</v>
       </c>
       <c r="G838" t="n">
-        <v>13.7773866653442</v>
+        <v>13.7773885726929</v>
       </c>
       <c r="H838" t="n">
         <v>5571</v>
@@ -24700,7 +24700,7 @@
         <v>20.25</v>
       </c>
       <c r="G839" t="n">
-        <v>13.7773866653442</v>
+        <v>13.7773885726929</v>
       </c>
       <c r="H839" t="n">
         <v>6746</v>
@@ -24729,7 +24729,7 @@
         <v>20.25</v>
       </c>
       <c r="G840" t="n">
-        <v>13.7773866653442</v>
+        <v>13.7773885726929</v>
       </c>
       <c r="H840" t="n">
         <v>10762</v>
@@ -24758,7 +24758,7 @@
         <v>20</v>
       </c>
       <c r="G841" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072959899902</v>
       </c>
       <c r="H841" t="n">
         <v>13567</v>
@@ -24787,7 +24787,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G842" t="n">
-        <v>13.2535066604614</v>
+        <v>13.2535057067871</v>
       </c>
       <c r="H842" t="n">
         <v>15876</v>
@@ -24816,7 +24816,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G843" t="n">
-        <v>13.335150718689</v>
+        <v>13.3351516723633</v>
       </c>
       <c r="H843" t="n">
         <v>5599</v>
@@ -24845,7 +24845,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G844" t="n">
-        <v>13.3215456008911</v>
+        <v>13.3215417861938</v>
       </c>
       <c r="H844" t="n">
         <v>4444</v>
@@ -24874,7 +24874,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G845" t="n">
-        <v>13.5664749145508</v>
+        <v>13.5664777755737</v>
       </c>
       <c r="H845" t="n">
         <v>16030</v>
@@ -24932,7 +24932,7 @@
         <v>20</v>
       </c>
       <c r="G847" t="n">
-        <v>13.6072978973389</v>
+        <v>13.6072959899902</v>
       </c>
       <c r="H847" t="n">
         <v>13458</v>
@@ -24990,7 +24990,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G849" t="n">
-        <v>13.684253692627</v>
+        <v>13.6842517852783</v>
       </c>
       <c r="H849" t="n">
         <v>13350</v>
@@ -25019,7 +25019,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G850" t="n">
-        <v>13.4184036254883</v>
+        <v>13.4184017181396</v>
       </c>
       <c r="H850" t="n">
         <v>26546</v>
@@ -25048,7 +25048,7 @@
         <v>19.5</v>
       </c>
       <c r="G851" t="n">
-        <v>13.642276763916</v>
+        <v>13.6422758102417</v>
       </c>
       <c r="H851" t="n">
         <v>10949</v>
@@ -25077,7 +25077,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G852" t="n">
-        <v>13.4603776931763</v>
+        <v>13.4603796005249</v>
       </c>
       <c r="H852" t="n">
         <v>13295</v>
@@ -25106,7 +25106,7 @@
         <v>19.5</v>
       </c>
       <c r="G853" t="n">
-        <v>13.642276763916</v>
+        <v>13.6422758102417</v>
       </c>
       <c r="H853" t="n">
         <v>8207</v>
@@ -25135,7 +25135,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G854" t="n">
-        <v>13.670262336731</v>
+        <v>13.6702604293823</v>
       </c>
       <c r="H854" t="n">
         <v>14808</v>
@@ -25164,7 +25164,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G855" t="n">
-        <v>13.894136428833</v>
+        <v>13.8941354751587</v>
       </c>
       <c r="H855" t="n">
         <v>5140</v>
@@ -25193,7 +25193,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G856" t="n">
-        <v>13.7262296676636</v>
+        <v>13.7262287139893</v>
       </c>
       <c r="H856" t="n">
         <v>8169</v>
@@ -25222,7 +25222,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G857" t="n">
-        <v>13.8661499023438</v>
+        <v>13.8661518096924</v>
       </c>
       <c r="H857" t="n">
         <v>15139</v>
@@ -25280,7 +25280,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G859" t="n">
-        <v>13.922119140625</v>
+        <v>13.9221172332764</v>
       </c>
       <c r="H859" t="n">
         <v>7532</v>
@@ -25309,7 +25309,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G860" t="n">
-        <v>13.8101835250854</v>
+        <v>13.8101816177368</v>
       </c>
       <c r="H860" t="n">
         <v>4321</v>
@@ -25338,7 +25338,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G861" t="n">
-        <v>13.8661499023438</v>
+        <v>13.8661518096924</v>
       </c>
       <c r="H861" t="n">
         <v>5548</v>
@@ -25367,7 +25367,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G862" t="n">
-        <v>13.7961912155151</v>
+        <v>13.7961902618408</v>
       </c>
       <c r="H862" t="n">
         <v>9967</v>
@@ -25396,7 +25396,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G863" t="n">
-        <v>13.9640922546387</v>
+        <v>13.9640951156616</v>
       </c>
       <c r="H863" t="n">
         <v>5481</v>
@@ -25425,7 +25425,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G864" t="n">
-        <v>13.8521575927734</v>
+        <v>13.8521585464478</v>
       </c>
       <c r="H864" t="n">
         <v>2178</v>
@@ -25454,7 +25454,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>14.1320009231567</v>
+        <v>14.1319999694824</v>
       </c>
       <c r="H865" t="n">
         <v>10277</v>
@@ -25483,7 +25483,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G866" t="n">
-        <v>13.8801431655884</v>
+        <v>13.8801403045654</v>
       </c>
       <c r="H866" t="n">
         <v>3916</v>
@@ -25512,7 +25512,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>13.922119140625</v>
+        <v>13.9221172332764</v>
       </c>
       <c r="H867" t="n">
         <v>2044</v>
@@ -25541,7 +25541,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G868" t="n">
-        <v>13.7262296676636</v>
+        <v>13.7262287139893</v>
       </c>
       <c r="H868" t="n">
         <v>20868</v>
@@ -25570,7 +25570,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G869" t="n">
-        <v>13.8101835250854</v>
+        <v>13.8101816177368</v>
       </c>
       <c r="H869" t="n">
         <v>5018</v>
@@ -25599,7 +25599,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G870" t="n">
-        <v>13.8101835250854</v>
+        <v>13.8101816177368</v>
       </c>
       <c r="H870" t="n">
         <v>6508</v>
@@ -25628,7 +25628,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G871" t="n">
-        <v>13.9640922546387</v>
+        <v>13.9640951156616</v>
       </c>
       <c r="H871" t="n">
         <v>3700</v>
@@ -25657,7 +25657,7 @@
         <v>19.5</v>
       </c>
       <c r="G872" t="n">
-        <v>13.642276763916</v>
+        <v>13.6422758102417</v>
       </c>
       <c r="H872" t="n">
         <v>6317</v>
@@ -25715,7 +25715,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G874" t="n">
-        <v>14.1320009231567</v>
+        <v>14.1319999694824</v>
       </c>
       <c r="H874" t="n">
         <v>27460</v>
@@ -25744,7 +25744,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G875" t="n">
-        <v>14.0620412826538</v>
+        <v>14.0620403289795</v>
       </c>
       <c r="H875" t="n">
         <v>19379</v>
@@ -25773,7 +25773,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G876" t="n">
-        <v>14.1320009231567</v>
+        <v>14.1319999694824</v>
       </c>
       <c r="H876" t="n">
         <v>9837</v>
@@ -25802,7 +25802,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G877" t="n">
-        <v>14.2719211578369</v>
+        <v>14.2719221115112</v>
       </c>
       <c r="H877" t="n">
         <v>16414</v>
@@ -25831,7 +25831,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>14.4118432998657</v>
+        <v>14.4118404388428</v>
       </c>
       <c r="H878" t="n">
         <v>158753</v>
@@ -25889,7 +25889,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G880" t="n">
-        <v>14.6217193603516</v>
+        <v>14.6217212677002</v>
       </c>
       <c r="H880" t="n">
         <v>33155</v>
@@ -25918,7 +25918,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G881" t="n">
-        <v>14.8316020965576</v>
+        <v>14.8316030502319</v>
       </c>
       <c r="H881" t="n">
         <v>25688</v>
@@ -25947,7 +25947,7 @@
         <v>21.25</v>
       </c>
       <c r="G882" t="n">
-        <v>14.866584777832</v>
+        <v>14.8665828704834</v>
       </c>
       <c r="H882" t="n">
         <v>15416</v>
@@ -25976,7 +25976,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G883" t="n">
-        <v>14.7616424560547</v>
+        <v>14.761643409729</v>
       </c>
       <c r="H883" t="n">
         <v>15829</v>
@@ -26005,7 +26005,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G884" t="n">
-        <v>14.6567029953003</v>
+        <v>14.656702041626</v>
       </c>
       <c r="H884" t="n">
         <v>26708</v>
@@ -26034,7 +26034,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G885" t="n">
-        <v>14.7266645431519</v>
+        <v>14.7266607284546</v>
       </c>
       <c r="H885" t="n">
         <v>11371</v>
@@ -26063,7 +26063,7 @@
         <v>21.25</v>
       </c>
       <c r="G886" t="n">
-        <v>14.866584777832</v>
+        <v>14.8665828704834</v>
       </c>
       <c r="H886" t="n">
         <v>15383</v>
@@ -26092,7 +26092,7 @@
         <v>21.25</v>
       </c>
       <c r="G887" t="n">
-        <v>14.866584777832</v>
+        <v>14.8665828704834</v>
       </c>
       <c r="H887" t="n">
         <v>4743</v>
@@ -26121,7 +26121,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>14.8316020965576</v>
+        <v>14.8316030502319</v>
       </c>
       <c r="H888" t="n">
         <v>15671</v>
@@ -26150,7 +26150,7 @@
         <v>21</v>
       </c>
       <c r="G889" t="n">
-        <v>14.6916828155518</v>
+        <v>14.6916837692261</v>
       </c>
       <c r="H889" t="n">
         <v>15824</v>
@@ -26179,7 +26179,7 @@
         <v>21</v>
       </c>
       <c r="G890" t="n">
-        <v>14.6916828155518</v>
+        <v>14.6916837692261</v>
       </c>
       <c r="H890" t="n">
         <v>16965</v>
@@ -26208,7 +26208,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>14.6217193603516</v>
+        <v>14.6217212677002</v>
       </c>
       <c r="H891" t="n">
         <v>14506</v>
@@ -26237,7 +26237,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G892" t="n">
-        <v>15.0764646530151</v>
+        <v>15.0764656066895</v>
       </c>
       <c r="H892" t="n">
         <v>21330</v>
@@ -26266,7 +26266,7 @@
         <v>21</v>
       </c>
       <c r="G893" t="n">
-        <v>14.6916828155518</v>
+        <v>14.6916837692261</v>
       </c>
       <c r="H893" t="n">
         <v>24090</v>
@@ -26295,7 +26295,7 @@
         <v>21</v>
       </c>
       <c r="G894" t="n">
-        <v>14.6916828155518</v>
+        <v>14.6916837692261</v>
       </c>
       <c r="H894" t="n">
         <v>11147</v>
@@ -26324,7 +26324,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G895" t="n">
-        <v>14.6217193603516</v>
+        <v>14.6217212677002</v>
       </c>
       <c r="H895" t="n">
         <v>19533</v>
@@ -26353,7 +26353,7 @@
         <v>21</v>
       </c>
       <c r="G896" t="n">
-        <v>14.6916828155518</v>
+        <v>14.6916837692261</v>
       </c>
       <c r="H896" t="n">
         <v>15147</v>
@@ -26382,7 +26382,7 @@
         <v>21</v>
       </c>
       <c r="G897" t="n">
-        <v>14.6916828155518</v>
+        <v>14.6916837692261</v>
       </c>
       <c r="H897" t="n">
         <v>9946</v>
@@ -26411,7 +26411,7 @@
         <v>21</v>
       </c>
       <c r="G898" t="n">
-        <v>14.6916828155518</v>
+        <v>14.6916837692261</v>
       </c>
       <c r="H898" t="n">
         <v>8292</v>
@@ -26440,7 +26440,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>14.6567029953003</v>
+        <v>14.656702041626</v>
       </c>
       <c r="H899" t="n">
         <v>13435</v>
@@ -26469,7 +26469,7 @@
         <v>21</v>
       </c>
       <c r="G900" t="n">
-        <v>14.6916828155518</v>
+        <v>14.6916837692261</v>
       </c>
       <c r="H900" t="n">
         <v>21947</v>
@@ -26498,7 +26498,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>14.4818029403687</v>
+        <v>14.4818019866943</v>
       </c>
       <c r="H901" t="n">
         <v>18262</v>
@@ -26556,7 +26556,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G903" t="n">
-        <v>14.3768615722656</v>
+        <v>14.3768606185913</v>
       </c>
       <c r="H903" t="n">
         <v>9049</v>
@@ -26585,7 +26585,7 @@
         <v>20.25</v>
       </c>
       <c r="G904" t="n">
-        <v>14.1669788360596</v>
+        <v>14.1669816970825</v>
       </c>
       <c r="H904" t="n">
         <v>12420</v>
@@ -26614,7 +26614,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G905" t="n">
-        <v>14.2719211578369</v>
+        <v>14.2719221115112</v>
       </c>
       <c r="H905" t="n">
         <v>5262</v>
@@ -26643,7 +26643,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>14.4468212127686</v>
+        <v>14.4468202590942</v>
       </c>
       <c r="H906" t="n">
         <v>6387</v>
@@ -26672,7 +26672,7 @@
         <v>20.25</v>
       </c>
       <c r="G907" t="n">
-        <v>14.1669788360596</v>
+        <v>14.1669816970825</v>
       </c>
       <c r="H907" t="n">
         <v>6128</v>
@@ -26701,7 +26701,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>14.4118432998657</v>
+        <v>14.4118404388428</v>
       </c>
       <c r="H908" t="n">
         <v>5747</v>
@@ -26730,7 +26730,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G909" t="n">
-        <v>14.4118432998657</v>
+        <v>14.4118404388428</v>
       </c>
       <c r="H909" t="n">
         <v>3405</v>
@@ -26759,7 +26759,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G910" t="n">
-        <v>14.0270566940308</v>
+        <v>14.0270576477051</v>
       </c>
       <c r="H910" t="n">
         <v>12652</v>
@@ -26788,7 +26788,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>14.1320009231567</v>
+        <v>14.1319999694824</v>
       </c>
       <c r="H911" t="n">
         <v>11043</v>
@@ -26817,7 +26817,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>14.201958656311</v>
+        <v>14.2019596099854</v>
       </c>
       <c r="H912" t="n">
         <v>9184</v>
@@ -26846,7 +26846,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G913" t="n">
-        <v>14.2719211578369</v>
+        <v>14.2719221115112</v>
       </c>
       <c r="H913" t="n">
         <v>5414</v>
@@ -26904,7 +26904,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>13.8521575927734</v>
+        <v>13.8521585464478</v>
       </c>
       <c r="H915" t="n">
         <v>9137</v>
@@ -26933,7 +26933,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G916" t="n">
-        <v>13.7262296676636</v>
+        <v>13.7262287139893</v>
       </c>
       <c r="H916" t="n">
         <v>10493</v>
@@ -26962,7 +26962,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G917" t="n">
-        <v>13.8241748809814</v>
+        <v>13.8241758346558</v>
       </c>
       <c r="H917" t="n">
         <v>8650</v>
@@ -26991,7 +26991,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G918" t="n">
-        <v>13.8661499023438</v>
+        <v>13.8661518096924</v>
       </c>
       <c r="H918" t="n">
         <v>19771</v>
@@ -27020,7 +27020,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G919" t="n">
-        <v>13.7821989059448</v>
+        <v>13.7821979522705</v>
       </c>
       <c r="H919" t="n">
         <v>6109</v>
@@ -27049,7 +27049,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G920" t="n">
-        <v>13.7262296676636</v>
+        <v>13.7262287139893</v>
       </c>
       <c r="H920" t="n">
         <v>9249</v>
@@ -27078,7 +27078,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G921" t="n">
-        <v>13.7961912155151</v>
+        <v>13.7961902618408</v>
       </c>
       <c r="H921" t="n">
         <v>8281</v>
@@ -27136,7 +27136,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G923" t="n">
-        <v>13.9081258773804</v>
+        <v>13.9081239700317</v>
       </c>
       <c r="H923" t="n">
         <v>5734</v>
@@ -27165,7 +27165,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G924" t="n">
-        <v>13.8661499023438</v>
+        <v>13.8661518096924</v>
       </c>
       <c r="H924" t="n">
         <v>11795</v>
@@ -27194,7 +27194,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G925" t="n">
-        <v>14.0270566940308</v>
+        <v>14.0270576477051</v>
       </c>
       <c r="H925" t="n">
         <v>4003</v>
@@ -27223,7 +27223,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G926" t="n">
-        <v>14.2719211578369</v>
+        <v>14.2719221115112</v>
       </c>
       <c r="H926" t="n">
         <v>6761</v>
@@ -27252,7 +27252,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G927" t="n">
-        <v>14.0620412826538</v>
+        <v>14.0620403289795</v>
       </c>
       <c r="H927" t="n">
         <v>3457</v>
@@ -27281,7 +27281,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G928" t="n">
-        <v>14.2719211578369</v>
+        <v>14.2719221115112</v>
       </c>
       <c r="H928" t="n">
         <v>9814</v>
@@ -27310,7 +27310,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>14.4818029403687</v>
+        <v>14.4818019866943</v>
       </c>
       <c r="H929" t="n">
         <v>17664</v>
@@ -27339,7 +27339,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G930" t="n">
-        <v>14.2369403839111</v>
+        <v>14.2369413375854</v>
       </c>
       <c r="H930" t="n">
         <v>7343</v>
@@ -27368,7 +27368,7 @@
         <v>20.25</v>
       </c>
       <c r="G931" t="n">
-        <v>14.1669788360596</v>
+        <v>14.1669816970825</v>
       </c>
       <c r="H931" t="n">
         <v>7780</v>
@@ -27426,7 +27426,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G933" t="n">
-        <v>14.1320009231567</v>
+        <v>14.1319999694824</v>
       </c>
       <c r="H933" t="n">
         <v>5244</v>
@@ -27455,7 +27455,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>14.0270566940308</v>
+        <v>14.0270576477051</v>
       </c>
       <c r="H934" t="n">
         <v>4511</v>
@@ -27484,7 +27484,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>14.201958656311</v>
+        <v>14.2019596099854</v>
       </c>
       <c r="H935" t="n">
         <v>7086</v>
@@ -27542,7 +27542,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G937" t="n">
-        <v>14.4118432998657</v>
+        <v>14.4118404388428</v>
       </c>
       <c r="H937" t="n">
         <v>14949</v>
@@ -27571,7 +27571,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>14.4818029403687</v>
+        <v>14.4818019866943</v>
       </c>
       <c r="H938" t="n">
         <v>7568</v>
@@ -27629,7 +27629,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>14.3768615722656</v>
+        <v>14.3768606185913</v>
       </c>
       <c r="H940" t="n">
         <v>8028</v>
@@ -27658,7 +27658,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G941" t="n">
-        <v>14.4468212127686</v>
+        <v>14.4468202590942</v>
       </c>
       <c r="H941" t="n">
         <v>6621</v>
@@ -27687,7 +27687,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>14.6217193603516</v>
+        <v>14.6217212677002</v>
       </c>
       <c r="H942" t="n">
         <v>24928</v>
@@ -27745,7 +27745,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G944" t="n">
-        <v>14.6567029953003</v>
+        <v>14.656702041626</v>
       </c>
       <c r="H944" t="n">
         <v>23422</v>
@@ -27774,7 +27774,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G945" t="n">
-        <v>14.6567029953003</v>
+        <v>14.656702041626</v>
       </c>
       <c r="H945" t="n">
         <v>19421</v>
@@ -27803,7 +27803,7 @@
         <v>21</v>
       </c>
       <c r="G946" t="n">
-        <v>14.6916828155518</v>
+        <v>14.6916837692261</v>
       </c>
       <c r="H946" t="n">
         <v>5859</v>
@@ -27832,7 +27832,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G947" t="n">
-        <v>14.4818029403687</v>
+        <v>14.4818019866943</v>
       </c>
       <c r="H947" t="n">
         <v>145981</v>
@@ -27861,7 +27861,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G948" t="n">
-        <v>14.6567029953003</v>
+        <v>14.656702041626</v>
       </c>
       <c r="H948" t="n">
         <v>31458</v>
@@ -27890,7 +27890,7 @@
         <v>21</v>
       </c>
       <c r="G949" t="n">
-        <v>14.6916828155518</v>
+        <v>14.6916837692261</v>
       </c>
       <c r="H949" t="n">
         <v>32568</v>
@@ -27919,7 +27919,7 @@
         <v>21</v>
       </c>
       <c r="G950" t="n">
-        <v>14.6916828155518</v>
+        <v>14.6916837692261</v>
       </c>
       <c r="H950" t="n">
         <v>21137</v>
@@ -27948,7 +27948,7 @@
         <v>21</v>
       </c>
       <c r="G951" t="n">
-        <v>14.6916828155518</v>
+        <v>14.6916837692261</v>
       </c>
       <c r="H951" t="n">
         <v>110845</v>
@@ -27977,7 +27977,7 @@
         <v>21</v>
       </c>
       <c r="G952" t="n">
-        <v>14.6916828155518</v>
+        <v>14.6916837692261</v>
       </c>
       <c r="H952" t="n">
         <v>104164</v>
@@ -28006,7 +28006,7 @@
         <v>21</v>
       </c>
       <c r="G953" t="n">
-        <v>14.6916828155518</v>
+        <v>14.6916837692261</v>
       </c>
       <c r="H953" t="n">
         <v>65243</v>
@@ -28035,7 +28035,7 @@
         <v>21</v>
       </c>
       <c r="G954" t="n">
-        <v>14.6916828155518</v>
+        <v>14.6916837692261</v>
       </c>
       <c r="H954" t="n">
         <v>49144</v>
@@ -28064,7 +28064,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>14.6217193603516</v>
+        <v>14.6217212677002</v>
       </c>
       <c r="H955" t="n">
         <v>37345</v>
@@ -28093,7 +28093,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G956" t="n">
-        <v>14.7266645431519</v>
+        <v>14.7266607284546</v>
       </c>
       <c r="H956" t="n">
         <v>25526</v>
@@ -28122,7 +28122,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>15.4262657165527</v>
+        <v>15.4262666702271</v>
       </c>
       <c r="H957" t="n">
         <v>45112</v>
@@ -28180,7 +28180,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G959" t="n">
-        <v>15.881007194519</v>
+        <v>15.881010055542</v>
       </c>
       <c r="H959" t="n">
         <v>39374</v>
@@ -28209,7 +28209,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G960" t="n">
-        <v>15.881007194519</v>
+        <v>15.881010055542</v>
       </c>
       <c r="H960" t="n">
         <v>24953</v>
@@ -28238,7 +28238,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G961" t="n">
-        <v>15.9859523773193</v>
+        <v>15.9859495162964</v>
       </c>
       <c r="H961" t="n">
         <v>12635</v>
@@ -28267,7 +28267,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G962" t="n">
-        <v>15.9859523773193</v>
+        <v>15.9859495162964</v>
       </c>
       <c r="H962" t="n">
         <v>15922</v>
@@ -28296,7 +28296,7 @@
         <v>22.75</v>
       </c>
       <c r="G963" t="n">
-        <v>15.9159889221191</v>
+        <v>15.9159908294678</v>
       </c>
       <c r="H963" t="n">
         <v>20269</v>
@@ -28383,7 +28383,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>16.0209274291992</v>
+        <v>16.0209312438965</v>
       </c>
       <c r="H966" t="n">
         <v>9102</v>
@@ -28412,7 +28412,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>15.950966835022</v>
+        <v>15.9509716033936</v>
       </c>
       <c r="H967" t="n">
         <v>22609</v>
@@ -28499,7 +28499,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G970" t="n">
-        <v>16.4057121276855</v>
+        <v>16.4057140350342</v>
       </c>
       <c r="H970" t="n">
         <v>20690</v>
@@ -28528,7 +28528,7 @@
         <v>23.5</v>
       </c>
       <c r="G971" t="n">
-        <v>16.44069480896</v>
+        <v>16.4406929016113</v>
       </c>
       <c r="H971" t="n">
         <v>13705</v>
@@ -28557,7 +28557,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G972" t="n">
-        <v>16.4057121276855</v>
+        <v>16.4057140350342</v>
       </c>
       <c r="H972" t="n">
         <v>12423</v>
@@ -28586,7 +28586,7 @@
         <v>23.5</v>
       </c>
       <c r="G973" t="n">
-        <v>16.44069480896</v>
+        <v>16.4406929016113</v>
       </c>
       <c r="H973" t="n">
         <v>12724</v>
@@ -28644,7 +28644,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>16.7555141448975</v>
+        <v>16.7555160522461</v>
       </c>
       <c r="H975" t="n">
         <v>10843</v>
@@ -28673,7 +28673,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G976" t="n">
-        <v>16.7555141448975</v>
+        <v>16.7555160522461</v>
       </c>
       <c r="H976" t="n">
         <v>9811</v>
@@ -28731,7 +28731,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>16.8604545593262</v>
+        <v>16.8604564666748</v>
       </c>
       <c r="H978" t="n">
         <v>25207</v>
@@ -28760,7 +28760,7 @@
         <v>24.5</v>
       </c>
       <c r="G979" t="n">
-        <v>17.1402950286865</v>
+        <v>17.1402969360352</v>
       </c>
       <c r="H979" t="n">
         <v>21063</v>
@@ -28789,7 +28789,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>17.0703353881836</v>
+        <v>17.0703372955322</v>
       </c>
       <c r="H980" t="n">
         <v>21811</v>
@@ -28847,7 +28847,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>17.0353546142578</v>
+        <v>17.0353584289551</v>
       </c>
       <c r="H982" t="n">
         <v>69410</v>
@@ -28905,7 +28905,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G984" t="n">
-        <v>17.385160446167</v>
+        <v>17.3851585388184</v>
       </c>
       <c r="H984" t="n">
         <v>47012</v>
@@ -28934,7 +28934,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G985" t="n">
-        <v>17.385160446167</v>
+        <v>17.3851585388184</v>
       </c>
       <c r="H985" t="n">
         <v>19876</v>
@@ -28963,7 +28963,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G986" t="n">
-        <v>17.2452392578125</v>
+        <v>17.2452373504639</v>
       </c>
       <c r="H986" t="n">
         <v>23257</v>
@@ -28992,7 +28992,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G987" t="n">
-        <v>17.4201393127441</v>
+        <v>17.4201374053955</v>
       </c>
       <c r="H987" t="n">
         <v>23686</v>
@@ -29021,7 +29021,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G988" t="n">
-        <v>17.4201393127441</v>
+        <v>17.4201374053955</v>
       </c>
       <c r="H988" t="n">
         <v>21263</v>
@@ -29108,7 +29108,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>17.2452392578125</v>
+        <v>17.2452373504639</v>
       </c>
       <c r="H991" t="n">
         <v>18313</v>
@@ -29166,7 +29166,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G993" t="n">
-        <v>17.3501758575439</v>
+        <v>17.3501777648926</v>
       </c>
       <c r="H993" t="n">
         <v>9273</v>
@@ -29224,7 +29224,7 @@
         <v>25.25</v>
       </c>
       <c r="G995" t="n">
-        <v>17.6649990081787</v>
+        <v>17.6650009155273</v>
       </c>
       <c r="H995" t="n">
         <v>39713</v>
@@ -29340,7 +29340,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G999" t="n">
-        <v>17.3501758575439</v>
+        <v>17.3501777648926</v>
       </c>
       <c r="H999" t="n">
         <v>26553</v>
@@ -29398,7 +29398,7 @@
         <v>24.75</v>
       </c>
       <c r="G1001" t="n">
-        <v>17.3151988983154</v>
+        <v>17.3151969909668</v>
       </c>
       <c r="H1001" t="n">
         <v>20638</v>
@@ -29427,7 +29427,7 @@
         <v>24.75</v>
       </c>
       <c r="G1002" t="n">
-        <v>17.3151988983154</v>
+        <v>17.3151969909668</v>
       </c>
       <c r="H1002" t="n">
         <v>23234</v>
@@ -29485,7 +29485,7 @@
         <v>25.25</v>
       </c>
       <c r="G1004" t="n">
-        <v>17.6649990081787</v>
+        <v>17.6650009155273</v>
       </c>
       <c r="H1004" t="n">
         <v>9043</v>
@@ -29543,7 +29543,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1006" t="n">
-        <v>17.3501758575439</v>
+        <v>17.3501777648926</v>
       </c>
       <c r="H1006" t="n">
         <v>11381</v>
@@ -29572,7 +29572,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1007" t="n">
-        <v>17.4201393127441</v>
+        <v>17.4201374053955</v>
       </c>
       <c r="H1007" t="n">
         <v>25227</v>
@@ -29601,7 +29601,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1008" t="n">
-        <v>17.385160446167</v>
+        <v>17.3851585388184</v>
       </c>
       <c r="H1008" t="n">
         <v>16919</v>
@@ -29630,7 +29630,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.385160446167</v>
+        <v>17.3851585388184</v>
       </c>
       <c r="H1009" t="n">
         <v>17124</v>
@@ -29688,7 +29688,7 @@
         <v>24.5</v>
       </c>
       <c r="G1011" t="n">
-        <v>17.1402950286865</v>
+        <v>17.1402969360352</v>
       </c>
       <c r="H1011" t="n">
         <v>17553</v>
@@ -29746,7 +29746,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G1013" t="n">
-        <v>17.0353546142578</v>
+        <v>17.0353584289551</v>
       </c>
       <c r="H1013" t="n">
         <v>16480</v>
@@ -29775,7 +29775,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1014" t="n">
-        <v>17.0703353881836</v>
+        <v>17.0703372955322</v>
       </c>
       <c r="H1014" t="n">
         <v>14042</v>
@@ -29891,7 +29891,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1018" t="n">
-        <v>16.9304161071777</v>
+        <v>16.9304141998291</v>
       </c>
       <c r="H1018" t="n">
         <v>22376</v>
@@ -29920,7 +29920,7 @@
         <v>24</v>
       </c>
       <c r="G1019" t="n">
-        <v>16.7904949188232</v>
+        <v>16.7904930114746</v>
       </c>
       <c r="H1019" t="n">
         <v>7005</v>
@@ -29949,7 +29949,7 @@
         <v>24</v>
       </c>
       <c r="G1020" t="n">
-        <v>16.7904949188232</v>
+        <v>16.7904930114746</v>
       </c>
       <c r="H1020" t="n">
         <v>13900</v>
@@ -29978,7 +29978,7 @@
         <v>24.5</v>
       </c>
       <c r="G1021" t="n">
-        <v>17.1402950286865</v>
+        <v>17.1402969360352</v>
       </c>
       <c r="H1021" t="n">
         <v>11905</v>
@@ -30036,7 +30036,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1023" t="n">
-        <v>16.9304161071777</v>
+        <v>16.9304141998291</v>
       </c>
       <c r="H1023" t="n">
         <v>10741</v>
@@ -30065,7 +30065,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>17.3501758575439</v>
+        <v>17.3501777648926</v>
       </c>
       <c r="H1024" t="n">
         <v>44398</v>
@@ -30152,7 +30152,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1027" t="n">
-        <v>17.385160446167</v>
+        <v>17.3851585388184</v>
       </c>
       <c r="H1027" t="n">
         <v>16578</v>
@@ -30181,7 +30181,7 @@
         <v>25.25</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.6649990081787</v>
+        <v>17.6650009155273</v>
       </c>
       <c r="H1028" t="n">
         <v>14286</v>
@@ -30297,7 +30297,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G1032" t="n">
-        <v>17.5250759124756</v>
+        <v>17.5250797271729</v>
       </c>
       <c r="H1032" t="n">
         <v>21061</v>
@@ -30326,7 +30326,7 @@
         <v>24.75</v>
       </c>
       <c r="G1033" t="n">
-        <v>17.3151988983154</v>
+        <v>17.3151969909668</v>
       </c>
       <c r="H1033" t="n">
         <v>17018</v>
@@ -30355,7 +30355,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G1034" t="n">
-        <v>17.5250759124756</v>
+        <v>17.5250797271729</v>
       </c>
       <c r="H1034" t="n">
         <v>9904</v>
@@ -30471,7 +30471,7 @@
         <v>25.25</v>
       </c>
       <c r="G1038" t="n">
-        <v>17.6649990081787</v>
+        <v>17.6650009155273</v>
       </c>
       <c r="H1038" t="n">
         <v>20154</v>
@@ -30616,7 +30616,7 @@
         <v>25.25</v>
       </c>
       <c r="G1043" t="n">
-        <v>17.6649990081787</v>
+        <v>17.6650009155273</v>
       </c>
       <c r="H1043" t="n">
         <v>12047</v>
@@ -30732,7 +30732,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>18.1197395324707</v>
+        <v>18.1197414398193</v>
       </c>
       <c r="H1047" t="n">
         <v>16122</v>
@@ -30761,7 +30761,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>18.4695434570312</v>
+        <v>18.4695415496826</v>
       </c>
       <c r="H1048" t="n">
         <v>20726</v>
@@ -30790,7 +30790,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1049" t="n">
-        <v>18.2596626281738</v>
+        <v>18.2596645355225</v>
       </c>
       <c r="H1049" t="n">
         <v>12352</v>
@@ -30819,7 +30819,7 @@
         <v>26.25</v>
       </c>
       <c r="G1050" t="n">
-        <v>18.3646030426025</v>
+        <v>18.3646049499512</v>
       </c>
       <c r="H1050" t="n">
         <v>7131</v>
@@ -30848,7 +30848,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1051" t="n">
-        <v>18.4695434570312</v>
+        <v>18.4695415496826</v>
       </c>
       <c r="H1051" t="n">
         <v>15126</v>
@@ -30877,7 +30877,7 @@
         <v>26.5</v>
       </c>
       <c r="G1052" t="n">
-        <v>18.5395069122314</v>
+        <v>18.5395030975342</v>
       </c>
       <c r="H1052" t="n">
         <v>95237</v>
@@ -30906,7 +30906,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1053" t="n">
-        <v>18.2596626281738</v>
+        <v>18.2596645355225</v>
       </c>
       <c r="H1053" t="n">
         <v>69984</v>
@@ -30935,7 +30935,7 @@
         <v>26.5</v>
       </c>
       <c r="G1054" t="n">
-        <v>18.5395069122314</v>
+        <v>18.5395030975342</v>
       </c>
       <c r="H1054" t="n">
         <v>174844</v>
@@ -30964,7 +30964,7 @@
         <v>26.5</v>
       </c>
       <c r="G1055" t="n">
-        <v>18.5395069122314</v>
+        <v>18.5395030975342</v>
       </c>
       <c r="H1055" t="n">
         <v>80338</v>
@@ -30993,7 +30993,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1056" t="n">
-        <v>18.399585723877</v>
+        <v>18.3995838165283</v>
       </c>
       <c r="H1056" t="n">
         <v>101511</v>
@@ -31022,7 +31022,7 @@
         <v>26.25</v>
       </c>
       <c r="G1057" t="n">
-        <v>18.3646030426025</v>
+        <v>18.3646049499512</v>
       </c>
       <c r="H1057" t="n">
         <v>105093</v>
@@ -31051,7 +31051,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G1058" t="n">
-        <v>18.5744857788086</v>
+        <v>18.5744819641113</v>
       </c>
       <c r="H1058" t="n">
         <v>83258</v>
@@ -31080,7 +31080,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1059" t="n">
-        <v>18.6794242858887</v>
+        <v>18.6794261932373</v>
       </c>
       <c r="H1059" t="n">
         <v>42775</v>
@@ -31109,7 +31109,7 @@
         <v>26.5</v>
       </c>
       <c r="G1060" t="n">
-        <v>18.5395069122314</v>
+        <v>18.5395030975342</v>
       </c>
       <c r="H1060" t="n">
         <v>52754</v>
@@ -31138,7 +31138,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>18.6794242858887</v>
+        <v>18.6794261932373</v>
       </c>
       <c r="H1061" t="n">
         <v>97139</v>
@@ -31167,7 +31167,7 @@
         <v>26.75</v>
       </c>
       <c r="G1062" t="n">
-        <v>18.7144069671631</v>
+        <v>18.7144050598145</v>
       </c>
       <c r="H1062" t="n">
         <v>86723</v>
@@ -31196,7 +31196,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1063" t="n">
-        <v>17.385160446167</v>
+        <v>17.3851585388184</v>
       </c>
       <c r="H1063" t="n">
         <v>79195</v>
@@ -31283,7 +31283,7 @@
         <v>23.25</v>
       </c>
       <c r="G1066" t="n">
-        <v>16.2657890319824</v>
+        <v>16.2657909393311</v>
       </c>
       <c r="H1066" t="n">
         <v>85994</v>
@@ -31341,7 +31341,7 @@
         <v>23</v>
       </c>
       <c r="G1068" t="n">
-        <v>16.0908889770508</v>
+        <v>16.0908908843994</v>
       </c>
       <c r="H1068" t="n">
         <v>64503</v>
@@ -31602,7 +31602,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1077" t="n">
-        <v>16.8604545593262</v>
+        <v>16.8604564666748</v>
       </c>
       <c r="H1077" t="n">
         <v>69626</v>
@@ -31631,7 +31631,7 @@
         <v>24</v>
       </c>
       <c r="G1078" t="n">
-        <v>16.7904949188232</v>
+        <v>16.7904930114746</v>
       </c>
       <c r="H1078" t="n">
         <v>46364</v>
@@ -31718,7 +31718,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G1081" t="n">
-        <v>18.0847625732422</v>
+        <v>18.0847644805908</v>
       </c>
       <c r="H1081" t="n">
         <v>24410</v>
@@ -31747,7 +31747,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>17.385160446167</v>
+        <v>17.3851585388184</v>
       </c>
       <c r="H1082" t="n">
         <v>24535</v>
@@ -31776,7 +31776,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G1083" t="n">
-        <v>17.5250759124756</v>
+        <v>17.5250797271729</v>
       </c>
       <c r="H1083" t="n">
         <v>25482</v>
@@ -31805,7 +31805,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G1084" t="n">
-        <v>17.5250759124756</v>
+        <v>17.5250797271729</v>
       </c>
       <c r="H1084" t="n">
         <v>31658</v>
@@ -31834,7 +31834,7 @@
         <v>25.5</v>
       </c>
       <c r="G1085" t="n">
-        <v>17.8398990631104</v>
+        <v>17.839900970459</v>
       </c>
       <c r="H1085" t="n">
         <v>7385</v>
@@ -31892,7 +31892,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>18.399585723877</v>
+        <v>18.3995838165283</v>
       </c>
       <c r="H1087" t="n">
         <v>40969</v>
@@ -31921,7 +31921,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>18.2596626281738</v>
+        <v>18.2596645355225</v>
       </c>
       <c r="H1088" t="n">
         <v>17580</v>
@@ -31950,7 +31950,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1089" t="n">
-        <v>18.399585723877</v>
+        <v>18.3995838165283</v>
       </c>
       <c r="H1089" t="n">
         <v>25851</v>
@@ -31979,7 +31979,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>18.4695434570312</v>
+        <v>18.4695415496826</v>
       </c>
       <c r="H1090" t="n">
         <v>20804</v>
@@ -32008,7 +32008,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G1091" t="n">
-        <v>18.5744857788086</v>
+        <v>18.5744819641113</v>
       </c>
       <c r="H1091" t="n">
         <v>18874</v>
@@ -32037,7 +32037,7 @@
         <v>26</v>
       </c>
       <c r="G1092" t="n">
-        <v>18.1897010803223</v>
+        <v>18.1897029876709</v>
       </c>
       <c r="H1092" t="n">
         <v>35575</v>
@@ -32066,7 +32066,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1093" t="n">
-        <v>18.399585723877</v>
+        <v>18.3995838165283</v>
       </c>
       <c r="H1093" t="n">
         <v>11658</v>
@@ -32095,7 +32095,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1094" t="n">
-        <v>18.399585723877</v>
+        <v>18.3995838165283</v>
       </c>
       <c r="H1094" t="n">
         <v>31171</v>
@@ -32124,7 +32124,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1095" t="n">
-        <v>18.4695434570312</v>
+        <v>18.4695415496826</v>
       </c>
       <c r="H1095" t="n">
         <v>13834</v>
@@ -32153,7 +32153,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>18.0847625732422</v>
+        <v>18.0847644805908</v>
       </c>
       <c r="H1096" t="n">
         <v>22352</v>
@@ -32211,7 +32211,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1098" t="n">
-        <v>18.399585723877</v>
+        <v>18.3995838165283</v>
       </c>
       <c r="H1098" t="n">
         <v>13051</v>
@@ -32240,7 +32240,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1099" t="n">
-        <v>19.0991859436035</v>
+        <v>19.0991878509521</v>
       </c>
       <c r="H1099" t="n">
         <v>54184</v>
@@ -32269,7 +32269,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1100" t="n">
-        <v>18.6872463226318</v>
+        <v>18.6872444152832</v>
       </c>
       <c r="H1100" t="n">
         <v>18796</v>
@@ -32385,7 +32385,7 @@
         <v>25.25</v>
       </c>
       <c r="G1104" t="n">
-        <v>18.9119396209717</v>
+        <v>18.9119415283203</v>
       </c>
       <c r="H1104" t="n">
         <v>15864</v>
@@ -32443,7 +32443,7 @@
         <v>25.5</v>
       </c>
       <c r="G1106" t="n">
-        <v>19.0991859436035</v>
+        <v>19.0991878509521</v>
       </c>
       <c r="H1106" t="n">
         <v>16490</v>
@@ -32501,7 +32501,7 @@
         <v>25.5</v>
       </c>
       <c r="G1108" t="n">
-        <v>19.0991859436035</v>
+        <v>19.0991878509521</v>
       </c>
       <c r="H1108" t="n">
         <v>15191</v>
@@ -32588,7 +32588,7 @@
         <v>25</v>
       </c>
       <c r="G1111" t="n">
-        <v>18.7246932983398</v>
+        <v>18.7246952056885</v>
       </c>
       <c r="H1111" t="n">
         <v>17961</v>
@@ -32617,7 +32617,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1112" t="n">
-        <v>18.6123485565186</v>
+        <v>18.6123466491699</v>
       </c>
       <c r="H1112" t="n">
         <v>8584</v>
@@ -32646,7 +32646,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>18.6123485565186</v>
+        <v>18.6123466491699</v>
       </c>
       <c r="H1113" t="n">
         <v>15089</v>
@@ -32675,7 +32675,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1114" t="n">
-        <v>18.574893951416</v>
+        <v>18.5748958587646</v>
       </c>
       <c r="H1114" t="n">
         <v>21829</v>
@@ -32733,7 +32733,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>19.2115364074707</v>
+        <v>19.2115345001221</v>
       </c>
       <c r="H1116" t="n">
         <v>14443</v>
@@ -32762,7 +32762,7 @@
         <v>24.75</v>
       </c>
       <c r="G1117" t="n">
-        <v>18.5374488830566</v>
+        <v>18.5374450683594</v>
       </c>
       <c r="H1117" t="n">
         <v>43716</v>
@@ -32849,7 +32849,7 @@
         <v>25.25</v>
       </c>
       <c r="G1120" t="n">
-        <v>18.9119396209717</v>
+        <v>18.9119415283203</v>
       </c>
       <c r="H1120" t="n">
         <v>36223</v>
@@ -32994,7 +32994,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1125" t="n">
-        <v>20.2601165771484</v>
+        <v>20.2601184844971</v>
       </c>
       <c r="H1125" t="n">
         <v>14815</v>
@@ -33023,7 +33023,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1126" t="n">
-        <v>20.1477699279785</v>
+        <v>20.1477718353271</v>
       </c>
       <c r="H1126" t="n">
         <v>20762</v>
@@ -33052,7 +33052,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>20.4848155975342</v>
+        <v>20.4848175048828</v>
       </c>
       <c r="H1127" t="n">
         <v>43114</v>
@@ -33168,7 +33168,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>20.2975673675537</v>
+        <v>20.2975692749023</v>
       </c>
       <c r="H1131" t="n">
         <v>12677</v>
@@ -33226,7 +33226,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>20.9342079162598</v>
+        <v>20.9342098236084</v>
       </c>
       <c r="H1133" t="n">
         <v>22670</v>
@@ -33284,7 +33284,7 @@
         <v>27.75</v>
       </c>
       <c r="G1135" t="n">
-        <v>20.7844104766846</v>
+        <v>20.7844085693359</v>
       </c>
       <c r="H1135" t="n">
         <v>9441</v>
@@ -33371,7 +33371,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1138" t="n">
-        <v>21.1963520050049</v>
+        <v>21.1963539123535</v>
       </c>
       <c r="H1138" t="n">
         <v>27473</v>
@@ -33400,7 +33400,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1139" t="n">
-        <v>21.2338047027588</v>
+        <v>21.2338027954102</v>
       </c>
       <c r="H1139" t="n">
         <v>14535</v>
@@ -33429,7 +33429,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1140" t="n">
-        <v>21.6831951141357</v>
+        <v>21.6831970214844</v>
       </c>
       <c r="H1140" t="n">
         <v>14646</v>
@@ -33487,7 +33487,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1142" t="n">
-        <v>21.7955436706543</v>
+        <v>21.7955455780029</v>
       </c>
       <c r="H1142" t="n">
         <v>12883</v>
@@ -33574,7 +33574,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1145" t="n">
-        <v>21.8704433441162</v>
+        <v>21.8704452514648</v>
       </c>
       <c r="H1145" t="n">
         <v>17737</v>
@@ -33603,7 +33603,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1146" t="n">
-        <v>21.7955436706543</v>
+        <v>21.7955455780029</v>
       </c>
       <c r="H1146" t="n">
         <v>19945</v>
@@ -33661,7 +33661,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1148" t="n">
-        <v>21.421049118042</v>
+        <v>21.4210510253906</v>
       </c>
       <c r="H1148" t="n">
         <v>13756</v>
@@ -33690,7 +33690,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>22.6194305419922</v>
+        <v>22.6194324493408</v>
       </c>
       <c r="H1149" t="n">
         <v>36662</v>
@@ -33748,7 +33748,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1151" t="n">
-        <v>23.4807682037354</v>
+        <v>23.4807662963867</v>
       </c>
       <c r="H1151" t="n">
         <v>15873</v>
@@ -33806,7 +33806,7 @@
         <v>31.75</v>
       </c>
       <c r="G1153" t="n">
-        <v>23.7803592681885</v>
+        <v>23.7803611755371</v>
       </c>
       <c r="H1153" t="n">
         <v>9750</v>
@@ -33835,7 +33835,7 @@
         <v>31.5</v>
       </c>
       <c r="G1154" t="n">
-        <v>23.5931129455566</v>
+        <v>23.5931148529053</v>
       </c>
       <c r="H1154" t="n">
         <v>16443</v>
@@ -33864,7 +33864,7 @@
         <v>32.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>24.3421039581299</v>
+        <v>24.3421020507812</v>
       </c>
       <c r="H1155" t="n">
         <v>17553</v>
@@ -33893,7 +33893,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G1156" t="n">
-        <v>23.8552589416504</v>
+        <v>23.855260848999</v>
       </c>
       <c r="H1156" t="n">
         <v>13909</v>
@@ -33980,7 +33980,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1159" t="n">
-        <v>23.7054615020752</v>
+        <v>23.7054634094238</v>
       </c>
       <c r="H1159" t="n">
         <v>14360</v>
@@ -34038,7 +34038,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1161" t="n">
-        <v>23.1062717437744</v>
+        <v>23.106273651123</v>
       </c>
       <c r="H1161" t="n">
         <v>10738</v>
@@ -34067,7 +34067,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G1162" t="n">
-        <v>22.2074851989746</v>
+        <v>22.2074871063232</v>
       </c>
       <c r="H1162" t="n">
         <v>32954</v>
@@ -34241,7 +34241,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>22.5819797515869</v>
+        <v>22.5819816589355</v>
       </c>
       <c r="H1168" t="n">
         <v>37622</v>
@@ -34299,7 +34299,7 @@
         <v>29.75</v>
       </c>
       <c r="G1170" t="n">
-        <v>22.2823848724365</v>
+        <v>22.2823867797852</v>
       </c>
       <c r="H1170" t="n">
         <v>13565</v>
@@ -34415,7 +34415,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.9190273284912</v>
+        <v>22.9190254211426</v>
       </c>
       <c r="H1174" t="n">
         <v>6446</v>
@@ -34444,7 +34444,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.7692279815674</v>
+        <v>22.7692260742188</v>
       </c>
       <c r="H1175" t="n">
         <v>11655</v>
@@ -34560,7 +34560,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1179" t="n">
-        <v>22.5445308685303</v>
+        <v>22.5445327758789</v>
       </c>
       <c r="H1179" t="n">
         <v>15545</v>
@@ -34676,7 +34676,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G1183" t="n">
-        <v>23.1062717437744</v>
+        <v>23.106273651123</v>
       </c>
       <c r="H1183" t="n">
         <v>7270</v>
@@ -34705,7 +34705,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>22.7692279815674</v>
+        <v>22.7692260742188</v>
       </c>
       <c r="H1184" t="n">
         <v>6570</v>
@@ -34763,7 +34763,7 @@
         <v>30.0499992370605</v>
       </c>
       <c r="G1186" t="n">
-        <v>22.507080078125</v>
+        <v>22.5070819854736</v>
       </c>
       <c r="H1186" t="n">
         <v>7733</v>
@@ -34850,7 +34850,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1189" t="n">
-        <v>22.13258934021</v>
+        <v>22.1325874328613</v>
       </c>
       <c r="H1189" t="n">
         <v>12240</v>
@@ -34937,7 +34937,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1192" t="n">
-        <v>22.5445308685303</v>
+        <v>22.5445327758789</v>
       </c>
       <c r="H1192" t="n">
         <v>6644</v>
@@ -34966,7 +34966,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>22.6194305419922</v>
+        <v>22.6194324493408</v>
       </c>
       <c r="H1193" t="n">
         <v>10195</v>
@@ -35024,7 +35024,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>22.6194305419922</v>
+        <v>22.6194324493408</v>
       </c>
       <c r="H1195" t="n">
         <v>6917</v>
@@ -35053,7 +35053,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1196" t="n">
-        <v>22.7317771911621</v>
+        <v>22.7317790985107</v>
       </c>
       <c r="H1196" t="n">
         <v>13834</v>
@@ -35082,7 +35082,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1197" t="n">
-        <v>22.6194305419922</v>
+        <v>22.6194324493408</v>
       </c>
       <c r="H1197" t="n">
         <v>11913</v>
@@ -35140,7 +35140,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1199" t="n">
-        <v>20.9342079162598</v>
+        <v>20.9342098236084</v>
       </c>
       <c r="H1199" t="n">
         <v>50937</v>
@@ -35227,7 +35227,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1202" t="n">
-        <v>21.6457443237305</v>
+        <v>21.6457462310791</v>
       </c>
       <c r="H1202" t="n">
         <v>11100</v>
@@ -35285,7 +35285,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1204" t="n">
-        <v>20.9342079162598</v>
+        <v>20.9342098236084</v>
       </c>
       <c r="H1204" t="n">
         <v>8904</v>
@@ -35343,7 +35343,7 @@
         <v>28.75</v>
       </c>
       <c r="G1206" t="n">
-        <v>21.5333957672119</v>
+        <v>21.5333976745605</v>
       </c>
       <c r="H1206" t="n">
         <v>7439</v>
@@ -35459,7 +35459,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G1210" t="n">
-        <v>22.0576915740967</v>
+        <v>22.057689666748</v>
       </c>
       <c r="H1210" t="n">
         <v>11771</v>
@@ -35488,7 +35488,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1211" t="n">
-        <v>21.6831951141357</v>
+        <v>21.6831970214844</v>
       </c>
       <c r="H1211" t="n">
         <v>8455</v>
@@ -35691,7 +35691,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1218" t="n">
-        <v>21.3836002349854</v>
+        <v>21.3835964202881</v>
       </c>
       <c r="H1218" t="n">
         <v>8191</v>
@@ -35720,7 +35720,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>21.6457443237305</v>
+        <v>21.6457462310791</v>
       </c>
       <c r="H1219" t="n">
         <v>9570</v>
@@ -35807,7 +35807,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1222" t="n">
-        <v>21.084005355835</v>
+        <v>21.0840072631836</v>
       </c>
       <c r="H1222" t="n">
         <v>9777</v>
@@ -35865,7 +35865,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1224" t="n">
-        <v>20.672061920166</v>
+        <v>20.6720600128174</v>
       </c>
       <c r="H1224" t="n">
         <v>16150</v>
@@ -35981,7 +35981,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1228" t="n">
-        <v>20.7095127105713</v>
+        <v>20.7095108032227</v>
       </c>
       <c r="H1228" t="n">
         <v>6987</v>
@@ -36010,7 +36010,7 @@
         <v>27.75</v>
       </c>
       <c r="G1229" t="n">
-        <v>20.7844104766846</v>
+        <v>20.7844085693359</v>
       </c>
       <c r="H1229" t="n">
         <v>6884</v>
@@ -36039,7 +36039,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>20.672061920166</v>
+        <v>20.6720600128174</v>
       </c>
       <c r="H1230" t="n">
         <v>7519</v>
@@ -36097,7 +36097,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1232" t="n">
-        <v>20.8967590332031</v>
+        <v>20.8967571258545</v>
       </c>
       <c r="H1232" t="n">
         <v>3171</v>
@@ -36184,7 +36184,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1235" t="n">
-        <v>20.9342079162598</v>
+        <v>20.9342098236084</v>
       </c>
       <c r="H1235" t="n">
         <v>46736</v>
@@ -36213,7 +36213,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1236" t="n">
-        <v>20.4473628997803</v>
+        <v>20.4473648071289</v>
       </c>
       <c r="H1236" t="n">
         <v>10958</v>
@@ -36300,7 +36300,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1239" t="n">
-        <v>20.7095127105713</v>
+        <v>20.7095108032227</v>
       </c>
       <c r="H1239" t="n">
         <v>6479</v>
@@ -36329,7 +36329,7 @@
         <v>27.75</v>
       </c>
       <c r="G1240" t="n">
-        <v>20.7844104766846</v>
+        <v>20.7844085693359</v>
       </c>
       <c r="H1240" t="n">
         <v>23095</v>
@@ -36387,7 +36387,7 @@
         <v>27.75</v>
       </c>
       <c r="G1242" t="n">
-        <v>20.7844104766846</v>
+        <v>20.7844085693359</v>
       </c>
       <c r="H1242" t="n">
         <v>13595</v>
@@ -36445,7 +36445,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1244" t="n">
-        <v>20.8593082427979</v>
+        <v>20.8593101501465</v>
       </c>
       <c r="H1244" t="n">
         <v>15972</v>
@@ -36532,7 +36532,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>21.3836002349854</v>
+        <v>21.3835964202881</v>
       </c>
       <c r="H1247" t="n">
         <v>13992</v>
@@ -36619,7 +36619,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1250" t="n">
-        <v>21.1963520050049</v>
+        <v>21.1963539123535</v>
       </c>
       <c r="H1250" t="n">
         <v>24364</v>
@@ -36648,7 +36648,7 @@
         <v>28.75</v>
       </c>
       <c r="G1251" t="n">
-        <v>21.5333957672119</v>
+        <v>21.5333976745605</v>
       </c>
       <c r="H1251" t="n">
         <v>13852</v>
@@ -36677,7 +36677,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1252" t="n">
-        <v>21.3836002349854</v>
+        <v>21.3835964202881</v>
       </c>
       <c r="H1252" t="n">
         <v>8324</v>
@@ -36706,7 +36706,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1253" t="n">
-        <v>21.421049118042</v>
+        <v>21.4210510253906</v>
       </c>
       <c r="H1253" t="n">
         <v>11612</v>
@@ -36822,7 +36822,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1257" t="n">
-        <v>21.1963520050049</v>
+        <v>21.1963539123535</v>
       </c>
       <c r="H1257" t="n">
         <v>18057</v>
@@ -37054,7 +37054,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1265" t="n">
-        <v>21.421049118042</v>
+        <v>21.4210510253906</v>
       </c>
       <c r="H1265" t="n">
         <v>9193</v>
@@ -37170,7 +37170,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1269" t="n">
-        <v>22.0202388763428</v>
+        <v>22.0202407836914</v>
       </c>
       <c r="H1269" t="n">
         <v>12848</v>
@@ -37286,7 +37286,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1273" t="n">
-        <v>21.7955436706543</v>
+        <v>21.7955455780029</v>
       </c>
       <c r="H1273" t="n">
         <v>10578</v>
@@ -37315,7 +37315,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1274" t="n">
-        <v>21.8704433441162</v>
+        <v>21.8704452514648</v>
       </c>
       <c r="H1274" t="n">
         <v>18498</v>
@@ -37402,7 +37402,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>21.7955436706543</v>
+        <v>21.7955455780029</v>
       </c>
       <c r="H1277" t="n">
         <v>7121</v>
@@ -37489,7 +37489,7 @@
         <v>28.75</v>
       </c>
       <c r="G1280" t="n">
-        <v>21.5333957672119</v>
+        <v>21.5333976745605</v>
       </c>
       <c r="H1280" t="n">
         <v>11073</v>
@@ -37518,7 +37518,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1281" t="n">
-        <v>21.8704433441162</v>
+        <v>21.8704452514648</v>
       </c>
       <c r="H1281" t="n">
         <v>20649</v>
@@ -37634,7 +37634,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1285" t="n">
-        <v>21.084005355835</v>
+        <v>21.0840072631836</v>
       </c>
       <c r="H1285" t="n">
         <v>8297</v>
@@ -37663,7 +37663,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>20.5222625732422</v>
+        <v>20.5222644805908</v>
       </c>
       <c r="H1286" t="n">
         <v>9991</v>
@@ -37692,7 +37692,7 @@
         <v>27.75</v>
       </c>
       <c r="G1287" t="n">
-        <v>20.7844104766846</v>
+        <v>20.7844085693359</v>
       </c>
       <c r="H1287" t="n">
         <v>9863</v>
@@ -37721,7 +37721,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1288" t="n">
-        <v>20.4473628997803</v>
+        <v>20.4473648071289</v>
       </c>
       <c r="H1288" t="n">
         <v>16811</v>
@@ -37837,7 +37837,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1292" t="n">
-        <v>20.8967590332031</v>
+        <v>20.8967571258545</v>
       </c>
       <c r="H1292" t="n">
         <v>4853</v>
@@ -37866,7 +37866,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1293" t="n">
-        <v>21.2338047027588</v>
+        <v>21.2338027954102</v>
       </c>
       <c r="H1293" t="n">
         <v>16505</v>
@@ -37953,7 +37953,7 @@
         <v>28.75</v>
       </c>
       <c r="G1296" t="n">
-        <v>21.5333957672119</v>
+        <v>21.5333976745605</v>
       </c>
       <c r="H1296" t="n">
         <v>12935</v>
@@ -37982,7 +37982,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1297" t="n">
-        <v>21.2338047027588</v>
+        <v>21.2338027954102</v>
       </c>
       <c r="H1297" t="n">
         <v>18554</v>
@@ -38040,7 +38040,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1299" t="n">
-        <v>21.084005355835</v>
+        <v>21.0840072631836</v>
       </c>
       <c r="H1299" t="n">
         <v>7612</v>
@@ -38069,7 +38069,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1300" t="n">
-        <v>21.2338047027588</v>
+        <v>21.2338027954102</v>
       </c>
       <c r="H1300" t="n">
         <v>12673</v>
@@ -38098,7 +38098,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1301" t="n">
-        <v>21.3836002349854</v>
+        <v>21.3835964202881</v>
       </c>
       <c r="H1301" t="n">
         <v>27906</v>
@@ -38156,7 +38156,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G1303" t="n">
-        <v>20.8593082427979</v>
+        <v>20.8593101501465</v>
       </c>
       <c r="H1303" t="n">
         <v>6711</v>
@@ -38214,7 +38214,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1305" t="n">
-        <v>20.5222625732422</v>
+        <v>20.5222644805908</v>
       </c>
       <c r="H1305" t="n">
         <v>19337</v>
@@ -38359,7 +38359,7 @@
         <v>26.5</v>
       </c>
       <c r="G1310" t="n">
-        <v>19.8481769561768</v>
+        <v>19.8481750488281</v>
       </c>
       <c r="H1310" t="n">
         <v>11852</v>
@@ -38504,7 +38504,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1315" t="n">
-        <v>21.084005355835</v>
+        <v>21.0840072631836</v>
       </c>
       <c r="H1315" t="n">
         <v>26559</v>
@@ -38562,7 +38562,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>21.7955436706543</v>
+        <v>21.7955455780029</v>
       </c>
       <c r="H1317" t="n">
         <v>35843</v>
@@ -38591,7 +38591,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1318" t="n">
-        <v>21.7955436706543</v>
+        <v>21.7955455780029</v>
       </c>
       <c r="H1318" t="n">
         <v>12862</v>
@@ -38620,7 +38620,7 @@
         <v>29.75</v>
       </c>
       <c r="G1319" t="n">
-        <v>22.2823848724365</v>
+        <v>22.2823867797852</v>
       </c>
       <c r="H1319" t="n">
         <v>23741</v>
@@ -38736,7 +38736,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>21.7955436706543</v>
+        <v>21.7955455780029</v>
       </c>
       <c r="H1323" t="n">
         <v>13749</v>
@@ -38794,7 +38794,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1325" t="n">
-        <v>21.2338047027588</v>
+        <v>21.2338027954102</v>
       </c>
       <c r="H1325" t="n">
         <v>26912</v>
@@ -38881,7 +38881,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>21.421049118042</v>
+        <v>21.4210510253906</v>
       </c>
       <c r="H1328" t="n">
         <v>9270</v>
@@ -38910,7 +38910,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1329" t="n">
-        <v>21.6457443237305</v>
+        <v>21.6457462310791</v>
       </c>
       <c r="H1329" t="n">
         <v>15467</v>
@@ -38968,7 +38968,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1331" t="n">
-        <v>21.8704433441162</v>
+        <v>21.8704452514648</v>
       </c>
       <c r="H1331" t="n">
         <v>14592</v>
@@ -39055,7 +39055,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1334" t="n">
-        <v>21.6457443237305</v>
+        <v>21.6457462310791</v>
       </c>
       <c r="H1334" t="n">
         <v>16389</v>
@@ -39084,7 +39084,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1335" t="n">
-        <v>22.13258934021</v>
+        <v>22.1325874328613</v>
       </c>
       <c r="H1335" t="n">
         <v>35511</v>
@@ -39113,7 +39113,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1336" t="n">
-        <v>21.6457443237305</v>
+        <v>21.6457462310791</v>
       </c>
       <c r="H1336" t="n">
         <v>77604</v>
@@ -39316,7 +39316,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1343" t="n">
-        <v>21.6457443237305</v>
+        <v>21.6457462310791</v>
       </c>
       <c r="H1343" t="n">
         <v>11646</v>
@@ -39374,7 +39374,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1345" t="n">
-        <v>21.8704433441162</v>
+        <v>21.8704452514648</v>
       </c>
       <c r="H1345" t="n">
         <v>54826</v>
@@ -39403,7 +39403,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1346" t="n">
-        <v>22.0202388763428</v>
+        <v>22.0202407836914</v>
       </c>
       <c r="H1346" t="n">
         <v>14000</v>
@@ -39519,7 +39519,7 @@
         <v>28.75</v>
       </c>
       <c r="G1350" t="n">
-        <v>21.5333957672119</v>
+        <v>21.5333976745605</v>
       </c>
       <c r="H1350" t="n">
         <v>19884</v>
@@ -39577,7 +39577,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1352" t="n">
-        <v>21.8704433441162</v>
+        <v>21.8704452514648</v>
       </c>
       <c r="H1352" t="n">
         <v>34037</v>
@@ -39722,7 +39722,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1357" t="n">
-        <v>21.8653793334961</v>
+        <v>21.8653774261475</v>
       </c>
       <c r="H1357" t="n">
         <v>13413</v>
@@ -39867,7 +39867,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1362" t="n">
-        <v>22.0951385498047</v>
+        <v>22.0951366424561</v>
       </c>
       <c r="H1362" t="n">
         <v>18518</v>
@@ -39954,7 +39954,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1365" t="n">
-        <v>22.133430480957</v>
+        <v>22.1334323883057</v>
       </c>
       <c r="H1365" t="n">
         <v>24277</v>
@@ -40012,7 +40012,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1367" t="n">
-        <v>22.3248977661133</v>
+        <v>22.3248958587646</v>
       </c>
       <c r="H1367" t="n">
         <v>21365</v>
@@ -40099,7 +40099,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1370" t="n">
-        <v>22.2866058349609</v>
+        <v>22.2866039276123</v>
       </c>
       <c r="H1370" t="n">
         <v>33120</v>
@@ -40128,7 +40128,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1371" t="n">
-        <v>22.133430480957</v>
+        <v>22.1334323883057</v>
       </c>
       <c r="H1371" t="n">
         <v>23820</v>
@@ -40157,7 +40157,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1372" t="n">
-        <v>22.0951385498047</v>
+        <v>22.0951366424561</v>
       </c>
       <c r="H1372" t="n">
         <v>85484</v>
@@ -40215,7 +40215,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1374" t="n">
-        <v>23.0524654388428</v>
+        <v>23.0524673461914</v>
       </c>
       <c r="H1374" t="n">
         <v>35517</v>
@@ -40273,7 +40273,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1376" t="n">
-        <v>23.5119857788086</v>
+        <v>23.5119876861572</v>
       </c>
       <c r="H1376" t="n">
         <v>16374</v>
@@ -40418,7 +40418,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1381" t="n">
-        <v>23.2439308166504</v>
+        <v>23.243932723999</v>
       </c>
       <c r="H1381" t="n">
         <v>34865</v>
@@ -40447,7 +40447,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1382" t="n">
-        <v>23.2439308166504</v>
+        <v>23.243932723999</v>
       </c>
       <c r="H1382" t="n">
         <v>22281</v>
@@ -40476,7 +40476,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1383" t="n">
-        <v>23.5119857788086</v>
+        <v>23.5119876861572</v>
       </c>
       <c r="H1383" t="n">
         <v>14701</v>
@@ -40505,7 +40505,7 @@
         <v>31</v>
       </c>
       <c r="G1384" t="n">
-        <v>23.7417430877686</v>
+        <v>23.7417449951172</v>
       </c>
       <c r="H1384" t="n">
         <v>19760</v>
@@ -40534,7 +40534,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1385" t="n">
-        <v>23.9715003967285</v>
+        <v>23.9714984893799</v>
       </c>
       <c r="H1385" t="n">
         <v>17646</v>
@@ -40621,7 +40621,7 @@
         <v>30.5</v>
       </c>
       <c r="G1388" t="n">
-        <v>23.3588123321533</v>
+        <v>23.3588104248047</v>
       </c>
       <c r="H1388" t="n">
         <v>38453</v>
@@ -40708,7 +40708,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1391" t="n">
-        <v>23.0524654388428</v>
+        <v>23.0524673461914</v>
       </c>
       <c r="H1391" t="n">
         <v>10266</v>
@@ -40795,7 +40795,7 @@
         <v>30.75</v>
       </c>
       <c r="G1394" t="n">
-        <v>23.5502777099609</v>
+        <v>23.5502758026123</v>
       </c>
       <c r="H1394" t="n">
         <v>14754</v>
@@ -40824,7 +40824,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1395" t="n">
-        <v>23.5119857788086</v>
+        <v>23.5119876861572</v>
       </c>
       <c r="H1395" t="n">
         <v>20505</v>
@@ -40940,7 +40940,7 @@
         <v>30.75</v>
       </c>
       <c r="G1399" t="n">
-        <v>23.5502777099609</v>
+        <v>23.5502758026123</v>
       </c>
       <c r="H1399" t="n">
         <v>10140</v>
@@ -40969,7 +40969,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1400" t="n">
-        <v>23.4736919403076</v>
+        <v>23.4736881256104</v>
       </c>
       <c r="H1400" t="n">
         <v>5546</v>
@@ -41056,7 +41056,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1403" t="n">
-        <v>23.4736919403076</v>
+        <v>23.4736881256104</v>
       </c>
       <c r="H1403" t="n">
         <v>9151</v>
@@ -41143,7 +41143,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1406" t="n">
-        <v>23.7034511566162</v>
+        <v>23.7034492492676</v>
       </c>
       <c r="H1406" t="n">
         <v>9838</v>
@@ -41172,7 +41172,7 @@
         <v>31</v>
       </c>
       <c r="G1407" t="n">
-        <v>23.7417430877686</v>
+        <v>23.7417449951172</v>
       </c>
       <c r="H1407" t="n">
         <v>18522</v>
@@ -41201,7 +41201,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1408" t="n">
-        <v>23.4736919403076</v>
+        <v>23.4736881256104</v>
       </c>
       <c r="H1408" t="n">
         <v>17091</v>
@@ -41230,7 +41230,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1409" t="n">
-        <v>23.2439308166504</v>
+        <v>23.243932723999</v>
       </c>
       <c r="H1409" t="n">
         <v>30358</v>
@@ -41288,7 +41288,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1411" t="n">
-        <v>23.2822265625</v>
+        <v>23.2822246551514</v>
       </c>
       <c r="H1411" t="n">
         <v>10487</v>
@@ -41346,7 +41346,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1413" t="n">
-        <v>23.5119857788086</v>
+        <v>23.5119876861572</v>
       </c>
       <c r="H1413" t="n">
         <v>7011</v>
@@ -41404,7 +41404,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1415" t="n">
-        <v>23.5119857788086</v>
+        <v>23.5119876861572</v>
       </c>
       <c r="H1415" t="n">
         <v>8004</v>
@@ -41462,7 +41462,7 @@
         <v>31</v>
       </c>
       <c r="G1417" t="n">
-        <v>23.7417430877686</v>
+        <v>23.7417449951172</v>
       </c>
       <c r="H1417" t="n">
         <v>18491</v>
@@ -41636,7 +41636,7 @@
         <v>32</v>
       </c>
       <c r="G1423" t="n">
-        <v>24.507604598999</v>
+        <v>24.5076065063477</v>
       </c>
       <c r="H1423" t="n">
         <v>35196</v>
@@ -41665,7 +41665,7 @@
         <v>32.25</v>
       </c>
       <c r="G1424" t="n">
-        <v>24.6990718841553</v>
+        <v>24.6990699768066</v>
       </c>
       <c r="H1424" t="n">
         <v>7546</v>
@@ -41694,7 +41694,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1425" t="n">
-        <v>24.4310188293457</v>
+        <v>24.4310169219971</v>
       </c>
       <c r="H1425" t="n">
         <v>4760</v>
@@ -41723,7 +41723,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1426" t="n">
-        <v>24.4310188293457</v>
+        <v>24.4310169219971</v>
       </c>
       <c r="H1426" t="n">
         <v>6108</v>
@@ -41752,7 +41752,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>24.2395515441895</v>
+        <v>24.2395534515381</v>
       </c>
       <c r="H1427" t="n">
         <v>4709</v>
@@ -41810,7 +41810,7 @@
         <v>31.75</v>
       </c>
       <c r="G1429" t="n">
-        <v>24.3161392211914</v>
+        <v>24.31614112854</v>
       </c>
       <c r="H1429" t="n">
         <v>7344</v>
@@ -41839,7 +41839,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1430" t="n">
-        <v>23.9715003967285</v>
+        <v>23.9714984893799</v>
       </c>
       <c r="H1430" t="n">
         <v>13137</v>
@@ -41897,7 +41897,7 @@
         <v>31</v>
       </c>
       <c r="G1432" t="n">
-        <v>23.7417430877686</v>
+        <v>23.7417449951172</v>
       </c>
       <c r="H1432" t="n">
         <v>8154</v>
@@ -41955,7 +41955,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1434" t="n">
-        <v>23.9715003967285</v>
+        <v>23.9714984893799</v>
       </c>
       <c r="H1434" t="n">
         <v>4979</v>
@@ -41984,7 +41984,7 @@
         <v>30.75</v>
       </c>
       <c r="G1435" t="n">
-        <v>23.5502777099609</v>
+        <v>23.5502758026123</v>
       </c>
       <c r="H1435" t="n">
         <v>7464</v>
@@ -42071,7 +42071,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1438" t="n">
-        <v>23.7034511566162</v>
+        <v>23.7034492492676</v>
       </c>
       <c r="H1438" t="n">
         <v>2412</v>
@@ -42100,7 +42100,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1439" t="n">
-        <v>23.7034511566162</v>
+        <v>23.7034492492676</v>
       </c>
       <c r="H1439" t="n">
         <v>6551</v>
@@ -42129,7 +42129,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>23.5119857788086</v>
+        <v>23.5119876861572</v>
       </c>
       <c r="H1440" t="n">
         <v>16624</v>
@@ -42187,7 +42187,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1442" t="n">
-        <v>24.4310188293457</v>
+        <v>24.4310169219971</v>
       </c>
       <c r="H1442" t="n">
         <v>13608</v>
@@ -42216,7 +42216,7 @@
         <v>32.5</v>
       </c>
       <c r="G1443" t="n">
-        <v>24.8905391693115</v>
+        <v>24.8905372619629</v>
       </c>
       <c r="H1443" t="n">
         <v>22128</v>
@@ -42245,7 +42245,7 @@
         <v>32.25</v>
       </c>
       <c r="G1444" t="n">
-        <v>24.6990718841553</v>
+        <v>24.6990699768066</v>
       </c>
       <c r="H1444" t="n">
         <v>18843</v>
@@ -42274,7 +42274,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1445" t="n">
-        <v>24.4310188293457</v>
+        <v>24.4310169219971</v>
       </c>
       <c r="H1445" t="n">
         <v>12699</v>
@@ -42332,7 +42332,7 @@
         <v>31.5</v>
       </c>
       <c r="G1447" t="n">
-        <v>24.1246719360352</v>
+        <v>24.1246738433838</v>
       </c>
       <c r="H1447" t="n">
         <v>14322</v>
@@ -42390,7 +42390,7 @@
         <v>31.5</v>
       </c>
       <c r="G1449" t="n">
-        <v>24.1246719360352</v>
+        <v>24.1246738433838</v>
       </c>
       <c r="H1449" t="n">
         <v>20868</v>
@@ -42419,7 +42419,7 @@
         <v>31.5</v>
       </c>
       <c r="G1450" t="n">
-        <v>24.1246719360352</v>
+        <v>24.1246738433838</v>
       </c>
       <c r="H1450" t="n">
         <v>9047</v>
@@ -42448,7 +42448,7 @@
         <v>31.5</v>
       </c>
       <c r="G1451" t="n">
-        <v>24.1246719360352</v>
+        <v>24.1246738433838</v>
       </c>
       <c r="H1451" t="n">
         <v>7207</v>
@@ -42651,7 +42651,7 @@
         <v>31</v>
       </c>
       <c r="G1458" t="n">
-        <v>23.7417430877686</v>
+        <v>23.7417449951172</v>
       </c>
       <c r="H1458" t="n">
         <v>3143</v>
@@ -42680,7 +42680,7 @@
         <v>30.5</v>
       </c>
       <c r="G1459" t="n">
-        <v>23.3588123321533</v>
+        <v>23.3588104248047</v>
       </c>
       <c r="H1459" t="n">
         <v>6982</v>
@@ -42709,7 +42709,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1460" t="n">
-        <v>22.8610000610352</v>
+        <v>22.8610019683838</v>
       </c>
       <c r="H1460" t="n">
         <v>16025</v>
@@ -42999,7 +42999,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1470" t="n">
-        <v>23.2439308166504</v>
+        <v>23.243932723999</v>
       </c>
       <c r="H1470" t="n">
         <v>7864</v>
@@ -43028,7 +43028,7 @@
         <v>30.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>23.3588123321533</v>
+        <v>23.3588104248047</v>
       </c>
       <c r="H1471" t="n">
         <v>5788</v>
@@ -43086,7 +43086,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1473" t="n">
-        <v>23.4736919403076</v>
+        <v>23.4736881256104</v>
       </c>
       <c r="H1473" t="n">
         <v>6025</v>
@@ -43115,7 +43115,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1474" t="n">
-        <v>23.7034511566162</v>
+        <v>23.7034492492676</v>
       </c>
       <c r="H1474" t="n">
         <v>3047</v>
@@ -43144,7 +43144,7 @@
         <v>31</v>
       </c>
       <c r="G1475" t="n">
-        <v>23.7417430877686</v>
+        <v>23.7417449951172</v>
       </c>
       <c r="H1475" t="n">
         <v>4856</v>
@@ -43173,7 +43173,7 @@
         <v>31</v>
       </c>
       <c r="G1476" t="n">
-        <v>23.7417430877686</v>
+        <v>23.7417449951172</v>
       </c>
       <c r="H1476" t="n">
         <v>3245</v>
@@ -43231,7 +43231,7 @@
         <v>31</v>
       </c>
       <c r="G1478" t="n">
-        <v>23.7417430877686</v>
+        <v>23.7417449951172</v>
       </c>
       <c r="H1478" t="n">
         <v>13045</v>
@@ -43260,7 +43260,7 @@
         <v>31</v>
       </c>
       <c r="G1479" t="n">
-        <v>23.7417430877686</v>
+        <v>23.7417449951172</v>
       </c>
       <c r="H1479" t="n">
         <v>2034</v>
@@ -43376,7 +43376,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G1483" t="n">
-        <v>23.2439308166504</v>
+        <v>23.243932723999</v>
       </c>
       <c r="H1483" t="n">
         <v>10756</v>
@@ -43405,7 +43405,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1484" t="n">
-        <v>23.7034511566162</v>
+        <v>23.7034492492676</v>
       </c>
       <c r="H1484" t="n">
         <v>6039</v>
@@ -43463,7 +43463,7 @@
         <v>31</v>
       </c>
       <c r="G1486" t="n">
-        <v>23.7417430877686</v>
+        <v>23.7417449951172</v>
       </c>
       <c r="H1486" t="n">
         <v>23000</v>
@@ -43550,7 +43550,7 @@
         <v>32.25</v>
       </c>
       <c r="G1489" t="n">
-        <v>24.6990718841553</v>
+        <v>24.6990699768066</v>
       </c>
       <c r="H1489" t="n">
         <v>21145</v>
@@ -43608,7 +43608,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1491" t="n">
-        <v>24.4310188293457</v>
+        <v>24.4310169219971</v>
       </c>
       <c r="H1491" t="n">
         <v>8560</v>
@@ -43637,7 +43637,7 @@
         <v>32</v>
       </c>
       <c r="G1492" t="n">
-        <v>24.507604598999</v>
+        <v>24.5076065063477</v>
       </c>
       <c r="H1492" t="n">
         <v>10571</v>
@@ -43666,7 +43666,7 @@
         <v>32</v>
       </c>
       <c r="G1493" t="n">
-        <v>24.507604598999</v>
+        <v>24.5076065063477</v>
       </c>
       <c r="H1493" t="n">
         <v>3531</v>
@@ -43724,7 +43724,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1495" t="n">
-        <v>24.3544330596924</v>
+        <v>24.3544311523438</v>
       </c>
       <c r="H1495" t="n">
         <v>4157</v>
@@ -43782,7 +43782,7 @@
         <v>31</v>
       </c>
       <c r="G1497" t="n">
-        <v>23.7417430877686</v>
+        <v>23.7417449951172</v>
       </c>
       <c r="H1497" t="n">
         <v>5951</v>
@@ -43927,7 +43927,7 @@
         <v>31.75</v>
       </c>
       <c r="G1502" t="n">
-        <v>24.3161392211914</v>
+        <v>24.31614112854</v>
       </c>
       <c r="H1502" t="n">
         <v>5415</v>
@@ -44014,7 +44014,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1505" t="n">
-        <v>24.2395515441895</v>
+        <v>24.2395534515381</v>
       </c>
       <c r="H1505" t="n">
         <v>22431</v>
@@ -44072,7 +44072,7 @@
         <v>31.75</v>
       </c>
       <c r="G1507" t="n">
-        <v>24.3161392211914</v>
+        <v>24.31614112854</v>
       </c>
       <c r="H1507" t="n">
         <v>8593</v>
@@ -44101,7 +44101,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1508" t="n">
-        <v>24.2778472900391</v>
+        <v>24.2778453826904</v>
       </c>
       <c r="H1508" t="n">
         <v>11152</v>
@@ -44188,7 +44188,7 @@
         <v>33</v>
       </c>
       <c r="G1511" t="n">
-        <v>25.2734661102295</v>
+        <v>25.2734680175781</v>
       </c>
       <c r="H1511" t="n">
         <v>11956</v>
@@ -44217,7 +44217,7 @@
         <v>33</v>
       </c>
       <c r="G1512" t="n">
-        <v>25.2734661102295</v>
+        <v>25.2734680175781</v>
       </c>
       <c r="H1512" t="n">
         <v>11088</v>
@@ -44246,7 +44246,7 @@
         <v>33</v>
       </c>
       <c r="G1513" t="n">
-        <v>25.2734661102295</v>
+        <v>25.2734680175781</v>
       </c>
       <c r="H1513" t="n">
         <v>7325</v>
@@ -44333,7 +44333,7 @@
         <v>32.25</v>
       </c>
       <c r="G1516" t="n">
-        <v>24.6990718841553</v>
+        <v>24.6990699768066</v>
       </c>
       <c r="H1516" t="n">
         <v>1644</v>
@@ -44391,7 +44391,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1518" t="n">
-        <v>24.2778472900391</v>
+        <v>24.2778453826904</v>
       </c>
       <c r="H1518" t="n">
         <v>30728</v>
@@ -44420,7 +44420,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1519" t="n">
-        <v>24.4310188293457</v>
+        <v>24.4310169219971</v>
       </c>
       <c r="H1519" t="n">
         <v>12096</v>
@@ -44449,7 +44449,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G1520" t="n">
-        <v>24.5841903686523</v>
+        <v>24.584192276001</v>
       </c>
       <c r="H1520" t="n">
         <v>6410</v>
@@ -44594,7 +44594,7 @@
         <v>32.5</v>
       </c>
       <c r="G1525" t="n">
-        <v>24.8905391693115</v>
+        <v>24.8905372619629</v>
       </c>
       <c r="H1525" t="n">
         <v>7821</v>
@@ -44623,7 +44623,7 @@
         <v>32.5</v>
       </c>
       <c r="G1526" t="n">
-        <v>24.8905391693115</v>
+        <v>24.8905372619629</v>
       </c>
       <c r="H1526" t="n">
         <v>3179</v>
@@ -44710,7 +44710,7 @@
         <v>33</v>
       </c>
       <c r="G1529" t="n">
-        <v>25.2734661102295</v>
+        <v>25.2734680175781</v>
       </c>
       <c r="H1529" t="n">
         <v>14818</v>
@@ -44739,7 +44739,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1530" t="n">
-        <v>25.1202964782715</v>
+        <v>25.1202945709229</v>
       </c>
       <c r="H1530" t="n">
         <v>4286</v>
@@ -44826,7 +44826,7 @@
         <v>32.5</v>
       </c>
       <c r="G1533" t="n">
-        <v>24.8905391693115</v>
+        <v>24.8905372619629</v>
       </c>
       <c r="H1533" t="n">
         <v>5349</v>
@@ -44855,7 +44855,7 @@
         <v>32.5</v>
       </c>
       <c r="G1534" t="n">
-        <v>24.8905391693115</v>
+        <v>24.8905372619629</v>
       </c>
       <c r="H1534" t="n">
         <v>2624</v>
@@ -44884,7 +44884,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1535" t="n">
-        <v>25.1202964782715</v>
+        <v>25.1202945709229</v>
       </c>
       <c r="H1535" t="n">
         <v>3339</v>
@@ -44913,7 +44913,7 @@
         <v>32.5</v>
       </c>
       <c r="G1536" t="n">
-        <v>24.8905391693115</v>
+        <v>24.8905372619629</v>
       </c>
       <c r="H1536" t="n">
         <v>25407</v>
@@ -44942,7 +44942,7 @@
         <v>33</v>
       </c>
       <c r="G1537" t="n">
-        <v>25.2734661102295</v>
+        <v>25.2734680175781</v>
       </c>
       <c r="H1537" t="n">
         <v>4864</v>
@@ -45029,7 +45029,7 @@
         <v>32.5</v>
       </c>
       <c r="G1540" t="n">
-        <v>24.8905391693115</v>
+        <v>24.8905372619629</v>
       </c>
       <c r="H1540" t="n">
         <v>3417</v>
@@ -45058,7 +45058,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1541" t="n">
-        <v>24.4310188293457</v>
+        <v>24.4310169219971</v>
       </c>
       <c r="H1541" t="n">
         <v>7838</v>
@@ -45087,7 +45087,7 @@
         <v>30.5</v>
       </c>
       <c r="G1542" t="n">
-        <v>23.3588123321533</v>
+        <v>23.3588104248047</v>
       </c>
       <c r="H1542" t="n">
         <v>20110</v>
@@ -45116,7 +45116,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G1543" t="n">
-        <v>23.7034511566162</v>
+        <v>23.7034492492676</v>
       </c>
       <c r="H1543" t="n">
         <v>6497</v>
@@ -45145,7 +45145,7 @@
         <v>31.75</v>
       </c>
       <c r="G1544" t="n">
-        <v>24.3161392211914</v>
+        <v>24.31614112854</v>
       </c>
       <c r="H1544" t="n">
         <v>49257</v>
@@ -45174,7 +45174,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1545" t="n">
-        <v>24.2778472900391</v>
+        <v>24.2778453826904</v>
       </c>
       <c r="H1545" t="n">
         <v>13081</v>
@@ -45203,7 +45203,7 @@
         <v>31.75</v>
       </c>
       <c r="G1546" t="n">
-        <v>24.3161392211914</v>
+        <v>24.31614112854</v>
       </c>
       <c r="H1546" t="n">
         <v>11004</v>
@@ -45232,7 +45232,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1547" t="n">
-        <v>24.2778472900391</v>
+        <v>24.2778453826904</v>
       </c>
       <c r="H1547" t="n">
         <v>8602</v>
@@ -45348,7 +45348,7 @@
         <v>32</v>
       </c>
       <c r="G1551" t="n">
-        <v>24.507604598999</v>
+        <v>24.5076065063477</v>
       </c>
       <c r="H1551" t="n">
         <v>9542</v>
@@ -45464,7 +45464,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1555" t="n">
-        <v>24.3544330596924</v>
+        <v>24.3544311523438</v>
       </c>
       <c r="H1555" t="n">
         <v>3185</v>
@@ -45580,7 +45580,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G1559" t="n">
-        <v>24.2778472900391</v>
+        <v>24.2778453826904</v>
       </c>
       <c r="H1559" t="n">
         <v>7934</v>
@@ -45725,7 +45725,7 @@
         <v>31</v>
       </c>
       <c r="G1564" t="n">
-        <v>23.7417430877686</v>
+        <v>23.7417449951172</v>
       </c>
       <c r="H1564" t="n">
         <v>13400</v>
@@ -45754,7 +45754,7 @@
         <v>30.5</v>
       </c>
       <c r="G1565" t="n">
-        <v>23.3588123321533</v>
+        <v>23.3588104248047</v>
       </c>
       <c r="H1565" t="n">
         <v>19902</v>
@@ -45783,7 +45783,7 @@
         <v>31</v>
       </c>
       <c r="G1566" t="n">
-        <v>23.7417430877686</v>
+        <v>23.7417449951172</v>
       </c>
       <c r="H1566" t="n">
         <v>10517</v>
@@ -45812,7 +45812,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1567" t="n">
-        <v>23.5119857788086</v>
+        <v>23.5119876861572</v>
       </c>
       <c r="H1567" t="n">
         <v>10669</v>
@@ -45841,7 +45841,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G1568" t="n">
-        <v>23.4736919403076</v>
+        <v>23.4736881256104</v>
       </c>
       <c r="H1568" t="n">
         <v>9526</v>
@@ -45870,7 +45870,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1569" t="n">
-        <v>23.1290550231934</v>
+        <v>23.1290531158447</v>
       </c>
       <c r="H1569" t="n">
         <v>6815</v>
@@ -45986,7 +45986,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1573" t="n">
-        <v>21.5207405090332</v>
+        <v>21.5207424163818</v>
       </c>
       <c r="H1573" t="n">
         <v>12641</v>
@@ -46218,7 +46218,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G1581" t="n">
-        <v>22.7078266143799</v>
+        <v>22.7078285217285</v>
       </c>
       <c r="H1581" t="n">
         <v>22398</v>
@@ -46247,7 +46247,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G1582" t="n">
-        <v>22.4780712127686</v>
+        <v>22.4780693054199</v>
       </c>
       <c r="H1582" t="n">
         <v>13178</v>
@@ -46276,7 +46276,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G1583" t="n">
-        <v>22.7078266143799</v>
+        <v>22.7078285217285</v>
       </c>
       <c r="H1583" t="n">
         <v>4756</v>
@@ -46305,7 +46305,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G1584" t="n">
-        <v>22.7078266143799</v>
+        <v>22.7078285217285</v>
       </c>
       <c r="H1584" t="n">
         <v>5864</v>
@@ -46363,7 +46363,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1586" t="n">
-        <v>22.5163612365723</v>
+        <v>22.5163631439209</v>
       </c>
       <c r="H1586" t="n">
         <v>3353</v>
@@ -46392,7 +46392,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1587" t="n">
-        <v>22.5163612365723</v>
+        <v>22.5163631439209</v>
       </c>
       <c r="H1587" t="n">
         <v>5318</v>
@@ -46479,7 +46479,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1590" t="n">
-        <v>22.133430480957</v>
+        <v>22.1334323883057</v>
       </c>
       <c r="H1590" t="n">
         <v>10987</v>
@@ -46566,7 +46566,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1593" t="n">
-        <v>21.8653793334961</v>
+        <v>21.8653774261475</v>
       </c>
       <c r="H1593" t="n">
         <v>16659</v>
@@ -46653,7 +46653,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1596" t="n">
-        <v>22.2866058349609</v>
+        <v>22.2866039276123</v>
       </c>
       <c r="H1596" t="n">
         <v>5563</v>
@@ -46682,7 +46682,7 @@
         <v>29.9500007629395</v>
       </c>
       <c r="G1597" t="n">
-        <v>22.9375858306885</v>
+        <v>22.9375896453857</v>
       </c>
       <c r="H1597" t="n">
         <v>23075</v>
@@ -46827,7 +46827,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G1602" t="n">
-        <v>22.3248977661133</v>
+        <v>22.3248958587646</v>
       </c>
       <c r="H1602" t="n">
         <v>4002</v>
@@ -46885,7 +46885,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1604" t="n">
-        <v>23.1290550231934</v>
+        <v>23.1290531158447</v>
       </c>
       <c r="H1604" t="n">
         <v>22535</v>
@@ -47030,7 +47030,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1609" t="n">
-        <v>23.1290550231934</v>
+        <v>23.1290531158447</v>
       </c>
       <c r="H1609" t="n">
         <v>5704</v>
@@ -47059,7 +47059,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1610" t="n">
-        <v>23.2822265625</v>
+        <v>23.2822246551514</v>
       </c>
       <c r="H1610" t="n">
         <v>9681</v>
@@ -79951,6 +79951,64 @@
         <v>8756</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>24.7999992370605</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>15721</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>24.8500003814697</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>24.8500003814697</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>24.4500007629395</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>24.7000007629395</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>24.7000007629395</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>3977</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>
